--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -6830,10 +6830,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119718968</v>
+        <v>119718975</v>
       </c>
       <c r="B57" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>752875</v>
+        <v>752883</v>
       </c>
       <c r="R57" t="n">
-        <v>7092391</v>
+        <v>7092344</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119718969</v>
+        <v>119718968</v>
       </c>
       <c r="B58" t="n">
         <v>91884</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752839</v>
+        <v>752875</v>
       </c>
       <c r="R58" t="n">
-        <v>7092424</v>
+        <v>7092391</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119718975</v>
+        <v>119718969</v>
       </c>
       <c r="B59" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>752883</v>
+        <v>752839</v>
       </c>
       <c r="R59" t="n">
-        <v>7092344</v>
+        <v>7092424</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7136,10 +7136,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119718971</v>
+        <v>119718959</v>
       </c>
       <c r="B60" t="n">
-        <v>84211</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7148,25 +7148,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3518</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7176,10 +7176,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>752816</v>
+        <v>752778</v>
       </c>
       <c r="R60" t="n">
-        <v>7092600</v>
+        <v>7092543</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119718959</v>
+        <v>119718986</v>
       </c>
       <c r="B61" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7254,21 +7254,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7278,10 +7278,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>752778</v>
+        <v>752810</v>
       </c>
       <c r="R61" t="n">
-        <v>7092543</v>
+        <v>7092635</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119718986</v>
+        <v>119718971</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>84211</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>3518</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>752810</v>
+        <v>752816</v>
       </c>
       <c r="R62" t="n">
-        <v>7092635</v>
+        <v>7092600</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718983</v>
+        <v>119718965</v>
       </c>
       <c r="B66" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752779</v>
+        <v>752909</v>
       </c>
       <c r="R66" t="n">
-        <v>7092474</v>
+        <v>7092430</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718965</v>
+        <v>119718983</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752909</v>
+        <v>752779</v>
       </c>
       <c r="R67" t="n">
-        <v>7092430</v>
+        <v>7092474</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -11258,10 +11258,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797533</v>
+        <v>119797599</v>
       </c>
       <c r="B100" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11270,43 +11270,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752826</v>
+        <v>752863</v>
       </c>
       <c r="R100" t="n">
-        <v>7092234</v>
+        <v>7092380</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11365,10 +11360,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797599</v>
+        <v>119797533</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11377,38 +11372,43 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752863</v>
+        <v>752826</v>
       </c>
       <c r="R101" t="n">
-        <v>7092380</v>
+        <v>7092234</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12501,10 +12501,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119797554</v>
+        <v>119797534</v>
       </c>
       <c r="B112" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12517,21 +12517,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12541,10 +12541,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>752858</v>
+        <v>752725</v>
       </c>
       <c r="R112" t="n">
-        <v>7092376</v>
+        <v>7092290</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12603,10 +12603,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119797560</v>
+        <v>119797530</v>
       </c>
       <c r="B113" t="n">
-        <v>57326</v>
+        <v>89275</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12615,43 +12615,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>752728</v>
+        <v>752727</v>
       </c>
       <c r="R113" t="n">
-        <v>7092269</v>
+        <v>7092459</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12686,11 +12681,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12699,26 +12689,6 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12735,10 +12705,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119797534</v>
+        <v>119797554</v>
       </c>
       <c r="B114" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12751,21 +12721,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12775,10 +12745,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>752725</v>
+        <v>752858</v>
       </c>
       <c r="R114" t="n">
-        <v>7092290</v>
+        <v>7092376</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12837,10 +12807,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119797530</v>
+        <v>119797560</v>
       </c>
       <c r="B115" t="n">
-        <v>89275</v>
+        <v>57326</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12849,38 +12819,43 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6286</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>752727</v>
+        <v>752728</v>
       </c>
       <c r="R115" t="n">
-        <v>7092459</v>
+        <v>7092269</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12915,6 +12890,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -12923,6 +12903,26 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
@@ -13143,10 +13143,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119797564</v>
+        <v>119797594</v>
       </c>
       <c r="B118" t="n">
-        <v>91852</v>
+        <v>89252</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13155,25 +13155,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13183,10 +13183,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>752716</v>
+        <v>752842</v>
       </c>
       <c r="R118" t="n">
-        <v>7092384</v>
+        <v>7092347</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13219,6 +13219,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13245,10 +13250,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119797611</v>
+        <v>119797595</v>
       </c>
       <c r="B119" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13257,38 +13262,42 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>752818</v>
+        <v>752803</v>
       </c>
       <c r="R119" t="n">
-        <v>7092235</v>
+        <v>7092370</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13321,6 +13330,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Bredvid grop</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13347,7 +13361,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119797566</v>
+        <v>119797564</v>
       </c>
       <c r="B120" t="n">
         <v>91852</v>
@@ -13387,10 +13401,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>752868</v>
+        <v>752716</v>
       </c>
       <c r="R120" t="n">
-        <v>7092254</v>
+        <v>7092384</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13449,10 +13463,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119797570</v>
+        <v>119797611</v>
       </c>
       <c r="B121" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13465,21 +13479,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13489,10 +13503,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>752707</v>
+        <v>752818</v>
       </c>
       <c r="R121" t="n">
-        <v>7092347</v>
+        <v>7092235</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13525,11 +13539,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Stigen</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13556,10 +13565,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119797573</v>
+        <v>119797566</v>
       </c>
       <c r="B122" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13568,25 +13577,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13596,10 +13605,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>752711</v>
+        <v>752868</v>
       </c>
       <c r="R122" t="n">
-        <v>7092477</v>
+        <v>7092254</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13658,7 +13667,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119797576</v>
+        <v>119797570</v>
       </c>
       <c r="B123" t="n">
         <v>91832</v>
@@ -13698,10 +13707,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>752864</v>
+        <v>752707</v>
       </c>
       <c r="R123" t="n">
-        <v>7092357</v>
+        <v>7092347</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13734,6 +13743,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Stigen</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13760,10 +13774,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119797594</v>
+        <v>119797573</v>
       </c>
       <c r="B124" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13772,25 +13786,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13800,10 +13814,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>752842</v>
+        <v>752711</v>
       </c>
       <c r="R124" t="n">
-        <v>7092347</v>
+        <v>7092477</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13836,11 +13850,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13867,10 +13876,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119797595</v>
+        <v>119797576</v>
       </c>
       <c r="B125" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13879,42 +13888,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>752803</v>
+        <v>752864</v>
       </c>
       <c r="R125" t="n">
-        <v>7092370</v>
+        <v>7092357</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13947,11 +13952,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Bredvid grop</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15207,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797572</v>
+        <v>119797532</v>
       </c>
       <c r="B138" t="n">
-        <v>91832</v>
+        <v>57463</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15223,34 +15223,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752714</v>
+        <v>752730</v>
       </c>
       <c r="R138" t="n">
-        <v>7092390</v>
+        <v>7092301</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15309,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797532</v>
+        <v>119797572</v>
       </c>
       <c r="B139" t="n">
-        <v>57463</v>
+        <v>91832</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15325,39 +15330,34 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752730</v>
+        <v>752714</v>
       </c>
       <c r="R139" t="n">
-        <v>7092301</v>
+        <v>7092390</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15966,10 +15966,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808292</v>
+        <v>119808299</v>
       </c>
       <c r="B145" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15978,25 +15978,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752837</v>
+        <v>752962</v>
       </c>
       <c r="R145" t="n">
-        <v>7092228</v>
+        <v>7092343</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,7 +16078,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808299</v>
+        <v>119808293</v>
       </c>
       <c r="B146" t="n">
         <v>91840</v>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752962</v>
+        <v>752820</v>
       </c>
       <c r="R146" t="n">
-        <v>7092343</v>
+        <v>7092239</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16190,10 +16190,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119808293</v>
+        <v>119808292</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16202,25 +16202,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752820</v>
+        <v>752837</v>
       </c>
       <c r="R147" t="n">
-        <v>7092239</v>
+        <v>7092228</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16302,10 +16302,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119808297</v>
+        <v>119808296</v>
       </c>
       <c r="B148" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16314,25 +16314,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16342,10 +16342,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752905</v>
+        <v>752902</v>
       </c>
       <c r="R148" t="n">
-        <v>7092298</v>
+        <v>7092285</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16414,7 +16414,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119808305</v>
+        <v>119808297</v>
       </c>
       <c r="B149" t="n">
         <v>91884</v>
@@ -16454,10 +16454,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752740</v>
+        <v>752905</v>
       </c>
       <c r="R149" t="n">
-        <v>7092467</v>
+        <v>7092298</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16526,7 +16526,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119808309</v>
+        <v>119808305</v>
       </c>
       <c r="B150" t="n">
         <v>91884</v>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752727</v>
+        <v>752740</v>
       </c>
       <c r="R150" t="n">
-        <v>7092321</v>
+        <v>7092467</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16638,10 +16638,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119808296</v>
+        <v>119808309</v>
       </c>
       <c r="B151" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16650,25 +16650,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752902</v>
+        <v>752727</v>
       </c>
       <c r="R151" t="n">
-        <v>7092285</v>
+        <v>7092321</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16862,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808312</v>
+        <v>119808302</v>
       </c>
       <c r="B153" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16874,25 +16874,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752773</v>
+        <v>752841</v>
       </c>
       <c r="R153" t="n">
-        <v>7092341</v>
+        <v>7092401</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808302</v>
+        <v>119808312</v>
       </c>
       <c r="B154" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16986,25 +16986,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752841</v>
+        <v>752773</v>
       </c>
       <c r="R154" t="n">
-        <v>7092401</v>
+        <v>7092341</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934795</v>
+        <v>119934819</v>
       </c>
       <c r="B186" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,42 +20353,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752996</v>
+        <v>752979</v>
       </c>
       <c r="R186" t="n">
-        <v>7092398</v>
+        <v>7092382</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20421,11 +20417,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20452,10 +20443,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934789</v>
+        <v>119934778</v>
       </c>
       <c r="B187" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20468,38 +20459,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752803</v>
+        <v>752778</v>
       </c>
       <c r="R187" t="n">
-        <v>7092378</v>
+        <v>7092476</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20558,10 +20545,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934778</v>
+        <v>119934795</v>
       </c>
       <c r="B188" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20574,34 +20561,38 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752778</v>
+        <v>752996</v>
       </c>
       <c r="R188" t="n">
-        <v>7092476</v>
+        <v>7092398</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20634,6 +20625,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20660,10 +20656,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934819</v>
+        <v>119934789</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20672,38 +20668,42 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752979</v>
+        <v>752803</v>
       </c>
       <c r="R189" t="n">
-        <v>7092382</v>
+        <v>7092378</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22981,10 +22981,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934760</v>
+        <v>119934808</v>
       </c>
       <c r="B211" t="n">
-        <v>91884</v>
+        <v>89252</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22993,30 +22993,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23025,10 +23025,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752896</v>
+        <v>752819</v>
       </c>
       <c r="R211" t="n">
-        <v>7092456</v>
+        <v>7092515</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23087,10 +23087,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934783</v>
+        <v>119934760</v>
       </c>
       <c r="B212" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23103,26 +23103,26 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -23131,10 +23131,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752771</v>
+        <v>752896</v>
       </c>
       <c r="R212" t="n">
-        <v>7092674</v>
+        <v>7092456</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23167,11 +23167,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23198,7 +23193,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934787</v>
+        <v>119934783</v>
       </c>
       <c r="B213" t="n">
         <v>91832</v>
@@ -23233,7 +23228,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23242,10 +23237,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752738</v>
+        <v>752771</v>
       </c>
       <c r="R213" t="n">
-        <v>7092548</v>
+        <v>7092674</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23282,7 +23277,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Vid stig</t>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23309,10 +23304,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934808</v>
+        <v>119934787</v>
       </c>
       <c r="B214" t="n">
-        <v>89252</v>
+        <v>91832</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23321,30 +23316,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23353,10 +23348,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752819</v>
+        <v>752738</v>
       </c>
       <c r="R214" t="n">
-        <v>7092515</v>
+        <v>7092548</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23389,6 +23384,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24558,10 +24558,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934812</v>
+        <v>119934798</v>
       </c>
       <c r="B226" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24570,25 +24570,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24598,10 +24598,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752796</v>
+        <v>752945</v>
       </c>
       <c r="R226" t="n">
-        <v>7092694</v>
+        <v>7092339</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24660,10 +24660,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934798</v>
+        <v>119934812</v>
       </c>
       <c r="B227" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24672,25 +24672,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24700,10 +24700,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752945</v>
+        <v>752796</v>
       </c>
       <c r="R227" t="n">
-        <v>7092339</v>
+        <v>7092694</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25598,10 +25598,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934748</v>
+        <v>119934761</v>
       </c>
       <c r="B236" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25614,34 +25614,38 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752762</v>
+        <v>752772</v>
       </c>
       <c r="R236" t="n">
-        <v>7092586</v>
+        <v>7092487</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25676,11 +25680,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD236" t="b">
         <v>0</v>
       </c>
@@ -25689,21 +25688,6 @@
       </c>
       <c r="AG236" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ236" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK236" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
@@ -25720,10 +25704,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934810</v>
+        <v>119934748</v>
       </c>
       <c r="B237" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25732,42 +25716,38 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752803</v>
+        <v>752762</v>
       </c>
       <c r="R237" t="n">
-        <v>7092670</v>
+        <v>7092586</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25802,6 +25782,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD237" t="b">
         <v>0</v>
       </c>
@@ -25810,6 +25795,21 @@
       </c>
       <c r="AG237" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT237" t="inlineStr"/>
       <c r="AW237" t="inlineStr">
@@ -25826,10 +25826,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934761</v>
+        <v>119934810</v>
       </c>
       <c r="B238" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25838,30 +25838,30 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -25870,10 +25870,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752772</v>
+        <v>752803</v>
       </c>
       <c r="R238" t="n">
-        <v>7092487</v>
+        <v>7092670</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -6830,10 +6830,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119718975</v>
+        <v>119718968</v>
       </c>
       <c r="B57" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>752883</v>
+        <v>752875</v>
       </c>
       <c r="R57" t="n">
-        <v>7092344</v>
+        <v>7092391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119718968</v>
+        <v>119718969</v>
       </c>
       <c r="B58" t="n">
         <v>91884</v>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752875</v>
+        <v>752839</v>
       </c>
       <c r="R58" t="n">
-        <v>7092391</v>
+        <v>7092424</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119718969</v>
+        <v>119718975</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>752839</v>
+        <v>752883</v>
       </c>
       <c r="R59" t="n">
-        <v>7092424</v>
+        <v>7092344</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -16862,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808302</v>
+        <v>119808312</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16874,25 +16874,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752841</v>
+        <v>752773</v>
       </c>
       <c r="R153" t="n">
-        <v>7092401</v>
+        <v>7092341</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808312</v>
+        <v>119808302</v>
       </c>
       <c r="B154" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16986,25 +16986,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752773</v>
+        <v>752841</v>
       </c>
       <c r="R154" t="n">
-        <v>7092341</v>
+        <v>7092401</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD154" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -6830,10 +6830,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119718973</v>
+        <v>119718969</v>
       </c>
       <c r="B57" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6846,21 +6846,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>752804</v>
+        <v>752839</v>
       </c>
       <c r="R57" t="n">
-        <v>7092441</v>
+        <v>7092424</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119718969</v>
+        <v>119718973</v>
       </c>
       <c r="B58" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6948,21 +6948,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6972,10 +6972,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>752839</v>
+        <v>752804</v>
       </c>
       <c r="R58" t="n">
-        <v>7092424</v>
+        <v>7092441</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119718968</v>
+        <v>119718985</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7352,25 +7352,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7380,10 +7380,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>752875</v>
+        <v>752967</v>
       </c>
       <c r="R62" t="n">
-        <v>7092391</v>
+        <v>7092339</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7442,10 +7442,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119718985</v>
+        <v>119718968</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7454,25 +7454,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>752967</v>
+        <v>752875</v>
       </c>
       <c r="R63" t="n">
-        <v>7092339</v>
+        <v>7092391</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8462,10 +8462,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119718971</v>
+        <v>119718957</v>
       </c>
       <c r="B73" t="n">
-        <v>84211</v>
+        <v>57463</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8474,38 +8474,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3518</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>752816</v>
+        <v>752907</v>
       </c>
       <c r="R73" t="n">
-        <v>7092600</v>
+        <v>7092425</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8564,10 +8573,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119718986</v>
+        <v>119718971</v>
       </c>
       <c r="B74" t="n">
-        <v>91834</v>
+        <v>84211</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8576,25 +8585,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>3518</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8604,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>752810</v>
+        <v>752816</v>
       </c>
       <c r="R74" t="n">
-        <v>7092635</v>
+        <v>7092600</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8666,10 +8675,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119718959</v>
+        <v>119718986</v>
       </c>
       <c r="B75" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8682,21 +8691,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8706,10 +8715,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>752778</v>
+        <v>752810</v>
       </c>
       <c r="R75" t="n">
-        <v>7092543</v>
+        <v>7092635</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8768,10 +8777,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119718984</v>
+        <v>119718959</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8780,25 +8789,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8808,10 +8817,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>752957</v>
+        <v>752778</v>
       </c>
       <c r="R76" t="n">
-        <v>7092406</v>
+        <v>7092543</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8870,10 +8879,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119718957</v>
+        <v>119718984</v>
       </c>
       <c r="B77" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8882,47 +8891,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>752907</v>
+        <v>752957</v>
       </c>
       <c r="R77" t="n">
-        <v>7092425</v>
+        <v>7092406</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797564</v>
+        <v>119797557</v>
       </c>
       <c r="B86" t="n">
-        <v>91852</v>
+        <v>91884</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9814,25 +9814,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752716</v>
+        <v>752808</v>
       </c>
       <c r="R86" t="n">
-        <v>7092384</v>
+        <v>7092251</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9904,10 +9904,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797540</v>
+        <v>119797564</v>
       </c>
       <c r="B87" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9916,25 +9916,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9944,10 +9944,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752867</v>
+        <v>752716</v>
       </c>
       <c r="R87" t="n">
-        <v>7092243</v>
+        <v>7092384</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9980,11 +9980,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10011,7 +10006,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797547</v>
+        <v>119797540</v>
       </c>
       <c r="B88" t="n">
         <v>91884</v>
@@ -10051,10 +10046,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752758</v>
+        <v>752867</v>
       </c>
       <c r="R88" t="n">
-        <v>7092263</v>
+        <v>7092243</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10087,6 +10082,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10113,7 +10113,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797557</v>
+        <v>119797547</v>
       </c>
       <c r="B89" t="n">
         <v>91884</v>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752808</v>
+        <v>752758</v>
       </c>
       <c r="R89" t="n">
-        <v>7092251</v>
+        <v>7092263</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -16414,7 +16414,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119808314</v>
+        <v>119808305</v>
       </c>
       <c r="B149" t="n">
         <v>91884</v>
@@ -16454,10 +16454,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752795</v>
+        <v>752740</v>
       </c>
       <c r="R149" t="n">
-        <v>7092304</v>
+        <v>7092467</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16526,7 +16526,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119808305</v>
+        <v>119808314</v>
       </c>
       <c r="B150" t="n">
         <v>91884</v>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752740</v>
+        <v>752795</v>
       </c>
       <c r="R150" t="n">
-        <v>7092467</v>
+        <v>7092304</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16862,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808307</v>
+        <v>119808302</v>
       </c>
       <c r="B153" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16878,21 +16878,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752764</v>
+        <v>752841</v>
       </c>
       <c r="R153" t="n">
-        <v>7092409</v>
+        <v>7092401</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808302</v>
+        <v>119808307</v>
       </c>
       <c r="B154" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16990,21 +16990,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752841</v>
+        <v>752764</v>
       </c>
       <c r="R154" t="n">
-        <v>7092401</v>
+        <v>7092409</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17086,10 +17086,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808308</v>
+        <v>119808294</v>
       </c>
       <c r="B155" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17098,25 +17098,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752743</v>
+        <v>752867</v>
       </c>
       <c r="R155" t="n">
-        <v>7092343</v>
+        <v>7092294</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17198,7 +17198,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119808295</v>
+        <v>119808308</v>
       </c>
       <c r="B156" t="n">
         <v>91884</v>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752872</v>
+        <v>752743</v>
       </c>
       <c r="R156" t="n">
-        <v>7092301</v>
+        <v>7092343</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17310,10 +17310,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119808294</v>
+        <v>119808295</v>
       </c>
       <c r="B157" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17322,25 +17322,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17350,10 +17350,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752867</v>
+        <v>752872</v>
       </c>
       <c r="R157" t="n">
-        <v>7092294</v>
+        <v>7092301</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18811,10 +18811,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119893483</v>
+        <v>119893537</v>
       </c>
       <c r="B171" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18827,21 +18827,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18851,10 +18851,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752795</v>
+        <v>752759</v>
       </c>
       <c r="R171" t="n">
-        <v>7092265</v>
+        <v>7092324</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18913,10 +18913,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893537</v>
+        <v>119893483</v>
       </c>
       <c r="B172" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18929,21 +18929,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18953,10 +18953,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752759</v>
+        <v>752795</v>
       </c>
       <c r="R172" t="n">
-        <v>7092324</v>
+        <v>7092265</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934823</v>
+        <v>119934810</v>
       </c>
       <c r="B186" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,30 +20353,30 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -20385,10 +20385,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752959</v>
+        <v>752803</v>
       </c>
       <c r="R186" t="n">
-        <v>7092467</v>
+        <v>7092670</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20447,10 +20447,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934762</v>
+        <v>119934815</v>
       </c>
       <c r="B187" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20459,42 +20459,38 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752732</v>
+        <v>752779</v>
       </c>
       <c r="R187" t="n">
-        <v>7092502</v>
+        <v>7092482</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20553,10 +20549,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934810</v>
+        <v>119934762</v>
       </c>
       <c r="B188" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20565,30 +20561,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20597,10 +20593,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752803</v>
+        <v>752732</v>
       </c>
       <c r="R188" t="n">
-        <v>7092670</v>
+        <v>7092502</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20659,10 +20655,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934815</v>
+        <v>119934823</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20671,38 +20667,42 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752779</v>
+        <v>752959</v>
       </c>
       <c r="R189" t="n">
-        <v>7092482</v>
+        <v>7092467</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20761,10 +20761,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934789</v>
+        <v>119934809</v>
       </c>
       <c r="B190" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20773,30 +20773,30 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -20805,7 +20805,7 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752803</v>
+        <v>752817</v>
       </c>
       <c r="R190" t="n">
         <v>7092378</v>
@@ -20969,10 +20969,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934809</v>
+        <v>119934789</v>
       </c>
       <c r="B192" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20981,30 +20981,30 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752817</v>
+        <v>752803</v>
       </c>
       <c r="R192" t="n">
         <v>7092378</v>
@@ -21075,10 +21075,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934772</v>
+        <v>119934791</v>
       </c>
       <c r="B193" t="n">
-        <v>91844</v>
+        <v>91832</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21087,38 +21087,42 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752757</v>
+        <v>752777</v>
       </c>
       <c r="R193" t="n">
-        <v>7092617</v>
+        <v>7092488</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21151,11 +21155,6 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21182,10 +21181,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934791</v>
+        <v>119934772</v>
       </c>
       <c r="B194" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21194,42 +21193,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752777</v>
+        <v>752757</v>
       </c>
       <c r="R194" t="n">
-        <v>7092488</v>
+        <v>7092617</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21262,6 +21257,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21288,10 +21288,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934818</v>
+        <v>119934760</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21300,38 +21300,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>753030</v>
+        <v>752896</v>
       </c>
       <c r="R195" t="n">
-        <v>7092403</v>
+        <v>7092456</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21390,7 +21394,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934760</v>
+        <v>119934767</v>
       </c>
       <c r="B196" t="n">
         <v>91884</v>
@@ -21423,21 +21427,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752896</v>
+        <v>752720</v>
       </c>
       <c r="R196" t="n">
-        <v>7092456</v>
+        <v>7092493</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21496,10 +21496,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934767</v>
+        <v>119934818</v>
       </c>
       <c r="B197" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21508,25 +21508,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21536,10 +21536,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752720</v>
+        <v>753030</v>
       </c>
       <c r="R197" t="n">
-        <v>7092493</v>
+        <v>7092403</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23403,10 +23403,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934798</v>
+        <v>119934806</v>
       </c>
       <c r="B215" t="n">
-        <v>91832</v>
+        <v>89252</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23415,38 +23415,42 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752945</v>
+        <v>752816</v>
       </c>
       <c r="R215" t="n">
-        <v>7092339</v>
+        <v>7092714</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23505,10 +23509,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934766</v>
+        <v>119934752</v>
       </c>
       <c r="B216" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23517,42 +23521,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752751</v>
+        <v>752794</v>
       </c>
       <c r="R216" t="n">
-        <v>7092507</v>
+        <v>7092570</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23585,6 +23585,11 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23611,10 +23616,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934761</v>
+        <v>119934798</v>
       </c>
       <c r="B217" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23627,38 +23632,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752772</v>
+        <v>752945</v>
       </c>
       <c r="R217" t="n">
-        <v>7092487</v>
+        <v>7092339</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23717,10 +23718,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934806</v>
+        <v>119934766</v>
       </c>
       <c r="B218" t="n">
-        <v>89252</v>
+        <v>91884</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23729,30 +23730,30 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -23761,10 +23762,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752816</v>
+        <v>752751</v>
       </c>
       <c r="R218" t="n">
-        <v>7092714</v>
+        <v>7092507</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23823,10 +23824,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934752</v>
+        <v>119934761</v>
       </c>
       <c r="B219" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23835,38 +23836,42 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752794</v>
+        <v>752772</v>
       </c>
       <c r="R219" t="n">
-        <v>7092570</v>
+        <v>7092487</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23899,11 +23904,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24346,10 +24346,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934792</v>
+        <v>119934774</v>
       </c>
       <c r="B224" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24362,26 +24362,26 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24390,10 +24390,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752867</v>
+        <v>752891</v>
       </c>
       <c r="R224" t="n">
-        <v>7092495</v>
+        <v>7092444</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24452,10 +24452,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934774</v>
+        <v>119934792</v>
       </c>
       <c r="B225" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24468,26 +24468,26 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24496,10 +24496,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752891</v>
+        <v>752867</v>
       </c>
       <c r="R225" t="n">
-        <v>7092444</v>
+        <v>7092495</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25502,10 +25502,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934783</v>
+        <v>119934775</v>
       </c>
       <c r="B235" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25518,26 +25518,26 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P235" t="inlineStr">
@@ -25546,10 +25546,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752771</v>
+        <v>752777</v>
       </c>
       <c r="R235" t="n">
-        <v>7092674</v>
+        <v>7092577</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25582,11 +25582,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25613,7 +25608,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934787</v>
+        <v>119934783</v>
       </c>
       <c r="B236" t="n">
         <v>91832</v>
@@ -25648,7 +25643,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -25657,10 +25652,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752738</v>
+        <v>752771</v>
       </c>
       <c r="R236" t="n">
-        <v>7092548</v>
+        <v>7092674</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25697,7 +25692,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Vid stig</t>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25724,10 +25719,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934768</v>
+        <v>119934787</v>
       </c>
       <c r="B237" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25740,34 +25735,38 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752771</v>
+        <v>752738</v>
       </c>
       <c r="R237" t="n">
-        <v>7092668</v>
+        <v>7092548</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25800,6 +25799,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25826,10 +25830,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934775</v>
+        <v>119934768</v>
       </c>
       <c r="B238" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25842,38 +25846,34 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752777</v>
+        <v>752771</v>
       </c>
       <c r="R238" t="n">
-        <v>7092577</v>
+        <v>7092668</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -8666,10 +8666,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119718981</v>
+        <v>119718984</v>
       </c>
       <c r="B75" t="n">
-        <v>89212</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8678,25 +8678,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1593</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8706,10 +8706,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>752869</v>
+        <v>752957</v>
       </c>
       <c r="R75" t="n">
-        <v>7092414</v>
+        <v>7092406</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119718984</v>
+        <v>119718981</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>89212</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8780,25 +8780,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>752957</v>
+        <v>752869</v>
       </c>
       <c r="R76" t="n">
-        <v>7092406</v>
+        <v>7092414</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10856,10 +10856,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797597</v>
+        <v>119797583</v>
       </c>
       <c r="B96" t="n">
-        <v>89252</v>
+        <v>91863</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10868,25 +10868,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752839</v>
+        <v>752719</v>
       </c>
       <c r="R96" t="n">
-        <v>7092201</v>
+        <v>7092452</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10958,10 +10958,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797583</v>
+        <v>119797597</v>
       </c>
       <c r="B97" t="n">
-        <v>91863</v>
+        <v>89252</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10970,25 +10970,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>6276</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10998,10 +10998,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752719</v>
+        <v>752839</v>
       </c>
       <c r="R97" t="n">
-        <v>7092452</v>
+        <v>7092201</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11580,10 +11580,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797599</v>
+        <v>119797556</v>
       </c>
       <c r="B103" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11592,25 +11592,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11620,10 +11620,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752863</v>
+        <v>752877</v>
       </c>
       <c r="R103" t="n">
-        <v>7092380</v>
+        <v>7092306</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11682,10 +11682,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797579</v>
+        <v>119797599</v>
       </c>
       <c r="B104" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11694,25 +11694,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11722,10 +11722,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752762</v>
+        <v>752863</v>
       </c>
       <c r="R104" t="n">
-        <v>7092223</v>
+        <v>7092380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11784,7 +11784,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119797578</v>
+        <v>119797579</v>
       </c>
       <c r="B105" t="n">
         <v>91832</v>
@@ -11824,10 +11824,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>752895</v>
+        <v>752762</v>
       </c>
       <c r="R105" t="n">
-        <v>7092346</v>
+        <v>7092223</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11886,10 +11886,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119797556</v>
+        <v>119797578</v>
       </c>
       <c r="B106" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11902,21 +11902,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11926,10 +11926,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>752877</v>
+        <v>752895</v>
       </c>
       <c r="R106" t="n">
-        <v>7092306</v>
+        <v>7092346</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -14270,10 +14270,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119797557</v>
+        <v>119797602</v>
       </c>
       <c r="B129" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14282,25 +14282,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14310,10 +14310,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>752808</v>
+        <v>752769</v>
       </c>
       <c r="R129" t="n">
-        <v>7092251</v>
+        <v>7092291</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14372,10 +14372,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119797537</v>
+        <v>119797533</v>
       </c>
       <c r="B130" t="n">
-        <v>91883</v>
+        <v>57463</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14388,34 +14388,39 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>752807</v>
+        <v>752826</v>
       </c>
       <c r="R130" t="n">
-        <v>7092369</v>
+        <v>7092234</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14448,11 +14453,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14479,10 +14479,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119797602</v>
+        <v>119797557</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14491,25 +14491,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14519,10 +14519,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>752769</v>
+        <v>752808</v>
       </c>
       <c r="R131" t="n">
-        <v>7092291</v>
+        <v>7092251</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14581,10 +14581,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797533</v>
+        <v>119797537</v>
       </c>
       <c r="B132" t="n">
-        <v>57463</v>
+        <v>91883</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14597,39 +14597,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752826</v>
+        <v>752807</v>
       </c>
       <c r="R132" t="n">
-        <v>7092234</v>
+        <v>7092369</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14662,6 +14657,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -21178,10 +21178,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934817</v>
+        <v>119934776</v>
       </c>
       <c r="B194" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21190,38 +21190,42 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752778</v>
+        <v>752759</v>
       </c>
       <c r="R194" t="n">
-        <v>7092478</v>
+        <v>7092525</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21280,10 +21284,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934818</v>
+        <v>119934774</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21292,38 +21296,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>753030</v>
+        <v>752891</v>
       </c>
       <c r="R195" t="n">
-        <v>7092403</v>
+        <v>7092444</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21382,10 +21390,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934776</v>
+        <v>119934762</v>
       </c>
       <c r="B196" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21398,26 +21406,26 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21426,10 +21434,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752759</v>
+        <v>752732</v>
       </c>
       <c r="R196" t="n">
-        <v>7092525</v>
+        <v>7092502</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21488,10 +21496,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934774</v>
+        <v>119934817</v>
       </c>
       <c r="B197" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21500,42 +21508,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752891</v>
+        <v>752778</v>
       </c>
       <c r="R197" t="n">
-        <v>7092444</v>
+        <v>7092478</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21594,10 +21598,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934762</v>
+        <v>119934818</v>
       </c>
       <c r="B198" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21606,42 +21610,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752732</v>
+        <v>753030</v>
       </c>
       <c r="R198" t="n">
-        <v>7092502</v>
+        <v>7092403</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -25838,10 +25838,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934796</v>
+        <v>119934767</v>
       </c>
       <c r="B238" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25854,21 +25854,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25878,10 +25878,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752805</v>
+        <v>752720</v>
       </c>
       <c r="R238" t="n">
-        <v>7092505</v>
+        <v>7092493</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25940,10 +25940,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934767</v>
+        <v>119934796</v>
       </c>
       <c r="B239" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25956,21 +25956,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25980,10 +25980,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752720</v>
+        <v>752805</v>
       </c>
       <c r="R239" t="n">
-        <v>7092493</v>
+        <v>7092505</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718981</v>
+        <v>119718959</v>
       </c>
       <c r="B66" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752869</v>
+        <v>752778</v>
       </c>
       <c r="R66" t="n">
-        <v>7092414</v>
+        <v>7092543</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718959</v>
+        <v>119718981</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752778</v>
+        <v>752869</v>
       </c>
       <c r="R67" t="n">
-        <v>7092543</v>
+        <v>7092414</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797610</v>
+        <v>119797594</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9814,25 +9814,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752864</v>
+        <v>752842</v>
       </c>
       <c r="R86" t="n">
-        <v>7092254</v>
+        <v>7092347</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9878,6 +9878,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9904,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797533</v>
+        <v>119797610</v>
       </c>
       <c r="B87" t="n">
-        <v>57463</v>
+        <v>91834</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9920,39 +9925,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752826</v>
+        <v>752864</v>
       </c>
       <c r="R87" t="n">
-        <v>7092234</v>
+        <v>7092254</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797594</v>
+        <v>119797561</v>
       </c>
       <c r="B88" t="n">
-        <v>89252</v>
+        <v>91844</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752842</v>
+        <v>752774</v>
       </c>
       <c r="R88" t="n">
-        <v>7092347</v>
+        <v>7092461</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp</t>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797561</v>
+        <v>119797533</v>
       </c>
       <c r="B89" t="n">
-        <v>91844</v>
+        <v>57463</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,38 +10130,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752774</v>
+        <v>752826</v>
       </c>
       <c r="R89" t="n">
-        <v>7092461</v>
+        <v>7092234</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10194,11 +10199,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,10 +10744,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119797553</v>
+        <v>119797532</v>
       </c>
       <c r="B95" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10760,34 +10760,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752830</v>
+        <v>752730</v>
       </c>
       <c r="R95" t="n">
-        <v>7092393</v>
+        <v>7092301</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10846,10 +10851,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797603</v>
+        <v>119797553</v>
       </c>
       <c r="B96" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10858,25 +10863,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10886,10 +10891,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752819</v>
+        <v>752830</v>
       </c>
       <c r="R96" t="n">
-        <v>7092254</v>
+        <v>7092393</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10948,10 +10953,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797532</v>
+        <v>119797603</v>
       </c>
       <c r="B97" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10960,43 +10965,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752730</v>
+        <v>752819</v>
       </c>
       <c r="R97" t="n">
-        <v>7092301</v>
+        <v>7092254</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119797565</v>
+        <v>119797607</v>
       </c>
       <c r="B99" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11169,38 +11169,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752765</v>
+        <v>752776</v>
       </c>
       <c r="R99" t="n">
-        <v>7092391</v>
+        <v>7092312</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11259,10 +11263,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797607</v>
+        <v>119797574</v>
       </c>
       <c r="B100" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11275,38 +11279,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752776</v>
+        <v>752787</v>
       </c>
       <c r="R100" t="n">
-        <v>7092312</v>
+        <v>7092311</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797574</v>
+        <v>119797579</v>
       </c>
       <c r="B101" t="n">
         <v>91832</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752787</v>
+        <v>752762</v>
       </c>
       <c r="R101" t="n">
-        <v>7092311</v>
+        <v>7092223</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119797579</v>
+        <v>119797608</v>
       </c>
       <c r="B102" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752762</v>
+        <v>752711</v>
       </c>
       <c r="R102" t="n">
-        <v>7092223</v>
+        <v>7092477</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797608</v>
+        <v>119797572</v>
       </c>
       <c r="B103" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11585,21 +11585,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752711</v>
+        <v>752714</v>
       </c>
       <c r="R103" t="n">
-        <v>7092477</v>
+        <v>7092390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797572</v>
+        <v>119797565</v>
       </c>
       <c r="B104" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11683,25 +11683,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752714</v>
+        <v>752765</v>
       </c>
       <c r="R104" t="n">
-        <v>7092390</v>
+        <v>7092391</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797588</v>
+        <v>119797560</v>
       </c>
       <c r="B116" t="n">
-        <v>89212</v>
+        <v>57326</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12931,30 +12931,31 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1593</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12963,10 +12964,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752818</v>
+        <v>752728</v>
       </c>
       <c r="R116" t="n">
-        <v>7092380</v>
+        <v>7092269</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13001,6 +13002,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13009,6 +13015,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13025,10 +13051,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119797560</v>
+        <v>119797588</v>
       </c>
       <c r="B117" t="n">
-        <v>57326</v>
+        <v>89212</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13037,31 +13063,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1593</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13070,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>752728</v>
+        <v>752818</v>
       </c>
       <c r="R117" t="n">
-        <v>7092269</v>
+        <v>7092380</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13108,11 +13133,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13121,26 +13141,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797552</v>
+        <v>119797530</v>
       </c>
       <c r="B132" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14612,25 +14612,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14640,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752818</v>
+        <v>752727</v>
       </c>
       <c r="R132" t="n">
-        <v>7092383</v>
+        <v>7092459</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14702,10 +14702,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797530</v>
+        <v>119797552</v>
       </c>
       <c r="B133" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14714,25 +14714,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752727</v>
+        <v>752818</v>
       </c>
       <c r="R133" t="n">
-        <v>7092459</v>
+        <v>7092383</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15110,10 +15110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797600</v>
+        <v>119797555</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15122,25 +15122,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752886</v>
+        <v>752885</v>
       </c>
       <c r="R137" t="n">
-        <v>7092295</v>
+        <v>7092323</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,7 +15212,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797555</v>
+        <v>119797558</v>
       </c>
       <c r="B138" t="n">
         <v>91884</v>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752885</v>
+        <v>752822</v>
       </c>
       <c r="R138" t="n">
-        <v>7092323</v>
+        <v>7092252</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797558</v>
+        <v>119797600</v>
       </c>
       <c r="B139" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15326,25 +15326,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752822</v>
+        <v>752886</v>
       </c>
       <c r="R139" t="n">
-        <v>7092252</v>
+        <v>7092295</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808308</v>
+        <v>119808299</v>
       </c>
       <c r="B144" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752743</v>
+        <v>752962</v>
       </c>
       <c r="R144" t="n">
         <v>7092343</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808312</v>
+        <v>119808308</v>
       </c>
       <c r="B145" t="n">
         <v>91884</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752773</v>
+        <v>752743</v>
       </c>
       <c r="R145" t="n">
-        <v>7092341</v>
+        <v>7092343</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808299</v>
+        <v>119808312</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752962</v>
+        <v>752773</v>
       </c>
       <c r="R146" t="n">
-        <v>7092343</v>
+        <v>7092341</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17422,10 +17422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808304</v>
+        <v>119808305</v>
       </c>
       <c r="B158" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17434,25 +17434,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752773</v>
+        <v>752740</v>
       </c>
       <c r="R158" t="n">
-        <v>7092434</v>
+        <v>7092467</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808305</v>
+        <v>119808304</v>
       </c>
       <c r="B159" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752740</v>
+        <v>752773</v>
       </c>
       <c r="R159" t="n">
-        <v>7092467</v>
+        <v>7092434</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17646,10 +17646,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808303</v>
+        <v>119808309</v>
       </c>
       <c r="B160" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17662,21 +17662,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752812</v>
+        <v>752727</v>
       </c>
       <c r="R160" t="n">
-        <v>7092433</v>
+        <v>7092321</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17758,10 +17758,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808309</v>
+        <v>119808303</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17774,21 +17774,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752727</v>
+        <v>752812</v>
       </c>
       <c r="R161" t="n">
-        <v>7092321</v>
+        <v>7092433</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19321,10 +19321,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119893598</v>
+        <v>119893208</v>
       </c>
       <c r="B176" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19333,25 +19333,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752767</v>
+        <v>752928</v>
       </c>
       <c r="R176" t="n">
-        <v>7092395</v>
+        <v>7092309</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19423,7 +19423,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119893208</v>
+        <v>119893329</v>
       </c>
       <c r="B177" t="n">
         <v>91884</v>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752928</v>
+        <v>752893</v>
       </c>
       <c r="R177" t="n">
-        <v>7092309</v>
+        <v>7092272</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19525,10 +19525,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119893329</v>
+        <v>119893598</v>
       </c>
       <c r="B178" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19537,25 +19537,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752893</v>
+        <v>752767</v>
       </c>
       <c r="R178" t="n">
-        <v>7092272</v>
+        <v>7092395</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119893537</v>
+        <v>119893473</v>
       </c>
       <c r="B184" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20153,21 +20153,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752759</v>
+        <v>752827</v>
       </c>
       <c r="R184" t="n">
-        <v>7092324</v>
+        <v>7092232</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20239,10 +20239,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119893473</v>
+        <v>119893537</v>
       </c>
       <c r="B185" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20255,21 +20255,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752827</v>
+        <v>752759</v>
       </c>
       <c r="R185" t="n">
-        <v>7092232</v>
+        <v>7092324</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20554,10 +20554,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934760</v>
+        <v>119934795</v>
       </c>
       <c r="B188" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20570,26 +20570,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20598,10 +20598,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752896</v>
+        <v>752996</v>
       </c>
       <c r="R188" t="n">
-        <v>7092456</v>
+        <v>7092398</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20634,6 +20634,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20660,10 +20665,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934795</v>
+        <v>119934760</v>
       </c>
       <c r="B189" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20676,26 +20681,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20704,10 +20709,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752996</v>
+        <v>752896</v>
       </c>
       <c r="R189" t="n">
-        <v>7092398</v>
+        <v>7092456</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20740,11 +20745,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934778</v>
+        <v>119934785</v>
       </c>
       <c r="B191" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20889,34 +20889,38 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752778</v>
+        <v>752721</v>
       </c>
       <c r="R191" t="n">
-        <v>7092476</v>
+        <v>7092493</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20975,7 +20979,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934785</v>
+        <v>119934784</v>
       </c>
       <c r="B192" t="n">
         <v>91832</v>
@@ -21010,7 +21014,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21019,10 +21023,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752721</v>
+        <v>752891</v>
       </c>
       <c r="R192" t="n">
-        <v>7092493</v>
+        <v>7092445</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21081,10 +21085,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934753</v>
+        <v>119934778</v>
       </c>
       <c r="B193" t="n">
-        <v>89275</v>
+        <v>91856</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21093,25 +21097,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21121,10 +21125,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752888</v>
+        <v>752778</v>
       </c>
       <c r="R193" t="n">
-        <v>7092677</v>
+        <v>7092476</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21285,10 +21289,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934784</v>
+        <v>119934753</v>
       </c>
       <c r="B195" t="n">
-        <v>91832</v>
+        <v>89275</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21297,42 +21301,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752891</v>
+        <v>752888</v>
       </c>
       <c r="R195" t="n">
-        <v>7092445</v>
+        <v>7092677</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21807,10 +21807,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934773</v>
+        <v>119934748</v>
       </c>
       <c r="B200" t="n">
-        <v>91844</v>
+        <v>89633</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21819,42 +21819,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752853</v>
+        <v>752762</v>
       </c>
       <c r="R200" t="n">
-        <v>7092405</v>
+        <v>7092586</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21891,7 +21887,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Undersida knäckt talltopp i mossa</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21902,6 +21898,21 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21918,10 +21929,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934764</v>
+        <v>119934773</v>
       </c>
       <c r="B201" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21930,30 +21941,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21962,10 +21973,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752759</v>
+        <v>752853</v>
       </c>
       <c r="R201" t="n">
-        <v>7092478</v>
+        <v>7092405</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21998,6 +22009,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22024,10 +22040,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934748</v>
+        <v>119934764</v>
       </c>
       <c r="B202" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22040,34 +22056,38 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752762</v>
+        <v>752759</v>
       </c>
       <c r="R202" t="n">
-        <v>7092586</v>
+        <v>7092478</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22102,11 +22122,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -22115,21 +22130,6 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -22563,10 +22563,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934789</v>
+        <v>119934777</v>
       </c>
       <c r="B207" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22579,38 +22579,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752803</v>
+        <v>752809</v>
       </c>
       <c r="R207" t="n">
-        <v>7092378</v>
+        <v>7092467</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22669,7 +22665,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934798</v>
+        <v>119934789</v>
       </c>
       <c r="B208" t="n">
         <v>91832</v>
@@ -22702,17 +22698,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752945</v>
+        <v>752803</v>
       </c>
       <c r="R208" t="n">
-        <v>7092339</v>
+        <v>7092378</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22771,7 +22771,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934797</v>
+        <v>119934798</v>
       </c>
       <c r="B209" t="n">
         <v>91832</v>
@@ -22811,10 +22811,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752806</v>
+        <v>752945</v>
       </c>
       <c r="R209" t="n">
-        <v>7092716</v>
+        <v>7092339</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22873,10 +22873,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934777</v>
+        <v>119934797</v>
       </c>
       <c r="B210" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22889,21 +22889,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752809</v>
+        <v>752806</v>
       </c>
       <c r="R210" t="n">
-        <v>7092467</v>
+        <v>7092716</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23298,10 +23298,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934806</v>
+        <v>119934823</v>
       </c>
       <c r="B214" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23310,25 +23310,25 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -23342,10 +23342,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752816</v>
+        <v>752959</v>
       </c>
       <c r="R214" t="n">
-        <v>7092714</v>
+        <v>7092467</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23404,10 +23404,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934823</v>
+        <v>119934806</v>
       </c>
       <c r="B215" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23416,25 +23416,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -23448,10 +23448,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752959</v>
+        <v>752816</v>
       </c>
       <c r="R215" t="n">
-        <v>7092467</v>
+        <v>7092714</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24878,10 +24878,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934792</v>
+        <v>119934809</v>
       </c>
       <c r="B229" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24890,30 +24890,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -24922,10 +24922,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752867</v>
+        <v>752817</v>
       </c>
       <c r="R229" t="n">
-        <v>7092495</v>
+        <v>7092378</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25090,10 +25090,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934809</v>
+        <v>119934792</v>
       </c>
       <c r="B231" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25102,30 +25102,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25134,10 +25134,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752817</v>
+        <v>752867</v>
       </c>
       <c r="R231" t="n">
-        <v>7092378</v>
+        <v>7092495</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25621,10 +25621,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934817</v>
+        <v>119934787</v>
       </c>
       <c r="B236" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25633,38 +25633,42 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752778</v>
+        <v>752738</v>
       </c>
       <c r="R236" t="n">
-        <v>7092478</v>
+        <v>7092548</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25697,6 +25701,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25723,10 +25732,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934821</v>
+        <v>119934817</v>
       </c>
       <c r="B237" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25735,42 +25744,38 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752994</v>
+        <v>752778</v>
       </c>
       <c r="R237" t="n">
-        <v>7092431</v>
+        <v>7092478</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25829,10 +25834,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934812</v>
+        <v>119934821</v>
       </c>
       <c r="B238" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25841,38 +25846,42 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752796</v>
+        <v>752994</v>
       </c>
       <c r="R238" t="n">
-        <v>7092694</v>
+        <v>7092431</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25931,10 +25940,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934787</v>
+        <v>119934812</v>
       </c>
       <c r="B239" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25943,42 +25952,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752738</v>
+        <v>752796</v>
       </c>
       <c r="R239" t="n">
-        <v>7092548</v>
+        <v>7092694</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26011,11 +26016,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD239" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718959</v>
+        <v>119718981</v>
       </c>
       <c r="B66" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752778</v>
+        <v>752869</v>
       </c>
       <c r="R66" t="n">
-        <v>7092543</v>
+        <v>7092414</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718981</v>
+        <v>119718959</v>
       </c>
       <c r="B67" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752869</v>
+        <v>752778</v>
       </c>
       <c r="R67" t="n">
-        <v>7092414</v>
+        <v>7092543</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9389,10 +9389,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119797543</v>
+        <v>119797575</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9405,21 +9405,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>752807</v>
+        <v>752836</v>
       </c>
       <c r="R82" t="n">
-        <v>7092368</v>
+        <v>7092356</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9465,11 +9465,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9496,10 +9491,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119797583</v>
+        <v>119797564</v>
       </c>
       <c r="B83" t="n">
-        <v>91863</v>
+        <v>91852</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9508,25 +9503,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9536,10 +9531,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>752719</v>
+        <v>752716</v>
       </c>
       <c r="R83" t="n">
-        <v>7092452</v>
+        <v>7092384</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9598,10 +9593,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119797575</v>
+        <v>119797543</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9614,21 +9609,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>752836</v>
+        <v>752807</v>
       </c>
       <c r="R84" t="n">
-        <v>7092356</v>
+        <v>7092368</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9674,6 +9669,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9700,10 +9700,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119797564</v>
+        <v>119797583</v>
       </c>
       <c r="B85" t="n">
-        <v>91852</v>
+        <v>91863</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9712,25 +9712,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>752716</v>
+        <v>752719</v>
       </c>
       <c r="R85" t="n">
-        <v>7092384</v>
+        <v>7092452</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797594</v>
+        <v>119797610</v>
       </c>
       <c r="B86" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9814,25 +9814,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752842</v>
+        <v>752864</v>
       </c>
       <c r="R86" t="n">
-        <v>7092347</v>
+        <v>7092254</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9878,11 +9878,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,10 +9904,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797610</v>
+        <v>119797533</v>
       </c>
       <c r="B87" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,34 +9920,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752864</v>
+        <v>752826</v>
       </c>
       <c r="R87" t="n">
-        <v>7092254</v>
+        <v>7092234</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797561</v>
+        <v>119797594</v>
       </c>
       <c r="B88" t="n">
-        <v>91844</v>
+        <v>89252</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752774</v>
+        <v>752842</v>
       </c>
       <c r="R88" t="n">
-        <v>7092461</v>
+        <v>7092347</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797533</v>
+        <v>119797561</v>
       </c>
       <c r="B89" t="n">
-        <v>57463</v>
+        <v>91844</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,43 +10130,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752826</v>
+        <v>752774</v>
       </c>
       <c r="R89" t="n">
-        <v>7092234</v>
+        <v>7092461</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10199,6 +10194,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,10 +10744,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119797532</v>
+        <v>119797553</v>
       </c>
       <c r="B95" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10760,39 +10760,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752730</v>
+        <v>752830</v>
       </c>
       <c r="R95" t="n">
-        <v>7092301</v>
+        <v>7092393</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10851,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797553</v>
+        <v>119797603</v>
       </c>
       <c r="B96" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10863,25 +10858,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10891,10 +10886,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752830</v>
+        <v>752819</v>
       </c>
       <c r="R96" t="n">
-        <v>7092393</v>
+        <v>7092254</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10953,10 +10948,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797603</v>
+        <v>119797532</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10965,38 +10960,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752819</v>
+        <v>752730</v>
       </c>
       <c r="R97" t="n">
-        <v>7092254</v>
+        <v>7092301</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119797607</v>
+        <v>119797565</v>
       </c>
       <c r="B99" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11169,42 +11169,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752776</v>
+        <v>752765</v>
       </c>
       <c r="R99" t="n">
-        <v>7092312</v>
+        <v>7092391</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11263,10 +11259,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797574</v>
+        <v>119797607</v>
       </c>
       <c r="B100" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11279,34 +11275,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752787</v>
+        <v>752776</v>
       </c>
       <c r="R100" t="n">
-        <v>7092311</v>
+        <v>7092312</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797579</v>
+        <v>119797574</v>
       </c>
       <c r="B101" t="n">
         <v>91832</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752762</v>
+        <v>752787</v>
       </c>
       <c r="R101" t="n">
-        <v>7092223</v>
+        <v>7092311</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119797608</v>
+        <v>119797579</v>
       </c>
       <c r="B102" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752711</v>
+        <v>752762</v>
       </c>
       <c r="R102" t="n">
-        <v>7092477</v>
+        <v>7092223</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797572</v>
+        <v>119797608</v>
       </c>
       <c r="B103" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11585,21 +11585,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752714</v>
+        <v>752711</v>
       </c>
       <c r="R103" t="n">
-        <v>7092390</v>
+        <v>7092477</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797565</v>
+        <v>119797572</v>
       </c>
       <c r="B104" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11683,25 +11683,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752765</v>
+        <v>752714</v>
       </c>
       <c r="R104" t="n">
-        <v>7092391</v>
+        <v>7092390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797560</v>
+        <v>119797588</v>
       </c>
       <c r="B116" t="n">
-        <v>57326</v>
+        <v>89212</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12931,31 +12931,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>1593</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12964,10 +12963,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752728</v>
+        <v>752818</v>
       </c>
       <c r="R116" t="n">
-        <v>7092269</v>
+        <v>7092380</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13002,11 +13001,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13015,26 +13009,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13051,10 +13025,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119797588</v>
+        <v>119797560</v>
       </c>
       <c r="B117" t="n">
-        <v>89212</v>
+        <v>57326</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13063,30 +13037,31 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1593</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13095,10 +13070,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>752818</v>
+        <v>752728</v>
       </c>
       <c r="R117" t="n">
-        <v>7092380</v>
+        <v>7092269</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13133,6 +13108,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13141,6 +13121,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797530</v>
+        <v>119797552</v>
       </c>
       <c r="B132" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14612,25 +14612,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14640,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752727</v>
+        <v>752818</v>
       </c>
       <c r="R132" t="n">
-        <v>7092459</v>
+        <v>7092383</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14702,10 +14702,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797552</v>
+        <v>119797530</v>
       </c>
       <c r="B133" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14714,25 +14714,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752818</v>
+        <v>752727</v>
       </c>
       <c r="R133" t="n">
-        <v>7092383</v>
+        <v>7092459</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15110,10 +15110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797555</v>
+        <v>119797600</v>
       </c>
       <c r="B137" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15122,25 +15122,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752885</v>
+        <v>752886</v>
       </c>
       <c r="R137" t="n">
-        <v>7092323</v>
+        <v>7092295</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,7 +15212,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797558</v>
+        <v>119797555</v>
       </c>
       <c r="B138" t="n">
         <v>91884</v>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752822</v>
+        <v>752885</v>
       </c>
       <c r="R138" t="n">
-        <v>7092252</v>
+        <v>7092323</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797600</v>
+        <v>119797558</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15326,25 +15326,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752886</v>
+        <v>752822</v>
       </c>
       <c r="R139" t="n">
-        <v>7092295</v>
+        <v>7092252</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808299</v>
+        <v>119808308</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752962</v>
+        <v>752743</v>
       </c>
       <c r="R144" t="n">
         <v>7092343</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808308</v>
+        <v>119808312</v>
       </c>
       <c r="B145" t="n">
         <v>91884</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752743</v>
+        <v>752773</v>
       </c>
       <c r="R145" t="n">
-        <v>7092343</v>
+        <v>7092341</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808312</v>
+        <v>119808299</v>
       </c>
       <c r="B146" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752773</v>
+        <v>752962</v>
       </c>
       <c r="R146" t="n">
-        <v>7092341</v>
+        <v>7092343</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17646,10 +17646,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808309</v>
+        <v>119808303</v>
       </c>
       <c r="B160" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17662,21 +17662,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752727</v>
+        <v>752812</v>
       </c>
       <c r="R160" t="n">
-        <v>7092321</v>
+        <v>7092433</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17758,10 +17758,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808303</v>
+        <v>119808309</v>
       </c>
       <c r="B161" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17774,21 +17774,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752812</v>
+        <v>752727</v>
       </c>
       <c r="R161" t="n">
-        <v>7092433</v>
+        <v>7092321</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -21807,10 +21807,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934748</v>
+        <v>119934773</v>
       </c>
       <c r="B200" t="n">
-        <v>89633</v>
+        <v>91844</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21819,38 +21819,42 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752762</v>
+        <v>752853</v>
       </c>
       <c r="R200" t="n">
-        <v>7092586</v>
+        <v>7092405</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21887,7 +21891,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Undersida knäckt talltopp i mossa</t>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21898,21 +21902,6 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21929,10 +21918,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934773</v>
+        <v>119934764</v>
       </c>
       <c r="B201" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21941,30 +21930,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21973,10 +21962,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752853</v>
+        <v>752759</v>
       </c>
       <c r="R201" t="n">
-        <v>7092405</v>
+        <v>7092478</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22009,11 +21998,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22040,10 +22024,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934764</v>
+        <v>119934748</v>
       </c>
       <c r="B202" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22056,38 +22040,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752759</v>
+        <v>752762</v>
       </c>
       <c r="R202" t="n">
-        <v>7092478</v>
+        <v>7092586</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22122,6 +22102,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -22130,6 +22115,21 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -22975,10 +22975,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934783</v>
+        <v>119934763</v>
       </c>
       <c r="B211" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22991,21 +22991,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -23019,10 +23019,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752771</v>
+        <v>752788</v>
       </c>
       <c r="R211" t="n">
-        <v>7092674</v>
+        <v>7092548</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23055,11 +23055,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23086,10 +23081,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934763</v>
+        <v>119934783</v>
       </c>
       <c r="B212" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23102,21 +23097,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -23130,10 +23125,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752788</v>
+        <v>752771</v>
       </c>
       <c r="R212" t="n">
-        <v>7092548</v>
+        <v>7092674</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23166,6 +23161,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -25307,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934790</v>
+        <v>119934811</v>
       </c>
       <c r="B233" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,32 +25319,28 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -25413,10 +25409,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934774</v>
+        <v>119934790</v>
       </c>
       <c r="B234" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25429,26 +25425,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -25457,10 +25453,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R234" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25519,10 +25515,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934811</v>
+        <v>119934774</v>
       </c>
       <c r="B235" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25531,38 +25527,42 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R235" t="n">
-        <v>7092405</v>
+        <v>7092444</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718981</v>
+        <v>119718959</v>
       </c>
       <c r="B66" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752869</v>
+        <v>752778</v>
       </c>
       <c r="R66" t="n">
-        <v>7092414</v>
+        <v>7092543</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718959</v>
+        <v>119718981</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752778</v>
+        <v>752869</v>
       </c>
       <c r="R67" t="n">
-        <v>7092543</v>
+        <v>7092414</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797610</v>
+        <v>119797594</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>89252</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9814,25 +9814,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752864</v>
+        <v>752842</v>
       </c>
       <c r="R86" t="n">
-        <v>7092254</v>
+        <v>7092347</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9878,6 +9878,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9904,10 +9909,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797533</v>
+        <v>119797610</v>
       </c>
       <c r="B87" t="n">
-        <v>57463</v>
+        <v>91834</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9920,39 +9925,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752826</v>
+        <v>752864</v>
       </c>
       <c r="R87" t="n">
-        <v>7092234</v>
+        <v>7092254</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797594</v>
+        <v>119797561</v>
       </c>
       <c r="B88" t="n">
-        <v>89252</v>
+        <v>91844</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752842</v>
+        <v>752774</v>
       </c>
       <c r="R88" t="n">
-        <v>7092347</v>
+        <v>7092461</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp</t>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797561</v>
+        <v>119797533</v>
       </c>
       <c r="B89" t="n">
-        <v>91844</v>
+        <v>57463</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,38 +10130,43 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4365</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752774</v>
+        <v>752826</v>
       </c>
       <c r="R89" t="n">
-        <v>7092461</v>
+        <v>7092234</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10194,11 +10199,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,10 +10744,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119797553</v>
+        <v>119797532</v>
       </c>
       <c r="B95" t="n">
-        <v>91884</v>
+        <v>57463</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10760,34 +10760,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752830</v>
+        <v>752730</v>
       </c>
       <c r="R95" t="n">
-        <v>7092393</v>
+        <v>7092301</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10846,10 +10851,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797603</v>
+        <v>119797553</v>
       </c>
       <c r="B96" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10858,25 +10863,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10886,10 +10891,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752819</v>
+        <v>752830</v>
       </c>
       <c r="R96" t="n">
-        <v>7092254</v>
+        <v>7092393</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10948,10 +10953,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797532</v>
+        <v>119797603</v>
       </c>
       <c r="B97" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10960,43 +10965,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752730</v>
+        <v>752819</v>
       </c>
       <c r="R97" t="n">
-        <v>7092301</v>
+        <v>7092254</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12919,10 +12919,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797588</v>
+        <v>119797560</v>
       </c>
       <c r="B116" t="n">
-        <v>89212</v>
+        <v>57326</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12931,30 +12931,31 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1593</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12963,10 +12964,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752818</v>
+        <v>752728</v>
       </c>
       <c r="R116" t="n">
-        <v>7092380</v>
+        <v>7092269</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13001,6 +13002,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13009,6 +13015,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -13025,10 +13051,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119797560</v>
+        <v>119797588</v>
       </c>
       <c r="B117" t="n">
-        <v>57326</v>
+        <v>89212</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13037,31 +13063,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>1593</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13070,10 +13095,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>752728</v>
+        <v>752818</v>
       </c>
       <c r="R117" t="n">
-        <v>7092269</v>
+        <v>7092380</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13108,11 +13133,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13121,26 +13141,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -15110,10 +15110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797600</v>
+        <v>119797555</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15122,25 +15122,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752886</v>
+        <v>752885</v>
       </c>
       <c r="R137" t="n">
-        <v>7092295</v>
+        <v>7092323</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,7 +15212,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797555</v>
+        <v>119797558</v>
       </c>
       <c r="B138" t="n">
         <v>91884</v>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752885</v>
+        <v>752822</v>
       </c>
       <c r="R138" t="n">
-        <v>7092323</v>
+        <v>7092252</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797558</v>
+        <v>119797600</v>
       </c>
       <c r="B139" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15326,25 +15326,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752822</v>
+        <v>752886</v>
       </c>
       <c r="R139" t="n">
-        <v>7092252</v>
+        <v>7092295</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808308</v>
+        <v>119808299</v>
       </c>
       <c r="B144" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752743</v>
+        <v>752962</v>
       </c>
       <c r="R144" t="n">
         <v>7092343</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808312</v>
+        <v>119808308</v>
       </c>
       <c r="B145" t="n">
         <v>91884</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752773</v>
+        <v>752743</v>
       </c>
       <c r="R145" t="n">
-        <v>7092341</v>
+        <v>7092343</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808299</v>
+        <v>119808312</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752962</v>
+        <v>752773</v>
       </c>
       <c r="R146" t="n">
-        <v>7092343</v>
+        <v>7092341</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17422,10 +17422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808305</v>
+        <v>119808304</v>
       </c>
       <c r="B158" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17434,25 +17434,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752740</v>
+        <v>752773</v>
       </c>
       <c r="R158" t="n">
-        <v>7092467</v>
+        <v>7092434</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808304</v>
+        <v>119808305</v>
       </c>
       <c r="B159" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752773</v>
+        <v>752740</v>
       </c>
       <c r="R159" t="n">
-        <v>7092434</v>
+        <v>7092467</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -20554,10 +20554,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934795</v>
+        <v>119934760</v>
       </c>
       <c r="B188" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20570,26 +20570,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20598,10 +20598,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752996</v>
+        <v>752896</v>
       </c>
       <c r="R188" t="n">
-        <v>7092398</v>
+        <v>7092456</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20634,11 +20634,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20665,10 +20660,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934760</v>
+        <v>119934795</v>
       </c>
       <c r="B189" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20681,26 +20676,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20709,10 +20704,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752896</v>
+        <v>752996</v>
       </c>
       <c r="R189" t="n">
-        <v>7092456</v>
+        <v>7092398</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20745,6 +20740,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21807,10 +21807,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934773</v>
+        <v>119934748</v>
       </c>
       <c r="B200" t="n">
-        <v>91844</v>
+        <v>89633</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21819,42 +21819,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752853</v>
+        <v>752762</v>
       </c>
       <c r="R200" t="n">
-        <v>7092405</v>
+        <v>7092586</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21891,7 +21887,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Undersida knäckt talltopp i mossa</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21902,6 +21898,21 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21918,10 +21929,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934764</v>
+        <v>119934773</v>
       </c>
       <c r="B201" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21930,30 +21941,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21962,10 +21973,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752759</v>
+        <v>752853</v>
       </c>
       <c r="R201" t="n">
-        <v>7092478</v>
+        <v>7092405</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21998,6 +22009,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22024,10 +22040,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934748</v>
+        <v>119934764</v>
       </c>
       <c r="B202" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22040,34 +22056,38 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752762</v>
+        <v>752759</v>
       </c>
       <c r="R202" t="n">
-        <v>7092586</v>
+        <v>7092478</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22102,11 +22122,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -22115,21 +22130,6 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ202" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -24032,10 +24032,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934772</v>
+        <v>119934765</v>
       </c>
       <c r="B221" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24044,38 +24044,42 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752757</v>
+        <v>752760</v>
       </c>
       <c r="R221" t="n">
-        <v>7092617</v>
+        <v>7092524</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24108,11 +24112,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24139,7 +24138,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934765</v>
+        <v>119934759</v>
       </c>
       <c r="B222" t="n">
         <v>91884</v>
@@ -24172,21 +24171,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752760</v>
+        <v>752845</v>
       </c>
       <c r="R222" t="n">
-        <v>7092524</v>
+        <v>7092505</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24219,6 +24214,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24245,10 +24245,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934759</v>
+        <v>119934775</v>
       </c>
       <c r="B223" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24261,34 +24261,38 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752845</v>
+        <v>752777</v>
       </c>
       <c r="R223" t="n">
-        <v>7092505</v>
+        <v>7092577</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24321,11 +24325,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24352,10 +24351,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934775</v>
+        <v>119934772</v>
       </c>
       <c r="B224" t="n">
-        <v>91856</v>
+        <v>91844</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24364,42 +24363,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2059</v>
+        <v>4365</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752777</v>
+        <v>752757</v>
       </c>
       <c r="R224" t="n">
-        <v>7092577</v>
+        <v>7092617</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24432,6 +24427,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24878,10 +24878,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934809</v>
+        <v>119934792</v>
       </c>
       <c r="B229" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24890,30 +24890,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -24922,10 +24922,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752817</v>
+        <v>752867</v>
       </c>
       <c r="R229" t="n">
-        <v>7092378</v>
+        <v>7092495</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25090,10 +25090,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934792</v>
+        <v>119934809</v>
       </c>
       <c r="B231" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25102,30 +25102,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25134,10 +25134,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752867</v>
+        <v>752817</v>
       </c>
       <c r="R231" t="n">
-        <v>7092495</v>
+        <v>7092378</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25307,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934811</v>
+        <v>119934790</v>
       </c>
       <c r="B233" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,28 +25319,32 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -25409,10 +25413,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934790</v>
+        <v>119934774</v>
       </c>
       <c r="B234" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25425,26 +25429,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -25453,10 +25457,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R234" t="n">
-        <v>7092405</v>
+        <v>7092444</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25515,10 +25519,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934774</v>
+        <v>119934811</v>
       </c>
       <c r="B235" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25527,42 +25531,38 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R235" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -8471,10 +8471,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119718973</v>
+        <v>119718969</v>
       </c>
       <c r="B73" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8487,21 +8487,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>752804</v>
+        <v>752839</v>
       </c>
       <c r="R73" t="n">
-        <v>7092441</v>
+        <v>7092424</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8573,10 +8573,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119718969</v>
+        <v>119718973</v>
       </c>
       <c r="B74" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8589,21 +8589,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>752839</v>
+        <v>752804</v>
       </c>
       <c r="R74" t="n">
-        <v>7092424</v>
+        <v>7092441</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9389,10 +9389,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119797575</v>
+        <v>119797543</v>
       </c>
       <c r="B82" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9405,21 +9405,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>752836</v>
+        <v>752807</v>
       </c>
       <c r="R82" t="n">
-        <v>7092356</v>
+        <v>7092368</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9465,6 +9465,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9491,10 +9496,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119797564</v>
+        <v>119797583</v>
       </c>
       <c r="B83" t="n">
-        <v>91852</v>
+        <v>91863</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9503,25 +9508,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9531,10 +9536,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>752716</v>
+        <v>752719</v>
       </c>
       <c r="R83" t="n">
-        <v>7092384</v>
+        <v>7092452</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9593,10 +9598,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119797543</v>
+        <v>119797575</v>
       </c>
       <c r="B84" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9609,21 +9614,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9633,10 +9638,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>752807</v>
+        <v>752836</v>
       </c>
       <c r="R84" t="n">
-        <v>7092368</v>
+        <v>7092356</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9669,11 +9674,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9700,10 +9700,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119797583</v>
+        <v>119797564</v>
       </c>
       <c r="B85" t="n">
-        <v>91863</v>
+        <v>91852</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9712,25 +9712,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>752719</v>
+        <v>752716</v>
       </c>
       <c r="R85" t="n">
-        <v>7092452</v>
+        <v>7092384</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797594</v>
+        <v>119797610</v>
       </c>
       <c r="B86" t="n">
-        <v>89252</v>
+        <v>91834</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9814,25 +9814,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9842,10 +9842,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752842</v>
+        <v>752864</v>
       </c>
       <c r="R86" t="n">
-        <v>7092347</v>
+        <v>7092254</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9878,11 +9878,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9909,10 +9904,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797610</v>
+        <v>119797533</v>
       </c>
       <c r="B87" t="n">
-        <v>91834</v>
+        <v>57463</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9925,34 +9920,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752864</v>
+        <v>752826</v>
       </c>
       <c r="R87" t="n">
-        <v>7092254</v>
+        <v>7092234</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10011,10 +10011,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797561</v>
+        <v>119797594</v>
       </c>
       <c r="B88" t="n">
-        <v>91844</v>
+        <v>89252</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10027,21 +10027,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10051,10 +10051,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752774</v>
+        <v>752842</v>
       </c>
       <c r="R88" t="n">
-        <v>7092461</v>
+        <v>7092347</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10118,10 +10118,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797533</v>
+        <v>119797561</v>
       </c>
       <c r="B89" t="n">
-        <v>57463</v>
+        <v>91844</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10130,43 +10130,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>4365</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752826</v>
+        <v>752774</v>
       </c>
       <c r="R89" t="n">
-        <v>7092234</v>
+        <v>7092461</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10199,6 +10194,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10744,10 +10744,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119797532</v>
+        <v>119797553</v>
       </c>
       <c r="B95" t="n">
-        <v>57463</v>
+        <v>91884</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10760,39 +10760,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752730</v>
+        <v>752830</v>
       </c>
       <c r="R95" t="n">
-        <v>7092301</v>
+        <v>7092393</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10851,10 +10846,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797553</v>
+        <v>119797603</v>
       </c>
       <c r="B96" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10863,25 +10858,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10891,10 +10886,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752830</v>
+        <v>752819</v>
       </c>
       <c r="R96" t="n">
-        <v>7092393</v>
+        <v>7092254</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10953,10 +10948,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797603</v>
+        <v>119797532</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10965,38 +10960,43 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752819</v>
+        <v>752730</v>
       </c>
       <c r="R97" t="n">
-        <v>7092254</v>
+        <v>7092301</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119797565</v>
+        <v>119797607</v>
       </c>
       <c r="B99" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11169,38 +11169,42 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752765</v>
+        <v>752776</v>
       </c>
       <c r="R99" t="n">
-        <v>7092391</v>
+        <v>7092312</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11259,10 +11263,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797607</v>
+        <v>119797574</v>
       </c>
       <c r="B100" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11275,38 +11279,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752776</v>
+        <v>752787</v>
       </c>
       <c r="R100" t="n">
-        <v>7092312</v>
+        <v>7092311</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797574</v>
+        <v>119797579</v>
       </c>
       <c r="B101" t="n">
         <v>91832</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752787</v>
+        <v>752762</v>
       </c>
       <c r="R101" t="n">
-        <v>7092311</v>
+        <v>7092223</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119797579</v>
+        <v>119797608</v>
       </c>
       <c r="B102" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752762</v>
+        <v>752711</v>
       </c>
       <c r="R102" t="n">
-        <v>7092223</v>
+        <v>7092477</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797608</v>
+        <v>119797572</v>
       </c>
       <c r="B103" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11585,21 +11585,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752711</v>
+        <v>752714</v>
       </c>
       <c r="R103" t="n">
-        <v>7092477</v>
+        <v>7092390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797572</v>
+        <v>119797565</v>
       </c>
       <c r="B104" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11683,25 +11683,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752714</v>
+        <v>752765</v>
       </c>
       <c r="R104" t="n">
-        <v>7092390</v>
+        <v>7092391</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797552</v>
+        <v>119797530</v>
       </c>
       <c r="B132" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14612,25 +14612,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14640,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752818</v>
+        <v>752727</v>
       </c>
       <c r="R132" t="n">
-        <v>7092383</v>
+        <v>7092459</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14702,10 +14702,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797530</v>
+        <v>119797552</v>
       </c>
       <c r="B133" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14714,25 +14714,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752727</v>
+        <v>752818</v>
       </c>
       <c r="R133" t="n">
-        <v>7092459</v>
+        <v>7092383</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15110,10 +15110,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797555</v>
+        <v>119797600</v>
       </c>
       <c r="B137" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15122,25 +15122,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15150,10 +15150,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752885</v>
+        <v>752886</v>
       </c>
       <c r="R137" t="n">
-        <v>7092323</v>
+        <v>7092295</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15212,7 +15212,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797558</v>
+        <v>119797555</v>
       </c>
       <c r="B138" t="n">
         <v>91884</v>
@@ -15252,10 +15252,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752822</v>
+        <v>752885</v>
       </c>
       <c r="R138" t="n">
-        <v>7092252</v>
+        <v>7092323</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15314,10 +15314,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797600</v>
+        <v>119797558</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15326,25 +15326,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15354,10 +15354,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752886</v>
+        <v>752822</v>
       </c>
       <c r="R139" t="n">
-        <v>7092295</v>
+        <v>7092252</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808299</v>
+        <v>119808308</v>
       </c>
       <c r="B144" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752962</v>
+        <v>752743</v>
       </c>
       <c r="R144" t="n">
         <v>7092343</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808308</v>
+        <v>119808312</v>
       </c>
       <c r="B145" t="n">
         <v>91884</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752743</v>
+        <v>752773</v>
       </c>
       <c r="R145" t="n">
-        <v>7092343</v>
+        <v>7092341</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808312</v>
+        <v>119808299</v>
       </c>
       <c r="B146" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752773</v>
+        <v>752962</v>
       </c>
       <c r="R146" t="n">
-        <v>7092341</v>
+        <v>7092343</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17646,10 +17646,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808303</v>
+        <v>119808309</v>
       </c>
       <c r="B160" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17662,21 +17662,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752812</v>
+        <v>752727</v>
       </c>
       <c r="R160" t="n">
-        <v>7092433</v>
+        <v>7092321</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17758,10 +17758,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808309</v>
+        <v>119808303</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17774,21 +17774,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752727</v>
+        <v>752812</v>
       </c>
       <c r="R161" t="n">
-        <v>7092321</v>
+        <v>7092433</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18199,10 +18199,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119893016</v>
+        <v>119893225</v>
       </c>
       <c r="B165" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18215,21 +18215,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18239,10 +18239,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752901</v>
+        <v>752927</v>
       </c>
       <c r="R165" t="n">
-        <v>7092374</v>
+        <v>7092298</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18301,7 +18301,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119893225</v>
+        <v>119893626</v>
       </c>
       <c r="B166" t="n">
         <v>91884</v>
@@ -18341,10 +18341,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752927</v>
+        <v>752767</v>
       </c>
       <c r="R166" t="n">
-        <v>7092298</v>
+        <v>7092396</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18403,10 +18403,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119893626</v>
+        <v>119893016</v>
       </c>
       <c r="B167" t="n">
-        <v>91884</v>
+        <v>91826</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18419,21 +18419,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18443,10 +18443,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752767</v>
+        <v>752901</v>
       </c>
       <c r="R167" t="n">
-        <v>7092396</v>
+        <v>7092374</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -20554,10 +20554,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934760</v>
+        <v>119934795</v>
       </c>
       <c r="B188" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20570,26 +20570,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20598,10 +20598,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752896</v>
+        <v>752996</v>
       </c>
       <c r="R188" t="n">
-        <v>7092456</v>
+        <v>7092398</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20634,6 +20634,11 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20660,10 +20665,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934795</v>
+        <v>119934760</v>
       </c>
       <c r="B189" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20676,26 +20681,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20704,10 +20709,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752996</v>
+        <v>752896</v>
       </c>
       <c r="R189" t="n">
-        <v>7092398</v>
+        <v>7092456</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20740,11 +20745,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20873,10 +20873,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934785</v>
+        <v>119934778</v>
       </c>
       <c r="B191" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20889,38 +20889,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752721</v>
+        <v>752778</v>
       </c>
       <c r="R191" t="n">
-        <v>7092493</v>
+        <v>7092476</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20979,7 +20975,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934784</v>
+        <v>119934785</v>
       </c>
       <c r="B192" t="n">
         <v>91832</v>
@@ -21014,7 +21010,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21023,10 +21019,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752891</v>
+        <v>752721</v>
       </c>
       <c r="R192" t="n">
-        <v>7092445</v>
+        <v>7092493</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21085,10 +21081,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934778</v>
+        <v>119934753</v>
       </c>
       <c r="B193" t="n">
-        <v>91856</v>
+        <v>89275</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21097,25 +21093,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21125,10 +21121,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752778</v>
+        <v>752888</v>
       </c>
       <c r="R193" t="n">
-        <v>7092476</v>
+        <v>7092677</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21289,10 +21285,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934753</v>
+        <v>119934784</v>
       </c>
       <c r="B195" t="n">
-        <v>89275</v>
+        <v>91832</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21301,38 +21297,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752888</v>
+        <v>752891</v>
       </c>
       <c r="R195" t="n">
-        <v>7092677</v>
+        <v>7092445</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -24032,10 +24032,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934765</v>
+        <v>119934772</v>
       </c>
       <c r="B221" t="n">
-        <v>91884</v>
+        <v>91844</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24044,42 +24044,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752760</v>
+        <v>752757</v>
       </c>
       <c r="R221" t="n">
-        <v>7092524</v>
+        <v>7092617</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24112,6 +24108,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24138,7 +24139,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934759</v>
+        <v>119934765</v>
       </c>
       <c r="B222" t="n">
         <v>91884</v>
@@ -24171,17 +24172,21 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752845</v>
+        <v>752760</v>
       </c>
       <c r="R222" t="n">
-        <v>7092505</v>
+        <v>7092524</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24214,11 +24219,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24245,10 +24245,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934775</v>
+        <v>119934759</v>
       </c>
       <c r="B223" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24261,38 +24261,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752777</v>
+        <v>752845</v>
       </c>
       <c r="R223" t="n">
-        <v>7092577</v>
+        <v>7092505</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24325,6 +24321,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24351,10 +24352,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934772</v>
+        <v>119934775</v>
       </c>
       <c r="B224" t="n">
-        <v>91844</v>
+        <v>91856</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24363,38 +24364,42 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752757</v>
+        <v>752777</v>
       </c>
       <c r="R224" t="n">
-        <v>7092617</v>
+        <v>7092577</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24427,11 +24432,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25307,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934790</v>
+        <v>119934811</v>
       </c>
       <c r="B233" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,32 +25319,28 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -25413,10 +25409,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934774</v>
+        <v>119934790</v>
       </c>
       <c r="B234" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25429,26 +25425,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -25457,10 +25453,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R234" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25519,10 +25515,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934811</v>
+        <v>119934774</v>
       </c>
       <c r="B235" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25531,38 +25527,42 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R235" t="n">
-        <v>7092405</v>
+        <v>7092444</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718959</v>
+        <v>119718981</v>
       </c>
       <c r="B66" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752778</v>
+        <v>752869</v>
       </c>
       <c r="R66" t="n">
-        <v>7092543</v>
+        <v>7092414</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718981</v>
+        <v>119718959</v>
       </c>
       <c r="B67" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752869</v>
+        <v>752778</v>
       </c>
       <c r="R67" t="n">
-        <v>7092414</v>
+        <v>7092543</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9389,10 +9389,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119797543</v>
+        <v>119797575</v>
       </c>
       <c r="B82" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9405,21 +9405,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9429,10 +9429,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>752807</v>
+        <v>752836</v>
       </c>
       <c r="R82" t="n">
-        <v>7092368</v>
+        <v>7092356</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9465,11 +9465,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9496,10 +9491,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119797583</v>
+        <v>119797564</v>
       </c>
       <c r="B83" t="n">
-        <v>91863</v>
+        <v>91852</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9508,25 +9503,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9536,10 +9531,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>752719</v>
+        <v>752716</v>
       </c>
       <c r="R83" t="n">
-        <v>7092452</v>
+        <v>7092384</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9598,10 +9593,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119797575</v>
+        <v>119797543</v>
       </c>
       <c r="B84" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9614,21 +9609,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9638,10 +9633,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>752836</v>
+        <v>752807</v>
       </c>
       <c r="R84" t="n">
-        <v>7092356</v>
+        <v>7092368</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9674,6 +9669,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9700,10 +9700,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119797564</v>
+        <v>119797583</v>
       </c>
       <c r="B85" t="n">
-        <v>91852</v>
+        <v>91863</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9712,25 +9712,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>752716</v>
+        <v>752719</v>
       </c>
       <c r="R85" t="n">
-        <v>7092384</v>
+        <v>7092452</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797530</v>
+        <v>119797552</v>
       </c>
       <c r="B132" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14612,25 +14612,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14640,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752727</v>
+        <v>752818</v>
       </c>
       <c r="R132" t="n">
-        <v>7092459</v>
+        <v>7092383</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14702,10 +14702,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797552</v>
+        <v>119797530</v>
       </c>
       <c r="B133" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14714,25 +14714,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752818</v>
+        <v>752727</v>
       </c>
       <c r="R133" t="n">
-        <v>7092383</v>
+        <v>7092459</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -17086,7 +17086,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808298</v>
+        <v>119808301</v>
       </c>
       <c r="B155" t="n">
         <v>91884</v>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752922</v>
+        <v>752896</v>
       </c>
       <c r="R155" t="n">
-        <v>7092310</v>
+        <v>7092397</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17198,7 +17198,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119808301</v>
+        <v>119808298</v>
       </c>
       <c r="B156" t="n">
         <v>91884</v>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752896</v>
+        <v>752922</v>
       </c>
       <c r="R156" t="n">
-        <v>7092397</v>
+        <v>7092310</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17422,10 +17422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808304</v>
+        <v>119808305</v>
       </c>
       <c r="B158" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17434,25 +17434,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752773</v>
+        <v>752740</v>
       </c>
       <c r="R158" t="n">
-        <v>7092434</v>
+        <v>7092467</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808305</v>
+        <v>119808304</v>
       </c>
       <c r="B159" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752740</v>
+        <v>752773</v>
       </c>
       <c r="R159" t="n">
-        <v>7092467</v>
+        <v>7092434</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -22975,10 +22975,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934763</v>
+        <v>119934783</v>
       </c>
       <c r="B211" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22991,21 +22991,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -23019,10 +23019,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752788</v>
+        <v>752771</v>
       </c>
       <c r="R211" t="n">
-        <v>7092548</v>
+        <v>7092674</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23055,6 +23055,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23081,10 +23086,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934783</v>
+        <v>119934763</v>
       </c>
       <c r="B212" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23097,21 +23102,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -23125,10 +23130,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752771</v>
+        <v>752788</v>
       </c>
       <c r="R212" t="n">
-        <v>7092674</v>
+        <v>7092548</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23161,11 +23166,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24458,10 +24458,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934767</v>
+        <v>119934776</v>
       </c>
       <c r="B225" t="n">
-        <v>91884</v>
+        <v>91856</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24474,34 +24474,38 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752720</v>
+        <v>752759</v>
       </c>
       <c r="R225" t="n">
-        <v>7092493</v>
+        <v>7092525</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24560,10 +24564,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934776</v>
+        <v>119934791</v>
       </c>
       <c r="B226" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24576,21 +24580,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -24604,10 +24608,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752759</v>
+        <v>752777</v>
       </c>
       <c r="R226" t="n">
-        <v>7092525</v>
+        <v>7092488</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24666,7 +24670,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934791</v>
+        <v>119934782</v>
       </c>
       <c r="B227" t="n">
         <v>91832</v>
@@ -24701,7 +24705,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24710,10 +24714,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752777</v>
+        <v>752743</v>
       </c>
       <c r="R227" t="n">
-        <v>7092488</v>
+        <v>7092544</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24772,10 +24776,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934782</v>
+        <v>119934767</v>
       </c>
       <c r="B228" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24788,38 +24792,34 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752743</v>
+        <v>752720</v>
       </c>
       <c r="R228" t="n">
-        <v>7092544</v>
+        <v>7092493</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25307,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934811</v>
+        <v>119934790</v>
       </c>
       <c r="B233" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,28 +25319,32 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -25409,10 +25413,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934790</v>
+        <v>119934774</v>
       </c>
       <c r="B234" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25425,26 +25429,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -25453,10 +25457,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R234" t="n">
-        <v>7092405</v>
+        <v>7092444</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25515,10 +25519,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934774</v>
+        <v>119934811</v>
       </c>
       <c r="B235" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25527,42 +25531,38 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R235" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -7748,10 +7748,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119718981</v>
+        <v>119718959</v>
       </c>
       <c r="B66" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7760,25 +7760,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7788,10 +7788,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>752869</v>
+        <v>752778</v>
       </c>
       <c r="R66" t="n">
-        <v>7092414</v>
+        <v>7092543</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7850,10 +7850,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119718959</v>
+        <v>119718981</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7862,25 +7862,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7890,10 +7890,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>752778</v>
+        <v>752869</v>
       </c>
       <c r="R67" t="n">
-        <v>7092543</v>
+        <v>7092414</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -11157,10 +11157,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119797607</v>
+        <v>119797565</v>
       </c>
       <c r="B99" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11169,42 +11169,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752776</v>
+        <v>752765</v>
       </c>
       <c r="R99" t="n">
-        <v>7092312</v>
+        <v>7092391</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11263,10 +11259,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797574</v>
+        <v>119797607</v>
       </c>
       <c r="B100" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11279,34 +11275,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752787</v>
+        <v>752776</v>
       </c>
       <c r="R100" t="n">
-        <v>7092311</v>
+        <v>7092312</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11365,7 +11365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797579</v>
+        <v>119797574</v>
       </c>
       <c r="B101" t="n">
         <v>91832</v>
@@ -11405,10 +11405,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752762</v>
+        <v>752787</v>
       </c>
       <c r="R101" t="n">
-        <v>7092223</v>
+        <v>7092311</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11467,10 +11467,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119797608</v>
+        <v>119797579</v>
       </c>
       <c r="B102" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11483,21 +11483,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11507,10 +11507,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752711</v>
+        <v>752762</v>
       </c>
       <c r="R102" t="n">
-        <v>7092477</v>
+        <v>7092223</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11569,10 +11569,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797572</v>
+        <v>119797608</v>
       </c>
       <c r="B103" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11585,21 +11585,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752714</v>
+        <v>752711</v>
       </c>
       <c r="R103" t="n">
-        <v>7092390</v>
+        <v>7092477</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11671,10 +11671,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797565</v>
+        <v>119797572</v>
       </c>
       <c r="B104" t="n">
-        <v>91852</v>
+        <v>91832</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11683,25 +11683,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11711,10 +11711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752765</v>
+        <v>752714</v>
       </c>
       <c r="R104" t="n">
-        <v>7092391</v>
+        <v>7092390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119797571</v>
+        <v>119797560</v>
       </c>
       <c r="B113" t="n">
-        <v>91832</v>
+        <v>57326</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12624,34 +12624,39 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>752807</v>
+        <v>752728</v>
       </c>
       <c r="R113" t="n">
-        <v>7092369</v>
+        <v>7092269</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12688,7 +12693,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>I grop</t>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12699,6 +12704,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
@@ -12715,7 +12740,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119797573</v>
+        <v>119797571</v>
       </c>
       <c r="B114" t="n">
         <v>91832</v>
@@ -12755,10 +12780,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>752711</v>
+        <v>752807</v>
       </c>
       <c r="R114" t="n">
-        <v>7092477</v>
+        <v>7092369</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12791,6 +12816,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12817,10 +12847,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119797554</v>
+        <v>119797573</v>
       </c>
       <c r="B115" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12833,21 +12863,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12857,10 +12887,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>752858</v>
+        <v>752711</v>
       </c>
       <c r="R115" t="n">
-        <v>7092376</v>
+        <v>7092477</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12919,10 +12949,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797560</v>
+        <v>119797554</v>
       </c>
       <c r="B116" t="n">
-        <v>57326</v>
+        <v>91884</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12935,39 +12965,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752728</v>
+        <v>752858</v>
       </c>
       <c r="R116" t="n">
-        <v>7092269</v>
+        <v>7092376</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13002,11 +13027,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13015,26 +13035,6 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL116" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
@@ -14600,10 +14600,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797552</v>
+        <v>119797530</v>
       </c>
       <c r="B132" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14612,25 +14612,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14640,10 +14640,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752818</v>
+        <v>752727</v>
       </c>
       <c r="R132" t="n">
-        <v>7092383</v>
+        <v>7092459</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14702,10 +14702,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797530</v>
+        <v>119797552</v>
       </c>
       <c r="B133" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14714,25 +14714,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14742,10 +14742,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752727</v>
+        <v>752818</v>
       </c>
       <c r="R133" t="n">
-        <v>7092459</v>
+        <v>7092383</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808308</v>
+        <v>119808299</v>
       </c>
       <c r="B144" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,7 +15894,7 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752743</v>
+        <v>752962</v>
       </c>
       <c r="R144" t="n">
         <v>7092343</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808312</v>
+        <v>119808308</v>
       </c>
       <c r="B145" t="n">
         <v>91884</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752773</v>
+        <v>752743</v>
       </c>
       <c r="R145" t="n">
-        <v>7092341</v>
+        <v>7092343</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808299</v>
+        <v>119808312</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752962</v>
+        <v>752773</v>
       </c>
       <c r="R146" t="n">
-        <v>7092343</v>
+        <v>7092341</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17086,7 +17086,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808301</v>
+        <v>119808298</v>
       </c>
       <c r="B155" t="n">
         <v>91884</v>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752896</v>
+        <v>752922</v>
       </c>
       <c r="R155" t="n">
-        <v>7092397</v>
+        <v>7092310</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17198,7 +17198,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119808298</v>
+        <v>119808301</v>
       </c>
       <c r="B156" t="n">
         <v>91884</v>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752922</v>
+        <v>752896</v>
       </c>
       <c r="R156" t="n">
-        <v>7092310</v>
+        <v>7092397</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17422,10 +17422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808305</v>
+        <v>119808304</v>
       </c>
       <c r="B158" t="n">
-        <v>91884</v>
+        <v>89275</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17434,25 +17434,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752740</v>
+        <v>752773</v>
       </c>
       <c r="R158" t="n">
-        <v>7092467</v>
+        <v>7092434</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808304</v>
+        <v>119808305</v>
       </c>
       <c r="B159" t="n">
-        <v>89275</v>
+        <v>91884</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17546,25 +17546,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752773</v>
+        <v>752740</v>
       </c>
       <c r="R159" t="n">
-        <v>7092434</v>
+        <v>7092467</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -21807,10 +21807,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934748</v>
+        <v>119934773</v>
       </c>
       <c r="B200" t="n">
-        <v>89633</v>
+        <v>91844</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21819,38 +21819,42 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752762</v>
+        <v>752853</v>
       </c>
       <c r="R200" t="n">
-        <v>7092586</v>
+        <v>7092405</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21887,7 +21891,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Undersida knäckt talltopp i mossa</t>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21898,21 +21902,6 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21929,10 +21918,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934773</v>
+        <v>119934764</v>
       </c>
       <c r="B201" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21941,30 +21930,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21973,10 +21962,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752853</v>
+        <v>752759</v>
       </c>
       <c r="R201" t="n">
-        <v>7092405</v>
+        <v>7092478</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22009,11 +21998,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22040,10 +22024,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934764</v>
+        <v>119934748</v>
       </c>
       <c r="B202" t="n">
-        <v>91884</v>
+        <v>89633</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22056,38 +22040,34 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752759</v>
+        <v>752762</v>
       </c>
       <c r="R202" t="n">
-        <v>7092478</v>
+        <v>7092586</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22122,6 +22102,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
@@ -22130,6 +22115,21 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
@@ -22563,10 +22563,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934777</v>
+        <v>119934789</v>
       </c>
       <c r="B207" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22579,34 +22579,38 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752809</v>
+        <v>752803</v>
       </c>
       <c r="R207" t="n">
-        <v>7092467</v>
+        <v>7092378</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22665,7 +22669,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934789</v>
+        <v>119934798</v>
       </c>
       <c r="B208" t="n">
         <v>91832</v>
@@ -22698,21 +22702,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752803</v>
+        <v>752945</v>
       </c>
       <c r="R208" t="n">
-        <v>7092378</v>
+        <v>7092339</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22771,7 +22771,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934798</v>
+        <v>119934797</v>
       </c>
       <c r="B209" t="n">
         <v>91832</v>
@@ -22811,10 +22811,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752945</v>
+        <v>752806</v>
       </c>
       <c r="R209" t="n">
-        <v>7092339</v>
+        <v>7092716</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22873,10 +22873,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934797</v>
+        <v>119934777</v>
       </c>
       <c r="B210" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22889,21 +22889,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22913,10 +22913,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752806</v>
+        <v>752809</v>
       </c>
       <c r="R210" t="n">
-        <v>7092716</v>
+        <v>7092467</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22975,10 +22975,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934783</v>
+        <v>119934763</v>
       </c>
       <c r="B211" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22991,21 +22991,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -23019,10 +23019,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752771</v>
+        <v>752788</v>
       </c>
       <c r="R211" t="n">
-        <v>7092674</v>
+        <v>7092548</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23055,11 +23055,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23086,10 +23081,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934763</v>
+        <v>119934783</v>
       </c>
       <c r="B212" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23102,21 +23097,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -23130,10 +23125,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752788</v>
+        <v>752771</v>
       </c>
       <c r="R212" t="n">
-        <v>7092548</v>
+        <v>7092674</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23166,6 +23161,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24458,10 +24458,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934776</v>
+        <v>119934767</v>
       </c>
       <c r="B225" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24474,38 +24474,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752759</v>
+        <v>752720</v>
       </c>
       <c r="R225" t="n">
-        <v>7092525</v>
+        <v>7092493</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24564,10 +24560,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934791</v>
+        <v>119934776</v>
       </c>
       <c r="B226" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24580,21 +24576,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -24608,10 +24604,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752777</v>
+        <v>752759</v>
       </c>
       <c r="R226" t="n">
-        <v>7092488</v>
+        <v>7092525</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24670,7 +24666,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934782</v>
+        <v>119934791</v>
       </c>
       <c r="B227" t="n">
         <v>91832</v>
@@ -24705,7 +24701,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24714,10 +24710,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752743</v>
+        <v>752777</v>
       </c>
       <c r="R227" t="n">
-        <v>7092544</v>
+        <v>7092488</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24776,10 +24772,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934767</v>
+        <v>119934782</v>
       </c>
       <c r="B228" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24792,34 +24788,38 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752720</v>
+        <v>752743</v>
       </c>
       <c r="R228" t="n">
-        <v>7092493</v>
+        <v>7092544</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25307,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934790</v>
+        <v>119934811</v>
       </c>
       <c r="B233" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,32 +25319,28 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -25413,10 +25409,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934774</v>
+        <v>119934790</v>
       </c>
       <c r="B234" t="n">
-        <v>91856</v>
+        <v>91832</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25429,26 +25425,26 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
@@ -25457,10 +25453,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R234" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25519,10 +25515,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934811</v>
+        <v>119934774</v>
       </c>
       <c r="B235" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25531,38 +25527,42 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R235" t="n">
-        <v>7092405</v>
+        <v>7092444</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -16190,10 +16190,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119808297</v>
+        <v>119808303</v>
       </c>
       <c r="B147" t="n">
-        <v>91902</v>
+        <v>91481</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16206,21 +16206,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752905</v>
+        <v>752812</v>
       </c>
       <c r="R147" t="n">
-        <v>7092298</v>
+        <v>7092433</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16302,7 +16302,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119808305</v>
+        <v>119808297</v>
       </c>
       <c r="B148" t="n">
         <v>91902</v>
@@ -16342,10 +16342,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752740</v>
+        <v>752905</v>
       </c>
       <c r="R148" t="n">
-        <v>7092467</v>
+        <v>7092298</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16414,7 +16414,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119808308</v>
+        <v>119808305</v>
       </c>
       <c r="B149" t="n">
         <v>91902</v>
@@ -16454,10 +16454,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752743</v>
+        <v>752740</v>
       </c>
       <c r="R149" t="n">
-        <v>7092343</v>
+        <v>7092467</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16526,10 +16526,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119808303</v>
+        <v>119808308</v>
       </c>
       <c r="B150" t="n">
-        <v>91481</v>
+        <v>91902</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16542,21 +16542,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752812</v>
+        <v>752743</v>
       </c>
       <c r="R150" t="n">
-        <v>7092433</v>
+        <v>7092343</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16638,10 +16638,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119808295</v>
+        <v>119808304</v>
       </c>
       <c r="B151" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16650,25 +16650,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752872</v>
+        <v>752773</v>
       </c>
       <c r="R151" t="n">
-        <v>7092301</v>
+        <v>7092434</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16750,10 +16750,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119808306</v>
+        <v>119808300</v>
       </c>
       <c r="B152" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16766,21 +16766,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16790,10 +16790,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752764</v>
+        <v>752943</v>
       </c>
       <c r="R152" t="n">
-        <v>7092409</v>
+        <v>7092394</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16862,10 +16862,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808304</v>
+        <v>119808295</v>
       </c>
       <c r="B153" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16874,25 +16874,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752773</v>
+        <v>752872</v>
       </c>
       <c r="R153" t="n">
-        <v>7092434</v>
+        <v>7092301</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808300</v>
+        <v>119808306</v>
       </c>
       <c r="B154" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16990,21 +16990,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752943</v>
+        <v>752764</v>
       </c>
       <c r="R154" t="n">
-        <v>7092394</v>
+        <v>7092409</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -23156,10 +23156,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934773</v>
+        <v>119934766</v>
       </c>
       <c r="B213" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23168,30 +23168,30 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23200,10 +23200,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752853</v>
+        <v>752751</v>
       </c>
       <c r="R213" t="n">
-        <v>7092405</v>
+        <v>7092507</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23236,11 +23236,6 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23267,10 +23262,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934766</v>
+        <v>119934773</v>
       </c>
       <c r="B214" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23279,30 +23274,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23311,10 +23306,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752751</v>
+        <v>752853</v>
       </c>
       <c r="R214" t="n">
-        <v>7092507</v>
+        <v>7092405</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23347,6 +23342,11 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD214" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY241"/>
+  <dimension ref="A1:AY242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9389,10 +9389,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119797578</v>
+        <v>119797581</v>
       </c>
       <c r="B82" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9405,34 +9405,38 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>752895</v>
+        <v>752686</v>
       </c>
       <c r="R82" t="n">
-        <v>7092346</v>
+        <v>7092272</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9465,6 +9469,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Nära stigen</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9491,10 +9500,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119797604</v>
+        <v>119797538</v>
       </c>
       <c r="B83" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9503,25 +9512,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9531,10 +9540,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>752825</v>
+        <v>752734</v>
       </c>
       <c r="R83" t="n">
-        <v>7092235</v>
+        <v>7092340</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9593,10 +9602,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119797583</v>
+        <v>119797550</v>
       </c>
       <c r="B84" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9609,21 +9618,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9633,10 +9642,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>752719</v>
+        <v>752815</v>
       </c>
       <c r="R84" t="n">
-        <v>7092452</v>
+        <v>7092360</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9695,7 +9704,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119797555</v>
+        <v>119797558</v>
       </c>
       <c r="B85" t="n">
         <v>91902</v>
@@ -9735,10 +9744,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>752885</v>
+        <v>752822</v>
       </c>
       <c r="R85" t="n">
-        <v>7092323</v>
+        <v>7092252</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9797,7 +9806,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119797542</v>
+        <v>119797556</v>
       </c>
       <c r="B86" t="n">
         <v>91902</v>
@@ -9837,10 +9846,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>752885</v>
+        <v>752877</v>
       </c>
       <c r="R86" t="n">
-        <v>7092352</v>
+        <v>7092306</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9873,11 +9882,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9904,10 +9908,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119797611</v>
+        <v>119797597</v>
       </c>
       <c r="B87" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9916,25 +9920,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9944,10 +9948,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>752818</v>
+        <v>752839</v>
       </c>
       <c r="R87" t="n">
-        <v>7092235</v>
+        <v>7092201</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10006,10 +10010,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119797602</v>
+        <v>119797565</v>
       </c>
       <c r="B88" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10022,21 +10026,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10046,10 +10050,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>752769</v>
+        <v>752765</v>
       </c>
       <c r="R88" t="n">
-        <v>7092291</v>
+        <v>7092391</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10108,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119797609</v>
+        <v>119797552</v>
       </c>
       <c r="B89" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10124,21 +10128,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10148,10 +10152,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>752855</v>
+        <v>752818</v>
       </c>
       <c r="R89" t="n">
-        <v>7092378</v>
+        <v>7092383</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10210,7 +10214,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119797600</v>
+        <v>119797598</v>
       </c>
       <c r="B90" t="n">
         <v>91858</v>
@@ -10250,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>752886</v>
+        <v>752740</v>
       </c>
       <c r="R90" t="n">
-        <v>7092295</v>
+        <v>7092313</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10312,7 +10316,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119797598</v>
+        <v>119797605</v>
       </c>
       <c r="B91" t="n">
         <v>91858</v>
@@ -10352,10 +10356,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>752740</v>
+        <v>752888</v>
       </c>
       <c r="R91" t="n">
-        <v>7092313</v>
+        <v>7092191</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10414,10 +10418,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119797567</v>
+        <v>119797602</v>
       </c>
       <c r="B92" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10430,21 +10434,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10454,10 +10458,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>752807</v>
+        <v>752769</v>
       </c>
       <c r="R92" t="n">
-        <v>7092251</v>
+        <v>7092291</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10516,10 +10520,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119797566</v>
+        <v>119797561</v>
       </c>
       <c r="B93" t="n">
-        <v>91870</v>
+        <v>91862</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10528,25 +10532,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10556,10 +10560,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>752868</v>
+        <v>752774</v>
       </c>
       <c r="R93" t="n">
-        <v>7092254</v>
+        <v>7092461</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10592,6 +10596,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10618,10 +10627,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119797540</v>
+        <v>119797579</v>
       </c>
       <c r="B94" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10634,21 +10643,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10658,10 +10667,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>752867</v>
+        <v>752762</v>
       </c>
       <c r="R94" t="n">
-        <v>7092243</v>
+        <v>7092223</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10694,11 +10703,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10725,10 +10729,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119797549</v>
+        <v>119797562</v>
       </c>
       <c r="B95" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10737,25 +10741,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10765,10 +10769,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752755</v>
+        <v>752870</v>
       </c>
       <c r="R95" t="n">
-        <v>7092400</v>
+        <v>7092247</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10801,6 +10805,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10827,10 +10836,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119797595</v>
+        <v>119797547</v>
       </c>
       <c r="B96" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10839,42 +10848,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752803</v>
+        <v>752758</v>
       </c>
       <c r="R96" t="n">
-        <v>7092370</v>
+        <v>7092263</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10907,11 +10912,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Bredvid grop</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10938,7 +10938,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119797550</v>
+        <v>119797540</v>
       </c>
       <c r="B97" t="n">
         <v>91902</v>
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752815</v>
+        <v>752867</v>
       </c>
       <c r="R97" t="n">
-        <v>7092360</v>
+        <v>7092243</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11014,6 +11014,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11040,10 +11045,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119797565</v>
+        <v>119797574</v>
       </c>
       <c r="B98" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11052,25 +11057,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11080,10 +11085,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>752765</v>
+        <v>752787</v>
       </c>
       <c r="R98" t="n">
-        <v>7092391</v>
+        <v>7092311</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11142,7 +11147,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119797601</v>
+        <v>119797603</v>
       </c>
       <c r="B99" t="n">
         <v>91858</v>
@@ -11182,10 +11187,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752857</v>
+        <v>752819</v>
       </c>
       <c r="R99" t="n">
-        <v>7092283</v>
+        <v>7092254</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11244,10 +11249,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119797608</v>
+        <v>119797554</v>
       </c>
       <c r="B100" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11260,21 +11265,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11284,10 +11289,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752711</v>
+        <v>752858</v>
       </c>
       <c r="R100" t="n">
-        <v>7092477</v>
+        <v>7092376</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11346,7 +11351,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119797597</v>
+        <v>119797594</v>
       </c>
       <c r="B101" t="n">
         <v>89269</v>
@@ -11386,10 +11391,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752839</v>
+        <v>752842</v>
       </c>
       <c r="R101" t="n">
-        <v>7092201</v>
+        <v>7092347</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11422,6 +11427,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11448,10 +11458,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119797599</v>
+        <v>119797544</v>
       </c>
       <c r="B102" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11460,25 +11470,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11488,10 +11498,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752863</v>
+        <v>752740</v>
       </c>
       <c r="R102" t="n">
-        <v>7092380</v>
+        <v>7092394</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11550,10 +11560,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119797581</v>
+        <v>119797530</v>
       </c>
       <c r="B103" t="n">
-        <v>91881</v>
+        <v>89292</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11562,42 +11572,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>6286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752686</v>
+        <v>752727</v>
       </c>
       <c r="R103" t="n">
-        <v>7092272</v>
+        <v>7092459</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11630,11 +11636,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Nära stigen</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11661,10 +11662,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119797564</v>
+        <v>119797601</v>
       </c>
       <c r="B104" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11677,21 +11678,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11701,10 +11702,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752716</v>
+        <v>752857</v>
       </c>
       <c r="R104" t="n">
-        <v>7092384</v>
+        <v>7092283</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11763,10 +11764,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119797562</v>
+        <v>119797566</v>
       </c>
       <c r="B105" t="n">
-        <v>91862</v>
+        <v>91870</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11775,25 +11776,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11803,10 +11804,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>752870</v>
+        <v>752868</v>
       </c>
       <c r="R105" t="n">
-        <v>7092247</v>
+        <v>7092254</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11839,11 +11840,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11870,10 +11866,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119797534</v>
+        <v>119797573</v>
       </c>
       <c r="B106" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11886,21 +11882,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11910,10 +11906,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>752725</v>
+        <v>752711</v>
       </c>
       <c r="R106" t="n">
-        <v>7092290</v>
+        <v>7092477</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11972,10 +11968,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119797530</v>
+        <v>119797572</v>
       </c>
       <c r="B107" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11984,25 +11980,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12012,10 +12008,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>752727</v>
+        <v>752714</v>
       </c>
       <c r="R107" t="n">
-        <v>7092459</v>
+        <v>7092390</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12074,10 +12070,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119797537</v>
+        <v>119797532</v>
       </c>
       <c r="B108" t="n">
-        <v>91901</v>
+        <v>57473</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12090,34 +12086,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>752807</v>
+        <v>752730</v>
       </c>
       <c r="R108" t="n">
-        <v>7092369</v>
+        <v>7092301</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12150,11 +12151,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12181,10 +12177,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119797546</v>
+        <v>119797578</v>
       </c>
       <c r="B109" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12197,21 +12193,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12221,10 +12217,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>752754</v>
+        <v>752895</v>
       </c>
       <c r="R109" t="n">
-        <v>7092268</v>
+        <v>7092346</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12283,10 +12279,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119797603</v>
+        <v>119797608</v>
       </c>
       <c r="B110" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12295,25 +12291,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12323,10 +12319,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>752819</v>
+        <v>752711</v>
       </c>
       <c r="R110" t="n">
-        <v>7092254</v>
+        <v>7092477</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12385,10 +12381,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119797556</v>
+        <v>119797534</v>
       </c>
       <c r="B111" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12401,21 +12397,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12425,10 +12421,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>752877</v>
+        <v>752725</v>
       </c>
       <c r="R111" t="n">
-        <v>7092306</v>
+        <v>7092290</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12487,10 +12483,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119797545</v>
+        <v>119797588</v>
       </c>
       <c r="B112" t="n">
-        <v>91902</v>
+        <v>89229</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12499,38 +12495,42 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>752728</v>
+        <v>752818</v>
       </c>
       <c r="R112" t="n">
-        <v>7092268</v>
+        <v>7092380</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12589,10 +12589,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119797573</v>
+        <v>119797548</v>
       </c>
       <c r="B113" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12605,21 +12605,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12629,10 +12629,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>752711</v>
+        <v>752765</v>
       </c>
       <c r="R113" t="n">
-        <v>7092477</v>
+        <v>7092348</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12691,7 +12691,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119797554</v>
+        <v>119797543</v>
       </c>
       <c r="B114" t="n">
         <v>91902</v>
@@ -12731,10 +12731,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>752858</v>
+        <v>752807</v>
       </c>
       <c r="R114" t="n">
-        <v>7092376</v>
+        <v>7092368</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12767,6 +12767,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12793,7 +12798,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119797548</v>
+        <v>119797553</v>
       </c>
       <c r="B115" t="n">
         <v>91902</v>
@@ -12833,10 +12838,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>752765</v>
+        <v>752830</v>
       </c>
       <c r="R115" t="n">
-        <v>7092348</v>
+        <v>7092393</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12895,10 +12900,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797561</v>
+        <v>119797537</v>
       </c>
       <c r="B116" t="n">
-        <v>91862</v>
+        <v>91901</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12907,25 +12912,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4365</v>
+        <v>5448</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12935,10 +12940,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752774</v>
+        <v>752807</v>
       </c>
       <c r="R116" t="n">
-        <v>7092461</v>
+        <v>7092369</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12975,7 +12980,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13002,10 +13007,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119797560</v>
+        <v>119797546</v>
       </c>
       <c r="B117" t="n">
-        <v>57336</v>
+        <v>91902</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13018,39 +13023,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>5449</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>752728</v>
+        <v>752754</v>
       </c>
       <c r="R117" t="n">
-        <v>7092269</v>
+        <v>7092268</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13085,11 +13085,6 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13098,26 +13093,6 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
@@ -13134,10 +13109,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119797557</v>
+        <v>119797571</v>
       </c>
       <c r="B118" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13150,21 +13125,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13174,10 +13149,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>752808</v>
+        <v>752807</v>
       </c>
       <c r="R118" t="n">
-        <v>7092251</v>
+        <v>7092369</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13210,6 +13185,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>I grop</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13236,10 +13216,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119797594</v>
+        <v>119797570</v>
       </c>
       <c r="B119" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13248,25 +13228,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13276,7 +13256,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>752842</v>
+        <v>752707</v>
       </c>
       <c r="R119" t="n">
         <v>7092347</v>
@@ -13316,7 +13296,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Äldre fruktkropp</t>
+          <t>Stigen</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13343,10 +13323,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119797547</v>
+        <v>119797576</v>
       </c>
       <c r="B120" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13359,21 +13339,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13383,10 +13363,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>752758</v>
+        <v>752864</v>
       </c>
       <c r="R120" t="n">
-        <v>7092263</v>
+        <v>7092357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13445,10 +13425,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119797538</v>
+        <v>119797560</v>
       </c>
       <c r="B121" t="n">
-        <v>91901</v>
+        <v>57336</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13461,34 +13441,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5448</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>752734</v>
+        <v>752728</v>
       </c>
       <c r="R121" t="n">
-        <v>7092340</v>
+        <v>7092269</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13523,6 +13508,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -13531,6 +13521,26 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
@@ -13547,10 +13557,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119797575</v>
+        <v>119797549</v>
       </c>
       <c r="B122" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13563,21 +13573,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13587,10 +13597,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>752836</v>
+        <v>752755</v>
       </c>
       <c r="R122" t="n">
-        <v>7092356</v>
+        <v>7092400</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13649,10 +13659,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119797571</v>
+        <v>119797583</v>
       </c>
       <c r="B123" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13665,21 +13675,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13689,10 +13699,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>752807</v>
+        <v>752719</v>
       </c>
       <c r="R123" t="n">
-        <v>7092369</v>
+        <v>7092452</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13725,11 +13735,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>I grop</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13756,10 +13761,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119797605</v>
+        <v>119797595</v>
       </c>
       <c r="B124" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13768,38 +13773,42 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>752888</v>
+        <v>752803</v>
       </c>
       <c r="R124" t="n">
-        <v>7092191</v>
+        <v>7092370</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13832,6 +13841,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Bredvid grop</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13858,10 +13872,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119797558</v>
+        <v>119797610</v>
       </c>
       <c r="B125" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13874,21 +13888,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13898,10 +13912,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>752822</v>
+        <v>752864</v>
       </c>
       <c r="R125" t="n">
-        <v>7092252</v>
+        <v>7092254</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13960,10 +13974,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119797588</v>
+        <v>119797599</v>
       </c>
       <c r="B126" t="n">
-        <v>89229</v>
+        <v>91858</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13972,39 +13986,35 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1593</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>752818</v>
+        <v>752863</v>
       </c>
       <c r="R126" t="n">
         <v>7092380</v>
@@ -14066,10 +14076,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119797574</v>
+        <v>119797611</v>
       </c>
       <c r="B127" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14082,21 +14092,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14106,10 +14116,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>752787</v>
+        <v>752818</v>
       </c>
       <c r="R127" t="n">
-        <v>7092311</v>
+        <v>7092235</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14168,10 +14178,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119797579</v>
+        <v>119797557</v>
       </c>
       <c r="B128" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14184,21 +14194,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14208,10 +14218,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>752762</v>
+        <v>752808</v>
       </c>
       <c r="R128" t="n">
-        <v>7092223</v>
+        <v>7092251</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14270,10 +14280,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119797539</v>
+        <v>119797564</v>
       </c>
       <c r="B129" t="n">
-        <v>91901</v>
+        <v>91870</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14282,25 +14292,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5448</v>
+        <v>4366</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14310,10 +14320,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>752737</v>
+        <v>752716</v>
       </c>
       <c r="R129" t="n">
-        <v>7092298</v>
+        <v>7092384</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14372,10 +14382,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119797576</v>
+        <v>119797604</v>
       </c>
       <c r="B130" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14384,25 +14394,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14412,10 +14422,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>752864</v>
+        <v>752825</v>
       </c>
       <c r="R130" t="n">
-        <v>7092357</v>
+        <v>7092235</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14474,10 +14484,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119797572</v>
+        <v>119797607</v>
       </c>
       <c r="B131" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14490,34 +14500,38 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>752714</v>
+        <v>752776</v>
       </c>
       <c r="R131" t="n">
-        <v>7092390</v>
+        <v>7092312</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14576,10 +14590,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119797610</v>
+        <v>119797545</v>
       </c>
       <c r="B132" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14592,21 +14606,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14616,10 +14630,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752864</v>
+        <v>752728</v>
       </c>
       <c r="R132" t="n">
-        <v>7092254</v>
+        <v>7092268</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14678,7 +14692,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119797543</v>
+        <v>119797542</v>
       </c>
       <c r="B133" t="n">
         <v>91902</v>
@@ -14718,10 +14732,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752807</v>
+        <v>752885</v>
       </c>
       <c r="R133" t="n">
-        <v>7092368</v>
+        <v>7092352</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14758,7 +14772,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>I grop</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14785,10 +14799,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119797552</v>
+        <v>119797600</v>
       </c>
       <c r="B134" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14797,25 +14811,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14825,10 +14839,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>752818</v>
+        <v>752886</v>
       </c>
       <c r="R134" t="n">
-        <v>7092383</v>
+        <v>7092295</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14887,10 +14901,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119797570</v>
+        <v>119797567</v>
       </c>
       <c r="B135" t="n">
-        <v>91850</v>
+        <v>91870</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14899,25 +14913,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14927,10 +14941,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>752707</v>
+        <v>752807</v>
       </c>
       <c r="R135" t="n">
-        <v>7092347</v>
+        <v>7092251</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14963,11 +14977,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Stigen</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14994,10 +15003,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119797533</v>
+        <v>119797609</v>
       </c>
       <c r="B136" t="n">
-        <v>57473</v>
+        <v>91852</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15010,39 +15019,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>103021</v>
+        <v>4362</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>752826</v>
+        <v>752855</v>
       </c>
       <c r="R136" t="n">
-        <v>7092234</v>
+        <v>7092378</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15101,10 +15105,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797607</v>
+        <v>119797575</v>
       </c>
       <c r="B137" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15117,38 +15121,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752776</v>
+        <v>752836</v>
       </c>
       <c r="R137" t="n">
-        <v>7092312</v>
+        <v>7092356</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15207,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797544</v>
+        <v>119797533</v>
       </c>
       <c r="B138" t="n">
-        <v>91902</v>
+        <v>57473</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15223,34 +15223,39 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5449</v>
+        <v>103021</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752740</v>
+        <v>752826</v>
       </c>
       <c r="R138" t="n">
-        <v>7092394</v>
+        <v>7092234</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15309,7 +15314,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797553</v>
+        <v>119797555</v>
       </c>
       <c r="B139" t="n">
         <v>91902</v>
@@ -15349,10 +15354,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752830</v>
+        <v>752885</v>
       </c>
       <c r="R139" t="n">
-        <v>7092393</v>
+        <v>7092323</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15411,10 +15416,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119797532</v>
+        <v>119797539</v>
       </c>
       <c r="B140" t="n">
-        <v>57473</v>
+        <v>91901</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15427,39 +15432,34 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>103021</v>
+        <v>5448</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>752730</v>
+        <v>752737</v>
       </c>
       <c r="R140" t="n">
-        <v>7092301</v>
+        <v>7092298</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15518,10 +15518,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119808311</v>
+        <v>119808297</v>
       </c>
       <c r="B141" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15530,25 +15530,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>752771</v>
+        <v>752905</v>
       </c>
       <c r="R141" t="n">
-        <v>7092333</v>
+        <v>7092298</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15630,7 +15630,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119808298</v>
+        <v>119808308</v>
       </c>
       <c r="B142" t="n">
         <v>91902</v>
@@ -15670,10 +15670,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>752922</v>
+        <v>752743</v>
       </c>
       <c r="R142" t="n">
-        <v>7092310</v>
+        <v>7092343</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15742,7 +15742,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119808294</v>
+        <v>119808299</v>
       </c>
       <c r="B143" t="n">
         <v>91858</v>
@@ -15782,10 +15782,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>752867</v>
+        <v>752962</v>
       </c>
       <c r="R143" t="n">
-        <v>7092294</v>
+        <v>7092343</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808312</v>
+        <v>119808293</v>
       </c>
       <c r="B144" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15866,25 +15866,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,10 +15894,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752773</v>
+        <v>752820</v>
       </c>
       <c r="R144" t="n">
-        <v>7092341</v>
+        <v>7092239</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808314</v>
+        <v>119808309</v>
       </c>
       <c r="B145" t="n">
         <v>91902</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752795</v>
+        <v>752727</v>
       </c>
       <c r="R145" t="n">
-        <v>7092304</v>
+        <v>7092321</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16078,10 +16078,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119808293</v>
+        <v>119808312</v>
       </c>
       <c r="B146" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -16090,25 +16090,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752820</v>
+        <v>752773</v>
       </c>
       <c r="R146" t="n">
-        <v>7092239</v>
+        <v>7092341</v>
       </c>
       <c r="S146" t="n">
         <v>25</v>
@@ -16153,7 +16153,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16163,7 +16163,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16190,10 +16190,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119808303</v>
+        <v>119808306</v>
       </c>
       <c r="B147" t="n">
-        <v>91481</v>
+        <v>91902</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -16206,21 +16206,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752812</v>
+        <v>752764</v>
       </c>
       <c r="R147" t="n">
-        <v>7092433</v>
+        <v>7092409</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16302,10 +16302,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119808297</v>
+        <v>119808292</v>
       </c>
       <c r="B148" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16318,21 +16318,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16342,10 +16342,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752905</v>
+        <v>752837</v>
       </c>
       <c r="R148" t="n">
-        <v>7092298</v>
+        <v>7092228</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16414,10 +16414,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119808305</v>
+        <v>119808302</v>
       </c>
       <c r="B149" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16426,25 +16426,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16454,10 +16454,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752740</v>
+        <v>752841</v>
       </c>
       <c r="R149" t="n">
-        <v>7092467</v>
+        <v>7092401</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16526,7 +16526,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119808308</v>
+        <v>119808313</v>
       </c>
       <c r="B150" t="n">
         <v>91902</v>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752743</v>
+        <v>752808</v>
       </c>
       <c r="R150" t="n">
-        <v>7092343</v>
+        <v>7092316</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16638,10 +16638,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119808304</v>
+        <v>119808303</v>
       </c>
       <c r="B151" t="n">
-        <v>89292</v>
+        <v>91481</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16650,25 +16650,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752773</v>
+        <v>752812</v>
       </c>
       <c r="R151" t="n">
-        <v>7092434</v>
+        <v>7092433</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16750,10 +16750,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119808300</v>
+        <v>119808298</v>
       </c>
       <c r="B152" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16766,21 +16766,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16790,10 +16790,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752943</v>
+        <v>752922</v>
       </c>
       <c r="R152" t="n">
-        <v>7092394</v>
+        <v>7092310</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808306</v>
+        <v>119808311</v>
       </c>
       <c r="B154" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16986,25 +16986,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752764</v>
+        <v>752771</v>
       </c>
       <c r="R154" t="n">
-        <v>7092409</v>
+        <v>7092333</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17086,10 +17086,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808307</v>
+        <v>119808294</v>
       </c>
       <c r="B155" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17102,21 +17102,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752764</v>
+        <v>752867</v>
       </c>
       <c r="R155" t="n">
-        <v>7092409</v>
+        <v>7092294</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17198,10 +17198,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119808292</v>
+        <v>119808296</v>
       </c>
       <c r="B156" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -17210,25 +17210,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752837</v>
+        <v>752902</v>
       </c>
       <c r="R156" t="n">
-        <v>7092228</v>
+        <v>7092285</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17310,10 +17310,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119808296</v>
+        <v>119808307</v>
       </c>
       <c r="B157" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17326,21 +17326,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17350,10 +17350,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752902</v>
+        <v>752764</v>
       </c>
       <c r="R157" t="n">
-        <v>7092285</v>
+        <v>7092409</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17422,10 +17422,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808302</v>
+        <v>119808301</v>
       </c>
       <c r="B158" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17434,25 +17434,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752841</v>
+        <v>752896</v>
       </c>
       <c r="R158" t="n">
-        <v>7092401</v>
+        <v>7092397</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808301</v>
+        <v>119808300</v>
       </c>
       <c r="B159" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17550,21 +17550,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752896</v>
+        <v>752943</v>
       </c>
       <c r="R159" t="n">
-        <v>7092397</v>
+        <v>7092394</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17646,10 +17646,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808299</v>
+        <v>119808305</v>
       </c>
       <c r="B160" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17658,25 +17658,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752962</v>
+        <v>752740</v>
       </c>
       <c r="R160" t="n">
-        <v>7092343</v>
+        <v>7092467</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17758,10 +17758,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808309</v>
+        <v>119808304</v>
       </c>
       <c r="B161" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17770,25 +17770,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752727</v>
+        <v>752773</v>
       </c>
       <c r="R161" t="n">
-        <v>7092321</v>
+        <v>7092434</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17870,7 +17870,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119808313</v>
+        <v>119808314</v>
       </c>
       <c r="B162" t="n">
         <v>91902</v>
@@ -17910,10 +17910,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>752808</v>
+        <v>752795</v>
       </c>
       <c r="R162" t="n">
-        <v>7092316</v>
+        <v>7092304</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17982,7 +17982,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119892118</v>
+        <v>119891898</v>
       </c>
       <c r="B163" t="n">
         <v>89292</v>
@@ -18018,14 +18018,14 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>752838</v>
+        <v>752740</v>
       </c>
       <c r="R163" t="n">
-        <v>7092399</v>
+        <v>7092396</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18084,10 +18084,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119893175</v>
+        <v>119892118</v>
       </c>
       <c r="B164" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18096,25 +18096,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18124,10 +18124,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752982</v>
+        <v>752838</v>
       </c>
       <c r="R164" t="n">
-        <v>7092371</v>
+        <v>7092399</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18186,7 +18186,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119891991</v>
+        <v>119893208</v>
       </c>
       <c r="B165" t="n">
         <v>91902</v>
@@ -18226,10 +18226,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752740</v>
+        <v>752928</v>
       </c>
       <c r="R165" t="n">
-        <v>7092396</v>
+        <v>7092309</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18288,10 +18288,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119892909</v>
+        <v>119797563</v>
       </c>
       <c r="B166" t="n">
-        <v>91844</v>
+        <v>91862</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18300,38 +18300,45 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3100</v>
+        <v>4365</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752854</v>
+        <v>752807</v>
       </c>
       <c r="R166" t="n">
-        <v>7092368</v>
+        <v>7092367</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18358,12 +18365,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18372,25 +18384,26 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119893626</v>
+        <v>119893329</v>
       </c>
       <c r="B167" t="n">
         <v>91902</v>
@@ -18430,10 +18443,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752767</v>
+        <v>752893</v>
       </c>
       <c r="R167" t="n">
-        <v>7092396</v>
+        <v>7092272</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18492,10 +18505,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119893301</v>
+        <v>119893348</v>
       </c>
       <c r="B168" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18508,21 +18521,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18532,10 +18545,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752892</v>
+        <v>752893</v>
       </c>
       <c r="R168" t="n">
-        <v>7092280</v>
+        <v>7092272</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18594,10 +18607,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119893537</v>
+        <v>119892875</v>
       </c>
       <c r="B169" t="n">
-        <v>91850</v>
+        <v>88170</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18610,21 +18623,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4361</v>
+        <v>4962</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18634,10 +18647,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752759</v>
+        <v>752854</v>
       </c>
       <c r="R169" t="n">
-        <v>7092324</v>
+        <v>7092368</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18696,10 +18709,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119893483</v>
+        <v>119893016</v>
       </c>
       <c r="B170" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18712,21 +18725,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18736,10 +18749,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752795</v>
+        <v>752901</v>
       </c>
       <c r="R170" t="n">
-        <v>7092265</v>
+        <v>7092374</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18798,10 +18811,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119893348</v>
+        <v>119893626</v>
       </c>
       <c r="B171" t="n">
-        <v>91901</v>
+        <v>91902</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18814,21 +18827,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18838,10 +18851,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752893</v>
+        <v>752767</v>
       </c>
       <c r="R171" t="n">
-        <v>7092272</v>
+        <v>7092396</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18900,10 +18913,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893423</v>
+        <v>119893430</v>
       </c>
       <c r="B172" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18916,34 +18929,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752740</v>
+        <v>752897</v>
       </c>
       <c r="R172" t="n">
-        <v>7092396</v>
+        <v>7092235</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19002,10 +19015,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119891898</v>
+        <v>119893537</v>
       </c>
       <c r="B173" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19014,38 +19027,38 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752740</v>
+        <v>752759</v>
       </c>
       <c r="R173" t="n">
-        <v>7092396</v>
+        <v>7092324</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19104,10 +19117,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119893466</v>
+        <v>119891959</v>
       </c>
       <c r="B174" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19116,25 +19129,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19144,10 +19157,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752823</v>
+        <v>752740</v>
       </c>
       <c r="R174" t="n">
-        <v>7092228</v>
+        <v>7092396</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19206,10 +19219,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119797563</v>
+        <v>119893598</v>
       </c>
       <c r="B175" t="n">
-        <v>91862</v>
+        <v>89292</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19222,41 +19235,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr"/>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752807</v>
+        <v>752767</v>
       </c>
       <c r="R175" t="n">
-        <v>7092367</v>
+        <v>7092395</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19283,17 +19289,12 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19302,29 +19303,28 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119893473</v>
+        <v>119892909</v>
       </c>
       <c r="B176" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19337,21 +19337,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752827</v>
+        <v>752854</v>
       </c>
       <c r="R176" t="n">
-        <v>7092232</v>
+        <v>7092368</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19423,7 +19423,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119893208</v>
+        <v>119893473</v>
       </c>
       <c r="B177" t="n">
         <v>91902</v>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752928</v>
+        <v>752827</v>
       </c>
       <c r="R177" t="n">
-        <v>7092309</v>
+        <v>7092232</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19525,10 +19525,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119892875</v>
+        <v>119893301</v>
       </c>
       <c r="B178" t="n">
-        <v>88170</v>
+        <v>91850</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19541,21 +19541,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4962</v>
+        <v>4361</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752854</v>
+        <v>752892</v>
       </c>
       <c r="R178" t="n">
-        <v>7092368</v>
+        <v>7092280</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19627,10 +19627,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119891959</v>
+        <v>119893175</v>
       </c>
       <c r="B179" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19639,25 +19639,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19667,10 +19667,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752740</v>
+        <v>752982</v>
       </c>
       <c r="R179" t="n">
-        <v>7092396</v>
+        <v>7092371</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19729,10 +19729,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119893016</v>
+        <v>119893225</v>
       </c>
       <c r="B180" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19745,21 +19745,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19769,10 +19769,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752901</v>
+        <v>752927</v>
       </c>
       <c r="R180" t="n">
-        <v>7092374</v>
+        <v>7092298</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19831,7 +19831,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119893225</v>
+        <v>119893483</v>
       </c>
       <c r="B181" t="n">
         <v>91902</v>
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752927</v>
+        <v>752795</v>
       </c>
       <c r="R181" t="n">
-        <v>7092298</v>
+        <v>7092265</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119893598</v>
+        <v>119893423</v>
       </c>
       <c r="B182" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19945,38 +19945,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752767</v>
+        <v>752740</v>
       </c>
       <c r="R182" t="n">
-        <v>7092395</v>
+        <v>7092396</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20035,7 +20035,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119893430</v>
+        <v>119891991</v>
       </c>
       <c r="B183" t="n">
         <v>91902</v>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752897</v>
+        <v>752740</v>
       </c>
       <c r="R183" t="n">
-        <v>7092235</v>
+        <v>7092396</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119893329</v>
+        <v>119893466</v>
       </c>
       <c r="B184" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20153,21 +20153,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752893</v>
+        <v>752823</v>
       </c>
       <c r="R184" t="n">
-        <v>7092272</v>
+        <v>7092228</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934778</v>
+        <v>119934818</v>
       </c>
       <c r="B186" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,25 +20353,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -20381,10 +20381,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752778</v>
+        <v>753030</v>
       </c>
       <c r="R186" t="n">
-        <v>7092476</v>
+        <v>7092403</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20443,10 +20443,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934755</v>
+        <v>119934797</v>
       </c>
       <c r="B187" t="n">
-        <v>91481</v>
+        <v>91850</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20459,21 +20459,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20483,10 +20483,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752777</v>
+        <v>752806</v>
       </c>
       <c r="R187" t="n">
-        <v>7092472</v>
+        <v>7092716</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20545,10 +20545,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934768</v>
+        <v>119934775</v>
       </c>
       <c r="B188" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20561,34 +20561,38 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752771</v>
+        <v>752777</v>
       </c>
       <c r="R188" t="n">
-        <v>7092668</v>
+        <v>7092577</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20647,10 +20651,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934789</v>
+        <v>119934815</v>
       </c>
       <c r="B189" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20659,42 +20663,38 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752803</v>
+        <v>752779</v>
       </c>
       <c r="R189" t="n">
-        <v>7092378</v>
+        <v>7092482</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20753,10 +20753,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934765</v>
+        <v>119934812</v>
       </c>
       <c r="B190" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20765,42 +20765,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752760</v>
+        <v>752796</v>
       </c>
       <c r="R190" t="n">
-        <v>7092524</v>
+        <v>7092694</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20859,7 +20855,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934759</v>
+        <v>119934766</v>
       </c>
       <c r="B191" t="n">
         <v>91902</v>
@@ -20892,17 +20888,21 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752845</v>
+        <v>752751</v>
       </c>
       <c r="R191" t="n">
-        <v>7092505</v>
+        <v>7092507</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20935,11 +20935,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20966,10 +20961,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934760</v>
+        <v>119934781</v>
       </c>
       <c r="B192" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20982,26 +20977,26 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21010,10 +21005,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752896</v>
+        <v>752766</v>
       </c>
       <c r="R192" t="n">
-        <v>7092456</v>
+        <v>7092643</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21046,6 +21041,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21072,7 +21072,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934782</v>
+        <v>119934783</v>
       </c>
       <c r="B193" t="n">
         <v>91850</v>
@@ -21107,7 +21107,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21116,10 +21116,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752743</v>
+        <v>752771</v>
       </c>
       <c r="R193" t="n">
-        <v>7092544</v>
+        <v>7092674</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21152,6 +21152,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21178,10 +21183,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934796</v>
+        <v>119934774</v>
       </c>
       <c r="B194" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21194,34 +21199,38 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752805</v>
+        <v>752891</v>
       </c>
       <c r="R194" t="n">
-        <v>7092505</v>
+        <v>7092444</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21280,10 +21289,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934817</v>
+        <v>119934777</v>
       </c>
       <c r="B195" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21292,25 +21301,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21320,10 +21329,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752778</v>
+        <v>752809</v>
       </c>
       <c r="R195" t="n">
-        <v>7092478</v>
+        <v>7092467</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21488,10 +21497,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934786</v>
+        <v>119934752</v>
       </c>
       <c r="B197" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21500,42 +21509,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752833</v>
+        <v>752794</v>
       </c>
       <c r="R197" t="n">
-        <v>7092510</v>
+        <v>7092570</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21568,6 +21573,11 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21594,10 +21604,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934764</v>
+        <v>119934806</v>
       </c>
       <c r="B198" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21606,30 +21616,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21638,10 +21648,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752759</v>
+        <v>752816</v>
       </c>
       <c r="R198" t="n">
-        <v>7092478</v>
+        <v>7092714</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21700,10 +21710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934767</v>
+        <v>119934808</v>
       </c>
       <c r="B199" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21712,38 +21722,42 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752720</v>
+        <v>752819</v>
       </c>
       <c r="R199" t="n">
-        <v>7092493</v>
+        <v>7092515</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21802,10 +21816,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934763</v>
+        <v>119934756</v>
       </c>
       <c r="B200" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21814,30 +21828,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -21846,10 +21860,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752788</v>
+        <v>752783</v>
       </c>
       <c r="R200" t="n">
-        <v>7092548</v>
+        <v>7092657</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21908,10 +21922,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934813</v>
+        <v>119934771</v>
       </c>
       <c r="B201" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21920,25 +21934,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21948,10 +21962,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752857</v>
+        <v>752765</v>
       </c>
       <c r="R201" t="n">
-        <v>7092672</v>
+        <v>7092632</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21984,6 +21998,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22010,10 +22029,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934785</v>
+        <v>119934823</v>
       </c>
       <c r="B202" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22026,26 +22045,26 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -22054,10 +22073,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752721</v>
+        <v>752959</v>
       </c>
       <c r="R202" t="n">
-        <v>7092493</v>
+        <v>7092467</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22116,10 +22135,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934809</v>
+        <v>119934773</v>
       </c>
       <c r="B203" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22128,30 +22147,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22160,10 +22179,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752817</v>
+        <v>752853</v>
       </c>
       <c r="R203" t="n">
-        <v>7092378</v>
+        <v>7092405</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22196,6 +22215,11 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22222,10 +22246,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934798</v>
+        <v>119934767</v>
       </c>
       <c r="B204" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22238,21 +22262,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22262,10 +22286,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752945</v>
+        <v>752720</v>
       </c>
       <c r="R204" t="n">
-        <v>7092339</v>
+        <v>7092493</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22324,10 +22348,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934818</v>
+        <v>119934762</v>
       </c>
       <c r="B205" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22336,38 +22360,42 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>753030</v>
+        <v>752732</v>
       </c>
       <c r="R205" t="n">
-        <v>7092403</v>
+        <v>7092502</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22426,10 +22454,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934815</v>
+        <v>119934772</v>
       </c>
       <c r="B206" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22438,25 +22466,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22466,10 +22494,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752779</v>
+        <v>752757</v>
       </c>
       <c r="R206" t="n">
-        <v>7092482</v>
+        <v>7092617</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22502,6 +22530,11 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22528,10 +22561,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934799</v>
+        <v>119934755</v>
       </c>
       <c r="B207" t="n">
-        <v>91881</v>
+        <v>91481</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22544,38 +22577,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5966</v>
+        <v>4745</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752754</v>
+        <v>752777</v>
       </c>
       <c r="R207" t="n">
-        <v>7092559</v>
+        <v>7092472</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22634,10 +22663,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934753</v>
+        <v>119934799</v>
       </c>
       <c r="B208" t="n">
-        <v>89292</v>
+        <v>91881</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22646,38 +22675,42 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752888</v>
+        <v>752754</v>
       </c>
       <c r="R208" t="n">
-        <v>7092677</v>
+        <v>7092559</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22736,10 +22769,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934784</v>
+        <v>119934761</v>
       </c>
       <c r="B209" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22752,26 +22785,26 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -22780,10 +22813,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752891</v>
+        <v>752772</v>
       </c>
       <c r="R209" t="n">
-        <v>7092445</v>
+        <v>7092487</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22842,10 +22875,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934794</v>
+        <v>119934768</v>
       </c>
       <c r="B210" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22858,38 +22891,34 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752999</v>
+        <v>752771</v>
       </c>
       <c r="R210" t="n">
-        <v>7092455</v>
+        <v>7092668</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22948,10 +22977,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934788</v>
+        <v>119934758</v>
       </c>
       <c r="B211" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22964,38 +22993,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752781</v>
+        <v>752979</v>
       </c>
       <c r="R211" t="n">
-        <v>7092640</v>
+        <v>7092382</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23028,6 +23053,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23054,10 +23084,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934812</v>
+        <v>119934798</v>
       </c>
       <c r="B212" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23066,25 +23096,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23094,10 +23124,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752796</v>
+        <v>752945</v>
       </c>
       <c r="R212" t="n">
-        <v>7092694</v>
+        <v>7092339</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23156,10 +23186,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934766</v>
+        <v>119934786</v>
       </c>
       <c r="B213" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23172,26 +23202,26 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23200,10 +23230,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752751</v>
+        <v>752833</v>
       </c>
       <c r="R213" t="n">
-        <v>7092507</v>
+        <v>7092510</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23262,10 +23292,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934773</v>
+        <v>119934760</v>
       </c>
       <c r="B214" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23274,30 +23304,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23306,10 +23336,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752853</v>
+        <v>752896</v>
       </c>
       <c r="R214" t="n">
-        <v>7092405</v>
+        <v>7092456</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23342,11 +23372,6 @@
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23373,10 +23398,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934748</v>
+        <v>119934763</v>
       </c>
       <c r="B215" t="n">
-        <v>89650</v>
+        <v>91902</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23389,34 +23414,38 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752762</v>
+        <v>752788</v>
       </c>
       <c r="R215" t="n">
-        <v>7092586</v>
+        <v>7092548</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23451,11 +23480,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -23464,21 +23488,6 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ215" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -23495,10 +23504,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934756</v>
+        <v>119934765</v>
       </c>
       <c r="B216" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23507,30 +23516,30 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -23539,10 +23548,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752783</v>
+        <v>752760</v>
       </c>
       <c r="R216" t="n">
-        <v>7092657</v>
+        <v>7092524</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23601,10 +23610,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934814</v>
+        <v>119934778</v>
       </c>
       <c r="B217" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23613,25 +23622,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23641,10 +23650,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752764</v>
+        <v>752778</v>
       </c>
       <c r="R217" t="n">
-        <v>7092560</v>
+        <v>7092476</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23703,7 +23712,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934790</v>
+        <v>119934794</v>
       </c>
       <c r="B218" t="n">
         <v>91850</v>
@@ -23747,10 +23756,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752853</v>
+        <v>752999</v>
       </c>
       <c r="R218" t="n">
-        <v>7092405</v>
+        <v>7092455</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23809,10 +23818,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934787</v>
+        <v>119934814</v>
       </c>
       <c r="B219" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23821,42 +23830,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752738</v>
+        <v>752764</v>
       </c>
       <c r="R219" t="n">
-        <v>7092548</v>
+        <v>7092560</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23889,11 +23894,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23920,10 +23920,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934758</v>
+        <v>119934776</v>
       </c>
       <c r="B220" t="n">
-        <v>91901</v>
+        <v>91874</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23936,34 +23936,38 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752979</v>
+        <v>752759</v>
       </c>
       <c r="R220" t="n">
-        <v>7092382</v>
+        <v>7092525</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23996,11 +24000,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24027,7 +24026,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934791</v>
+        <v>119934785</v>
       </c>
       <c r="B221" t="n">
         <v>91850</v>
@@ -24062,7 +24061,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -24071,10 +24070,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752777</v>
+        <v>752721</v>
       </c>
       <c r="R221" t="n">
-        <v>7092488</v>
+        <v>7092493</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24133,7 +24132,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934795</v>
+        <v>119934790</v>
       </c>
       <c r="B222" t="n">
         <v>91850</v>
@@ -24168,7 +24167,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -24177,10 +24176,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752996</v>
+        <v>752853</v>
       </c>
       <c r="R222" t="n">
-        <v>7092398</v>
+        <v>7092405</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24213,11 +24212,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24244,10 +24238,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934819</v>
+        <v>119934764</v>
       </c>
       <c r="B223" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24256,38 +24250,42 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752979</v>
+        <v>752759</v>
       </c>
       <c r="R223" t="n">
-        <v>7092382</v>
+        <v>7092478</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24346,7 +24344,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934781</v>
+        <v>119934792</v>
       </c>
       <c r="B224" t="n">
         <v>91850</v>
@@ -24381,7 +24379,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24390,10 +24388,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752766</v>
+        <v>752867</v>
       </c>
       <c r="R224" t="n">
-        <v>7092643</v>
+        <v>7092495</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24426,11 +24424,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24457,10 +24450,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934806</v>
+        <v>119934796</v>
       </c>
       <c r="B225" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24469,42 +24462,38 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752816</v>
+        <v>752805</v>
       </c>
       <c r="R225" t="n">
-        <v>7092714</v>
+        <v>7092505</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24563,10 +24552,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934808</v>
+        <v>119934788</v>
       </c>
       <c r="B226" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24575,25 +24564,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -24607,10 +24596,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752819</v>
+        <v>752781</v>
       </c>
       <c r="R226" t="n">
-        <v>7092515</v>
+        <v>7092640</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24669,10 +24658,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934761</v>
+        <v>119934787</v>
       </c>
       <c r="B227" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24685,26 +24674,26 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24713,10 +24702,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752772</v>
+        <v>752738</v>
       </c>
       <c r="R227" t="n">
-        <v>7092487</v>
+        <v>7092548</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24749,6 +24738,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24775,10 +24769,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934774</v>
+        <v>119934813</v>
       </c>
       <c r="B228" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24787,42 +24781,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752891</v>
+        <v>752857</v>
       </c>
       <c r="R228" t="n">
-        <v>7092444</v>
+        <v>7092672</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24983,10 +24973,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934775</v>
+        <v>119934784</v>
       </c>
       <c r="B230" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24999,26 +24989,26 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25027,10 +25017,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>752777</v>
+        <v>752891</v>
       </c>
       <c r="R230" t="n">
-        <v>7092577</v>
+        <v>7092445</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25089,10 +25079,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934777</v>
+        <v>119934753</v>
       </c>
       <c r="B231" t="n">
-        <v>91874</v>
+        <v>89292</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25101,25 +25091,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2059</v>
+        <v>6286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25129,10 +25119,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752809</v>
+        <v>752888</v>
       </c>
       <c r="R231" t="n">
-        <v>7092467</v>
+        <v>7092677</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25191,10 +25181,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934772</v>
+        <v>119934789</v>
       </c>
       <c r="B232" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25203,38 +25193,42 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752757</v>
+        <v>752803</v>
       </c>
       <c r="R232" t="n">
-        <v>7092617</v>
+        <v>7092378</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25267,11 +25261,6 @@
       <c r="AA232" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25298,10 +25287,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934771</v>
+        <v>119934821</v>
       </c>
       <c r="B233" t="n">
-        <v>91862</v>
+        <v>91852</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25310,38 +25299,42 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752765</v>
+        <v>752994</v>
       </c>
       <c r="R233" t="n">
-        <v>7092632</v>
+        <v>7092431</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25374,11 +25367,6 @@
       <c r="AA233" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -25405,7 +25393,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934797</v>
+        <v>119934791</v>
       </c>
       <c r="B234" t="n">
         <v>91850</v>
@@ -25438,17 +25426,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752806</v>
+        <v>752777</v>
       </c>
       <c r="R234" t="n">
-        <v>7092716</v>
+        <v>7092488</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25507,10 +25499,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934792</v>
+        <v>119934817</v>
       </c>
       <c r="B235" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25519,42 +25511,38 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752867</v>
+        <v>752778</v>
       </c>
       <c r="R235" t="n">
-        <v>7092495</v>
+        <v>7092478</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25613,10 +25601,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934823</v>
+        <v>119934819</v>
       </c>
       <c r="B236" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25625,42 +25613,38 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752959</v>
+        <v>752979</v>
       </c>
       <c r="R236" t="n">
-        <v>7092467</v>
+        <v>7092382</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25719,7 +25703,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934762</v>
+        <v>119934759</v>
       </c>
       <c r="B237" t="n">
         <v>91902</v>
@@ -25752,21 +25736,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752732</v>
+        <v>752845</v>
       </c>
       <c r="R237" t="n">
-        <v>7092502</v>
+        <v>7092505</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25799,6 +25779,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25825,10 +25810,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934821</v>
+        <v>119934809</v>
       </c>
       <c r="B238" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25837,30 +25822,30 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -25869,10 +25854,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752994</v>
+        <v>752817</v>
       </c>
       <c r="R238" t="n">
-        <v>7092431</v>
+        <v>7092378</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25931,10 +25916,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934776</v>
+        <v>119934748</v>
       </c>
       <c r="B239" t="n">
-        <v>91874</v>
+        <v>89650</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25947,38 +25932,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752759</v>
+        <v>752762</v>
       </c>
       <c r="R239" t="n">
-        <v>7092525</v>
+        <v>7092586</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26013,6 +25994,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC239" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD239" t="b">
         <v>0</v>
       </c>
@@ -26021,6 +26007,21 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
@@ -26037,10 +26038,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934752</v>
+        <v>119934795</v>
       </c>
       <c r="B240" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -26049,38 +26050,42 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P240" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752794</v>
+        <v>752996</v>
       </c>
       <c r="R240" t="n">
-        <v>7092570</v>
+        <v>7092398</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26117,7 +26122,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26144,7 +26149,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934783</v>
+        <v>119934782</v>
       </c>
       <c r="B241" t="n">
         <v>91850</v>
@@ -26179,7 +26184,7 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -26188,10 +26193,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752771</v>
+        <v>752743</v>
       </c>
       <c r="R241" t="n">
-        <v>7092674</v>
+        <v>7092544</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26226,11 +26231,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
-        </is>
-      </c>
       <c r="AD241" t="b">
         <v>0</v>
       </c>
@@ -26252,6 +26252,108 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>120403802</v>
+      </c>
+      <c r="B242" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>752941</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7092305</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -15207,10 +15207,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797533</v>
+        <v>119797555</v>
       </c>
       <c r="B138" t="n">
-        <v>57473</v>
+        <v>91902</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15223,39 +15223,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>103021</v>
+        <v>5449</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752826</v>
+        <v>752885</v>
       </c>
       <c r="R138" t="n">
-        <v>7092234</v>
+        <v>7092323</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15314,10 +15309,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797555</v>
+        <v>119797539</v>
       </c>
       <c r="B139" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15330,21 +15325,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15354,10 +15349,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752885</v>
+        <v>752737</v>
       </c>
       <c r="R139" t="n">
-        <v>7092323</v>
+        <v>7092298</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15416,10 +15411,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119797539</v>
+        <v>119797533</v>
       </c>
       <c r="B140" t="n">
-        <v>91901</v>
+        <v>57473</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15432,34 +15427,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>752737</v>
+        <v>752826</v>
       </c>
       <c r="R140" t="n">
-        <v>7092298</v>
+        <v>7092234</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -19831,10 +19831,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119893483</v>
+        <v>119893423</v>
       </c>
       <c r="B181" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19847,34 +19847,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752795</v>
+        <v>752740</v>
       </c>
       <c r="R181" t="n">
-        <v>7092265</v>
+        <v>7092396</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119893423</v>
+        <v>119893483</v>
       </c>
       <c r="B182" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19949,34 +19949,34 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752740</v>
+        <v>752795</v>
       </c>
       <c r="R182" t="n">
-        <v>7092396</v>
+        <v>7092265</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20753,10 +20753,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934812</v>
+        <v>119934781</v>
       </c>
       <c r="B190" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20765,38 +20765,42 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752796</v>
+        <v>752766</v>
       </c>
       <c r="R190" t="n">
-        <v>7092694</v>
+        <v>7092643</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20829,6 +20833,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20855,10 +20864,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934766</v>
+        <v>119934812</v>
       </c>
       <c r="B191" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20867,42 +20876,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752751</v>
+        <v>752796</v>
       </c>
       <c r="R191" t="n">
-        <v>7092507</v>
+        <v>7092694</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20961,7 +20966,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934781</v>
+        <v>119934783</v>
       </c>
       <c r="B192" t="n">
         <v>91850</v>
@@ -21005,10 +21010,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752766</v>
+        <v>752771</v>
       </c>
       <c r="R192" t="n">
-        <v>7092643</v>
+        <v>7092674</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21045,7 +21050,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21072,10 +21077,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934783</v>
+        <v>119934766</v>
       </c>
       <c r="B193" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21088,26 +21093,26 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21116,10 +21121,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752771</v>
+        <v>752751</v>
       </c>
       <c r="R193" t="n">
-        <v>7092674</v>
+        <v>7092507</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21152,11 +21157,6 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21710,10 +21710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934808</v>
+        <v>119934771</v>
       </c>
       <c r="B199" t="n">
-        <v>89269</v>
+        <v>91862</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21726,38 +21726,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752819</v>
+        <v>752765</v>
       </c>
       <c r="R199" t="n">
-        <v>7092515</v>
+        <v>7092632</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21790,6 +21786,11 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21816,10 +21817,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934756</v>
+        <v>119934808</v>
       </c>
       <c r="B200" t="n">
-        <v>89292</v>
+        <v>89269</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21832,26 +21833,26 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -21860,10 +21861,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752783</v>
+        <v>752819</v>
       </c>
       <c r="R200" t="n">
-        <v>7092657</v>
+        <v>7092515</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21922,10 +21923,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934771</v>
+        <v>119934756</v>
       </c>
       <c r="B201" t="n">
-        <v>91862</v>
+        <v>89292</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21938,34 +21939,38 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4365</v>
+        <v>6286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752765</v>
+        <v>752783</v>
       </c>
       <c r="R201" t="n">
-        <v>7092632</v>
+        <v>7092657</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21998,11 +22003,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22875,10 +22875,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934768</v>
+        <v>119934798</v>
       </c>
       <c r="B210" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22891,21 +22891,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22915,10 +22915,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752771</v>
+        <v>752945</v>
       </c>
       <c r="R210" t="n">
-        <v>7092668</v>
+        <v>7092339</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22977,10 +22977,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934758</v>
+        <v>119934768</v>
       </c>
       <c r="B211" t="n">
-        <v>91901</v>
+        <v>91902</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22993,21 +22993,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23017,10 +23017,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752979</v>
+        <v>752771</v>
       </c>
       <c r="R211" t="n">
-        <v>7092382</v>
+        <v>7092668</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23053,11 +23053,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23084,10 +23079,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934798</v>
+        <v>119934758</v>
       </c>
       <c r="B212" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23100,21 +23095,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23124,10 +23119,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752945</v>
+        <v>752979</v>
       </c>
       <c r="R212" t="n">
-        <v>7092339</v>
+        <v>7092382</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23160,6 +23155,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23504,10 +23504,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934765</v>
+        <v>119934814</v>
       </c>
       <c r="B216" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23516,42 +23516,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752760</v>
+        <v>752764</v>
       </c>
       <c r="R216" t="n">
-        <v>7092524</v>
+        <v>7092560</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23610,10 +23606,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934778</v>
+        <v>119934765</v>
       </c>
       <c r="B217" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23626,34 +23622,38 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752778</v>
+        <v>752760</v>
       </c>
       <c r="R217" t="n">
-        <v>7092476</v>
+        <v>7092524</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23712,10 +23712,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934794</v>
+        <v>119934778</v>
       </c>
       <c r="B218" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23728,38 +23728,34 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752999</v>
+        <v>752778</v>
       </c>
       <c r="R218" t="n">
-        <v>7092455</v>
+        <v>7092476</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23818,10 +23814,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934814</v>
+        <v>119934794</v>
       </c>
       <c r="B219" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23830,38 +23826,42 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752764</v>
+        <v>752999</v>
       </c>
       <c r="R219" t="n">
-        <v>7092560</v>
+        <v>7092455</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24769,10 +24769,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934813</v>
+        <v>119934784</v>
       </c>
       <c r="B228" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24781,38 +24781,42 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752857</v>
+        <v>752891</v>
       </c>
       <c r="R228" t="n">
-        <v>7092672</v>
+        <v>7092445</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24871,7 +24875,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934811</v>
+        <v>119934813</v>
       </c>
       <c r="B229" t="n">
         <v>91858</v>
@@ -24911,10 +24915,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752853</v>
+        <v>752857</v>
       </c>
       <c r="R229" t="n">
-        <v>7092405</v>
+        <v>7092672</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24973,10 +24977,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934784</v>
+        <v>119934811</v>
       </c>
       <c r="B230" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24985,42 +24989,38 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R230" t="n">
-        <v>7092445</v>
+        <v>7092405</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -15518,7 +15518,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119808297</v>
+        <v>119808301</v>
       </c>
       <c r="B141" t="n">
         <v>91902</v>
@@ -15558,10 +15558,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>752905</v>
+        <v>752896</v>
       </c>
       <c r="R141" t="n">
-        <v>7092298</v>
+        <v>7092397</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15630,10 +15630,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119808308</v>
+        <v>119808300</v>
       </c>
       <c r="B142" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15646,21 +15646,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15670,10 +15670,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>752743</v>
+        <v>752943</v>
       </c>
       <c r="R142" t="n">
-        <v>7092343</v>
+        <v>7092394</v>
       </c>
       <c r="S142" t="n">
         <v>25</v>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15742,10 +15742,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119808299</v>
+        <v>119808311</v>
       </c>
       <c r="B143" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15758,21 +15758,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15782,10 +15782,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>752962</v>
+        <v>752771</v>
       </c>
       <c r="R143" t="n">
-        <v>7092343</v>
+        <v>7092333</v>
       </c>
       <c r="S143" t="n">
         <v>25</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15854,10 +15854,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119808293</v>
+        <v>119808307</v>
       </c>
       <c r="B144" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15870,21 +15870,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15894,10 +15894,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752820</v>
+        <v>752764</v>
       </c>
       <c r="R144" t="n">
-        <v>7092239</v>
+        <v>7092409</v>
       </c>
       <c r="S144" t="n">
         <v>25</v>
@@ -15929,7 +15929,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -15939,7 +15939,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15966,7 +15966,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119808309</v>
+        <v>119808297</v>
       </c>
       <c r="B145" t="n">
         <v>91902</v>
@@ -16006,10 +16006,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752727</v>
+        <v>752905</v>
       </c>
       <c r="R145" t="n">
-        <v>7092321</v>
+        <v>7092298</v>
       </c>
       <c r="S145" t="n">
         <v>25</v>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16190,7 +16190,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119808306</v>
+        <v>119808314</v>
       </c>
       <c r="B147" t="n">
         <v>91902</v>
@@ -16230,10 +16230,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752764</v>
+        <v>752795</v>
       </c>
       <c r="R147" t="n">
-        <v>7092409</v>
+        <v>7092304</v>
       </c>
       <c r="S147" t="n">
         <v>25</v>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16302,10 +16302,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119808292</v>
+        <v>119808306</v>
       </c>
       <c r="B148" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -16318,21 +16318,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16342,10 +16342,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752837</v>
+        <v>752764</v>
       </c>
       <c r="R148" t="n">
-        <v>7092228</v>
+        <v>7092409</v>
       </c>
       <c r="S148" t="n">
         <v>25</v>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16414,10 +16414,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119808302</v>
+        <v>119808298</v>
       </c>
       <c r="B149" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -16426,25 +16426,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16454,10 +16454,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752841</v>
+        <v>752922</v>
       </c>
       <c r="R149" t="n">
-        <v>7092401</v>
+        <v>7092310</v>
       </c>
       <c r="S149" t="n">
         <v>25</v>
@@ -16489,7 +16489,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16526,10 +16526,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119808313</v>
+        <v>119808299</v>
       </c>
       <c r="B150" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16538,25 +16538,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16566,10 +16566,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752808</v>
+        <v>752962</v>
       </c>
       <c r="R150" t="n">
-        <v>7092316</v>
+        <v>7092343</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16638,10 +16638,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119808303</v>
+        <v>119808308</v>
       </c>
       <c r="B151" t="n">
-        <v>91481</v>
+        <v>91902</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16654,21 +16654,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16678,10 +16678,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752812</v>
+        <v>752743</v>
       </c>
       <c r="R151" t="n">
-        <v>7092433</v>
+        <v>7092343</v>
       </c>
       <c r="S151" t="n">
         <v>25</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16750,10 +16750,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119808298</v>
+        <v>119808296</v>
       </c>
       <c r="B152" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16762,25 +16762,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16790,10 +16790,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752922</v>
+        <v>752902</v>
       </c>
       <c r="R152" t="n">
-        <v>7092310</v>
+        <v>7092285</v>
       </c>
       <c r="S152" t="n">
         <v>25</v>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16862,7 +16862,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808295</v>
+        <v>119808309</v>
       </c>
       <c r="B153" t="n">
         <v>91902</v>
@@ -16902,10 +16902,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752872</v>
+        <v>752727</v>
       </c>
       <c r="R153" t="n">
-        <v>7092301</v>
+        <v>7092321</v>
       </c>
       <c r="S153" t="n">
         <v>25</v>
@@ -16937,7 +16937,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16974,10 +16974,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808311</v>
+        <v>119808305</v>
       </c>
       <c r="B154" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16986,25 +16986,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17014,10 +17014,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752771</v>
+        <v>752740</v>
       </c>
       <c r="R154" t="n">
-        <v>7092333</v>
+        <v>7092467</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17059,7 +17059,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17086,10 +17086,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808294</v>
+        <v>119808304</v>
       </c>
       <c r="B155" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -17098,25 +17098,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17126,10 +17126,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752867</v>
+        <v>752773</v>
       </c>
       <c r="R155" t="n">
-        <v>7092294</v>
+        <v>7092434</v>
       </c>
       <c r="S155" t="n">
         <v>25</v>
@@ -17161,7 +17161,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17198,7 +17198,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119808296</v>
+        <v>119808294</v>
       </c>
       <c r="B156" t="n">
         <v>91858</v>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752902</v>
+        <v>752867</v>
       </c>
       <c r="R156" t="n">
-        <v>7092285</v>
+        <v>7092294</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17310,10 +17310,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119808307</v>
+        <v>119808302</v>
       </c>
       <c r="B157" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17326,21 +17326,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17350,10 +17350,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752764</v>
+        <v>752841</v>
       </c>
       <c r="R157" t="n">
-        <v>7092409</v>
+        <v>7092401</v>
       </c>
       <c r="S157" t="n">
         <v>25</v>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17422,7 +17422,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119808301</v>
+        <v>119808295</v>
       </c>
       <c r="B158" t="n">
         <v>91902</v>
@@ -17462,10 +17462,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752896</v>
+        <v>752872</v>
       </c>
       <c r="R158" t="n">
-        <v>7092397</v>
+        <v>7092301</v>
       </c>
       <c r="S158" t="n">
         <v>25</v>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17534,10 +17534,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119808300</v>
+        <v>119808313</v>
       </c>
       <c r="B159" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17550,21 +17550,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17574,10 +17574,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752943</v>
+        <v>752808</v>
       </c>
       <c r="R159" t="n">
-        <v>7092394</v>
+        <v>7092316</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -17609,7 +17609,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17646,10 +17646,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808305</v>
+        <v>119808293</v>
       </c>
       <c r="B160" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17658,25 +17658,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17686,10 +17686,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752740</v>
+        <v>752820</v>
       </c>
       <c r="R160" t="n">
-        <v>7092467</v>
+        <v>7092239</v>
       </c>
       <c r="S160" t="n">
         <v>25</v>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17758,10 +17758,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808304</v>
+        <v>119808292</v>
       </c>
       <c r="B161" t="n">
-        <v>89292</v>
+        <v>91852</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17770,25 +17770,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17798,10 +17798,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752773</v>
+        <v>752837</v>
       </c>
       <c r="R161" t="n">
-        <v>7092434</v>
+        <v>7092228</v>
       </c>
       <c r="S161" t="n">
         <v>25</v>
@@ -17833,7 +17833,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17843,7 +17843,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17870,10 +17870,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119808314</v>
+        <v>119808303</v>
       </c>
       <c r="B162" t="n">
-        <v>91902</v>
+        <v>91481</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17886,21 +17886,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17910,10 +17910,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>752795</v>
+        <v>752812</v>
       </c>
       <c r="R162" t="n">
-        <v>7092304</v>
+        <v>7092433</v>
       </c>
       <c r="S162" t="n">
         <v>25</v>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18084,10 +18084,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119892118</v>
+        <v>119893423</v>
       </c>
       <c r="B164" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18096,38 +18096,38 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752838</v>
+        <v>752740</v>
       </c>
       <c r="R164" t="n">
-        <v>7092399</v>
+        <v>7092396</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18186,10 +18186,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119893208</v>
+        <v>119891959</v>
       </c>
       <c r="B165" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18198,25 +18198,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18226,10 +18226,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752928</v>
+        <v>752740</v>
       </c>
       <c r="R165" t="n">
-        <v>7092309</v>
+        <v>7092396</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18288,10 +18288,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119797563</v>
+        <v>119893016</v>
       </c>
       <c r="B166" t="n">
-        <v>91862</v>
+        <v>91844</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18300,45 +18300,38 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+          <t>(Schmidt : Fr.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752807</v>
+        <v>752901</v>
       </c>
       <c r="R166" t="n">
-        <v>7092367</v>
+        <v>7092374</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18365,17 +18358,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18384,26 +18372,25 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119893329</v>
+        <v>119893208</v>
       </c>
       <c r="B167" t="n">
         <v>91902</v>
@@ -18443,10 +18430,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752893</v>
+        <v>752928</v>
       </c>
       <c r="R167" t="n">
-        <v>7092272</v>
+        <v>7092309</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18505,10 +18492,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119893348</v>
+        <v>119892909</v>
       </c>
       <c r="B168" t="n">
-        <v>91901</v>
+        <v>91844</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18521,21 +18508,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18545,10 +18532,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752893</v>
+        <v>752854</v>
       </c>
       <c r="R168" t="n">
-        <v>7092272</v>
+        <v>7092368</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18607,10 +18594,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119892875</v>
+        <v>119891991</v>
       </c>
       <c r="B169" t="n">
-        <v>88170</v>
+        <v>91902</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18623,21 +18610,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4962</v>
+        <v>5449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18647,10 +18634,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752854</v>
+        <v>752740</v>
       </c>
       <c r="R169" t="n">
-        <v>7092368</v>
+        <v>7092396</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18709,10 +18696,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119893016</v>
+        <v>119893626</v>
       </c>
       <c r="B170" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18725,21 +18712,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18749,10 +18736,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752901</v>
+        <v>752767</v>
       </c>
       <c r="R170" t="n">
-        <v>7092374</v>
+        <v>7092396</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18811,10 +18798,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119893626</v>
+        <v>119797563</v>
       </c>
       <c r="B171" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18823,38 +18810,45 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752767</v>
+        <v>752807</v>
       </c>
       <c r="R171" t="n">
-        <v>7092396</v>
+        <v>7092367</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18881,12 +18875,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18895,28 +18894,29 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893430</v>
+        <v>119893466</v>
       </c>
       <c r="B172" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18929,21 +18929,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18953,10 +18953,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752897</v>
+        <v>752823</v>
       </c>
       <c r="R172" t="n">
-        <v>7092235</v>
+        <v>7092228</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19015,10 +19015,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119893537</v>
+        <v>119893329</v>
       </c>
       <c r="B173" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19031,21 +19031,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752759</v>
+        <v>752893</v>
       </c>
       <c r="R173" t="n">
-        <v>7092324</v>
+        <v>7092272</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19117,10 +19117,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119891959</v>
+        <v>119893473</v>
       </c>
       <c r="B174" t="n">
-        <v>91870</v>
+        <v>91902</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19129,25 +19129,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4366</v>
+        <v>5449</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19157,10 +19157,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752740</v>
+        <v>752827</v>
       </c>
       <c r="R174" t="n">
-        <v>7092396</v>
+        <v>7092232</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19321,10 +19321,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119892909</v>
+        <v>119893537</v>
       </c>
       <c r="B176" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19337,21 +19337,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752854</v>
+        <v>752759</v>
       </c>
       <c r="R176" t="n">
-        <v>7092368</v>
+        <v>7092324</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19423,7 +19423,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119893473</v>
+        <v>119893483</v>
       </c>
       <c r="B177" t="n">
         <v>91902</v>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752827</v>
+        <v>752795</v>
       </c>
       <c r="R177" t="n">
-        <v>7092232</v>
+        <v>7092265</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19729,7 +19729,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119893225</v>
+        <v>119892970</v>
       </c>
       <c r="B180" t="n">
         <v>91902</v>
@@ -19769,10 +19769,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752927</v>
+        <v>752853</v>
       </c>
       <c r="R180" t="n">
-        <v>7092298</v>
+        <v>7092386</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19831,10 +19831,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119893423</v>
+        <v>119892875</v>
       </c>
       <c r="B181" t="n">
-        <v>91874</v>
+        <v>88170</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19847,34 +19847,34 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>2059</v>
+        <v>4962</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752740</v>
+        <v>752854</v>
       </c>
       <c r="R181" t="n">
-        <v>7092396</v>
+        <v>7092368</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19933,7 +19933,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119893483</v>
+        <v>119893225</v>
       </c>
       <c r="B182" t="n">
         <v>91902</v>
@@ -19973,10 +19973,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752795</v>
+        <v>752927</v>
       </c>
       <c r="R182" t="n">
-        <v>7092265</v>
+        <v>7092298</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20035,7 +20035,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119891991</v>
+        <v>119893430</v>
       </c>
       <c r="B183" t="n">
         <v>91902</v>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752740</v>
+        <v>752897</v>
       </c>
       <c r="R183" t="n">
-        <v>7092396</v>
+        <v>7092235</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119893466</v>
+        <v>119893348</v>
       </c>
       <c r="B184" t="n">
-        <v>91852</v>
+        <v>91901</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20153,21 +20153,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752823</v>
+        <v>752893</v>
       </c>
       <c r="R184" t="n">
-        <v>7092228</v>
+        <v>7092272</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20239,10 +20239,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119892970</v>
+        <v>119892118</v>
       </c>
       <c r="B185" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20251,25 +20251,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752853</v>
+        <v>752838</v>
       </c>
       <c r="R185" t="n">
-        <v>7092386</v>
+        <v>7092399</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934818</v>
+        <v>119934775</v>
       </c>
       <c r="B186" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,38 +20353,42 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>753030</v>
+        <v>752777</v>
       </c>
       <c r="R186" t="n">
-        <v>7092403</v>
+        <v>7092577</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20443,10 +20447,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934797</v>
+        <v>119934809</v>
       </c>
       <c r="B187" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20455,38 +20459,42 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752806</v>
+        <v>752817</v>
       </c>
       <c r="R187" t="n">
-        <v>7092716</v>
+        <v>7092378</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20545,10 +20553,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934775</v>
+        <v>119934765</v>
       </c>
       <c r="B188" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20561,26 +20569,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20589,10 +20597,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752777</v>
+        <v>752760</v>
       </c>
       <c r="R188" t="n">
-        <v>7092577</v>
+        <v>7092524</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20651,10 +20659,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934815</v>
+        <v>119934768</v>
       </c>
       <c r="B189" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20663,25 +20671,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20691,10 +20699,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752779</v>
+        <v>752771</v>
       </c>
       <c r="R189" t="n">
-        <v>7092482</v>
+        <v>7092668</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20753,10 +20761,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934781</v>
+        <v>119934778</v>
       </c>
       <c r="B190" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20769,38 +20777,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752766</v>
+        <v>752778</v>
       </c>
       <c r="R190" t="n">
-        <v>7092643</v>
+        <v>7092476</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20833,11 +20837,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20864,10 +20863,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934812</v>
+        <v>119934792</v>
       </c>
       <c r="B191" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20876,38 +20875,42 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752796</v>
+        <v>752867</v>
       </c>
       <c r="R191" t="n">
-        <v>7092694</v>
+        <v>7092495</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20966,10 +20969,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934783</v>
+        <v>119934817</v>
       </c>
       <c r="B192" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20978,42 +20981,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752771</v>
+        <v>752778</v>
       </c>
       <c r="R192" t="n">
-        <v>7092674</v>
+        <v>7092478</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21046,11 +21045,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21077,10 +21071,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934766</v>
+        <v>119934821</v>
       </c>
       <c r="B193" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21093,26 +21087,26 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21121,10 +21115,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752751</v>
+        <v>752994</v>
       </c>
       <c r="R193" t="n">
-        <v>7092507</v>
+        <v>7092431</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21183,10 +21177,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934774</v>
+        <v>119934819</v>
       </c>
       <c r="B194" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21195,42 +21189,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752891</v>
+        <v>752979</v>
       </c>
       <c r="R194" t="n">
-        <v>7092444</v>
+        <v>7092382</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21289,10 +21279,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934777</v>
+        <v>119934767</v>
       </c>
       <c r="B195" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21305,21 +21295,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21329,10 +21319,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752809</v>
+        <v>752720</v>
       </c>
       <c r="R195" t="n">
-        <v>7092467</v>
+        <v>7092493</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21391,10 +21381,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934810</v>
+        <v>119934774</v>
       </c>
       <c r="B196" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21403,30 +21393,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21435,10 +21425,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752803</v>
+        <v>752891</v>
       </c>
       <c r="R196" t="n">
-        <v>7092670</v>
+        <v>7092444</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21497,10 +21487,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934752</v>
+        <v>119934818</v>
       </c>
       <c r="B197" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21509,25 +21499,25 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21537,10 +21527,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752794</v>
+        <v>753030</v>
       </c>
       <c r="R197" t="n">
-        <v>7092570</v>
+        <v>7092403</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21573,11 +21563,6 @@
       <c r="AA197" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21604,10 +21589,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934806</v>
+        <v>119934783</v>
       </c>
       <c r="B198" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21616,30 +21601,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21648,10 +21633,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752816</v>
+        <v>752771</v>
       </c>
       <c r="R198" t="n">
-        <v>7092714</v>
+        <v>7092674</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21684,6 +21669,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21710,10 +21700,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934771</v>
+        <v>119934806</v>
       </c>
       <c r="B199" t="n">
-        <v>91862</v>
+        <v>89269</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21726,34 +21716,38 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4365</v>
+        <v>6276</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752765</v>
+        <v>752816</v>
       </c>
       <c r="R199" t="n">
-        <v>7092632</v>
+        <v>7092714</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21786,11 +21780,6 @@
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21817,10 +21806,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934808</v>
+        <v>119934810</v>
       </c>
       <c r="B200" t="n">
-        <v>89269</v>
+        <v>91858</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21829,30 +21818,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -21861,10 +21850,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752819</v>
+        <v>752803</v>
       </c>
       <c r="R200" t="n">
-        <v>7092515</v>
+        <v>7092670</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21923,7 +21912,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934756</v>
+        <v>119934752</v>
       </c>
       <c r="B201" t="n">
         <v>89292</v>
@@ -21956,21 +21945,17 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752783</v>
+        <v>752794</v>
       </c>
       <c r="R201" t="n">
-        <v>7092657</v>
+        <v>7092570</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22003,6 +21988,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22029,10 +22019,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934823</v>
+        <v>119934813</v>
       </c>
       <c r="B202" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22041,42 +22031,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752959</v>
+        <v>752857</v>
       </c>
       <c r="R202" t="n">
-        <v>7092467</v>
+        <v>7092672</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22135,10 +22121,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934773</v>
+        <v>119934781</v>
       </c>
       <c r="B203" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22147,30 +22133,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22179,10 +22165,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752853</v>
+        <v>752766</v>
       </c>
       <c r="R203" t="n">
-        <v>7092405</v>
+        <v>7092643</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22219,7 +22205,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22246,10 +22232,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934767</v>
+        <v>119934814</v>
       </c>
       <c r="B204" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22258,25 +22244,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22286,10 +22272,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752720</v>
+        <v>752764</v>
       </c>
       <c r="R204" t="n">
-        <v>7092493</v>
+        <v>7092560</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22348,7 +22334,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934762</v>
+        <v>119934763</v>
       </c>
       <c r="B205" t="n">
         <v>91902</v>
@@ -22392,10 +22378,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752732</v>
+        <v>752788</v>
       </c>
       <c r="R205" t="n">
-        <v>7092502</v>
+        <v>7092548</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22454,10 +22440,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934772</v>
+        <v>119934785</v>
       </c>
       <c r="B206" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22466,38 +22452,42 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752757</v>
+        <v>752721</v>
       </c>
       <c r="R206" t="n">
-        <v>7092617</v>
+        <v>7092493</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22530,11 +22520,6 @@
       <c r="AA206" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22561,10 +22546,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934755</v>
+        <v>119934808</v>
       </c>
       <c r="B207" t="n">
-        <v>91481</v>
+        <v>89269</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22573,38 +22558,42 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4745</v>
+        <v>6276</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752777</v>
+        <v>752819</v>
       </c>
       <c r="R207" t="n">
-        <v>7092472</v>
+        <v>7092515</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22663,10 +22652,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934799</v>
+        <v>119934790</v>
       </c>
       <c r="B208" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22679,21 +22668,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -22707,10 +22696,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752754</v>
+        <v>752853</v>
       </c>
       <c r="R208" t="n">
-        <v>7092559</v>
+        <v>7092405</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22769,10 +22758,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934761</v>
+        <v>119934787</v>
       </c>
       <c r="B209" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22785,26 +22774,26 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -22813,10 +22802,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752772</v>
+        <v>752738</v>
       </c>
       <c r="R209" t="n">
-        <v>7092487</v>
+        <v>7092548</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22849,6 +22838,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22875,10 +22869,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934798</v>
+        <v>119934755</v>
       </c>
       <c r="B210" t="n">
-        <v>91850</v>
+        <v>91481</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22891,21 +22885,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22915,10 +22909,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752945</v>
+        <v>752777</v>
       </c>
       <c r="R210" t="n">
-        <v>7092339</v>
+        <v>7092472</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22977,10 +22971,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934768</v>
+        <v>119934756</v>
       </c>
       <c r="B211" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22989,38 +22983,42 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752771</v>
+        <v>752783</v>
       </c>
       <c r="R211" t="n">
-        <v>7092668</v>
+        <v>7092657</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23079,10 +23077,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934758</v>
+        <v>119934776</v>
       </c>
       <c r="B212" t="n">
-        <v>91901</v>
+        <v>91874</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23095,34 +23093,38 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752979</v>
+        <v>752759</v>
       </c>
       <c r="R212" t="n">
-        <v>7092382</v>
+        <v>7092525</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23155,11 +23157,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23292,10 +23289,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934760</v>
+        <v>119934797</v>
       </c>
       <c r="B214" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23308,38 +23305,34 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752896</v>
+        <v>752806</v>
       </c>
       <c r="R214" t="n">
-        <v>7092456</v>
+        <v>7092716</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23398,10 +23391,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934763</v>
+        <v>119934782</v>
       </c>
       <c r="B215" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23414,26 +23407,26 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -23442,10 +23435,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752788</v>
+        <v>752743</v>
       </c>
       <c r="R215" t="n">
-        <v>7092548</v>
+        <v>7092544</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23504,10 +23497,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934814</v>
+        <v>119934761</v>
       </c>
       <c r="B216" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23516,38 +23509,42 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752764</v>
+        <v>752772</v>
       </c>
       <c r="R216" t="n">
-        <v>7092560</v>
+        <v>7092487</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23606,7 +23603,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934765</v>
+        <v>119934760</v>
       </c>
       <c r="B217" t="n">
         <v>91902</v>
@@ -23641,7 +23638,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -23650,10 +23647,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752760</v>
+        <v>752896</v>
       </c>
       <c r="R217" t="n">
-        <v>7092524</v>
+        <v>7092456</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23712,10 +23709,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934778</v>
+        <v>119934791</v>
       </c>
       <c r="B218" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23728,34 +23725,38 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752778</v>
+        <v>752777</v>
       </c>
       <c r="R218" t="n">
-        <v>7092476</v>
+        <v>7092488</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23814,10 +23815,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934794</v>
+        <v>119934799</v>
       </c>
       <c r="B219" t="n">
-        <v>91850</v>
+        <v>91881</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23830,21 +23831,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4361</v>
+        <v>5966</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -23858,10 +23859,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752999</v>
+        <v>752754</v>
       </c>
       <c r="R219" t="n">
-        <v>7092455</v>
+        <v>7092559</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23920,10 +23921,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934776</v>
+        <v>119934748</v>
       </c>
       <c r="B220" t="n">
-        <v>91874</v>
+        <v>89650</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23936,38 +23937,34 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752759</v>
+        <v>752762</v>
       </c>
       <c r="R220" t="n">
-        <v>7092525</v>
+        <v>7092586</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24002,6 +23999,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
@@ -24010,6 +24012,21 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -24026,10 +24043,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934785</v>
+        <v>119934758</v>
       </c>
       <c r="B221" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24042,38 +24059,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752721</v>
+        <v>752979</v>
       </c>
       <c r="R221" t="n">
-        <v>7092493</v>
+        <v>7092382</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24106,6 +24119,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24132,7 +24150,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934790</v>
+        <v>119934788</v>
       </c>
       <c r="B222" t="n">
         <v>91850</v>
@@ -24176,10 +24194,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752853</v>
+        <v>752781</v>
       </c>
       <c r="R222" t="n">
-        <v>7092405</v>
+        <v>7092640</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24238,10 +24256,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934764</v>
+        <v>119934796</v>
       </c>
       <c r="B223" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24254,38 +24272,34 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752759</v>
+        <v>752805</v>
       </c>
       <c r="R223" t="n">
-        <v>7092478</v>
+        <v>7092505</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24344,7 +24358,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934792</v>
+        <v>119934795</v>
       </c>
       <c r="B224" t="n">
         <v>91850</v>
@@ -24379,7 +24393,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24388,10 +24402,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752867</v>
+        <v>752996</v>
       </c>
       <c r="R224" t="n">
-        <v>7092495</v>
+        <v>7092398</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24424,6 +24438,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24450,10 +24469,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934796</v>
+        <v>119934766</v>
       </c>
       <c r="B225" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24466,34 +24485,38 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752805</v>
+        <v>752751</v>
       </c>
       <c r="R225" t="n">
-        <v>7092505</v>
+        <v>7092507</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24552,10 +24575,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934788</v>
+        <v>119934759</v>
       </c>
       <c r="B226" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24568,38 +24591,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752781</v>
+        <v>752845</v>
       </c>
       <c r="R226" t="n">
-        <v>7092640</v>
+        <v>7092505</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24632,6 +24651,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24658,10 +24682,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934787</v>
+        <v>119934823</v>
       </c>
       <c r="B227" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24674,26 +24698,26 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24702,10 +24726,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752738</v>
+        <v>752959</v>
       </c>
       <c r="R227" t="n">
-        <v>7092548</v>
+        <v>7092467</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24738,11 +24762,6 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24769,10 +24788,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934784</v>
+        <v>119934771</v>
       </c>
       <c r="B228" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24781,42 +24800,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752891</v>
+        <v>752765</v>
       </c>
       <c r="R228" t="n">
-        <v>7092445</v>
+        <v>7092632</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24849,6 +24864,11 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24875,10 +24895,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934813</v>
+        <v>119934798</v>
       </c>
       <c r="B229" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24887,25 +24907,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -24915,10 +24935,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752857</v>
+        <v>752945</v>
       </c>
       <c r="R229" t="n">
-        <v>7092672</v>
+        <v>7092339</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24977,10 +24997,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934811</v>
+        <v>119934753</v>
       </c>
       <c r="B230" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -24989,25 +25009,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25017,10 +25037,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>752853</v>
+        <v>752888</v>
       </c>
       <c r="R230" t="n">
-        <v>7092405</v>
+        <v>7092677</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25079,10 +25099,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934753</v>
+        <v>119934784</v>
       </c>
       <c r="B231" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25091,38 +25111,42 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752888</v>
+        <v>752891</v>
       </c>
       <c r="R231" t="n">
-        <v>7092677</v>
+        <v>7092445</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25181,10 +25205,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934789</v>
+        <v>119934815</v>
       </c>
       <c r="B232" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25193,42 +25217,38 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752803</v>
+        <v>752779</v>
       </c>
       <c r="R232" t="n">
-        <v>7092378</v>
+        <v>7092482</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25287,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934821</v>
+        <v>119934764</v>
       </c>
       <c r="B233" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25303,21 +25323,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -25331,10 +25351,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752994</v>
+        <v>752759</v>
       </c>
       <c r="R233" t="n">
-        <v>7092431</v>
+        <v>7092478</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25393,10 +25413,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934791</v>
+        <v>119934811</v>
       </c>
       <c r="B234" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25405,42 +25425,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752777</v>
+        <v>752853</v>
       </c>
       <c r="R234" t="n">
-        <v>7092488</v>
+        <v>7092405</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25499,10 +25515,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934817</v>
+        <v>119934794</v>
       </c>
       <c r="B235" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25511,38 +25527,42 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752778</v>
+        <v>752999</v>
       </c>
       <c r="R235" t="n">
-        <v>7092478</v>
+        <v>7092455</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25601,10 +25621,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934819</v>
+        <v>119934762</v>
       </c>
       <c r="B236" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25613,38 +25633,42 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752979</v>
+        <v>752732</v>
       </c>
       <c r="R236" t="n">
-        <v>7092382</v>
+        <v>7092502</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25703,10 +25727,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934759</v>
+        <v>119934777</v>
       </c>
       <c r="B237" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25719,21 +25743,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -25743,10 +25767,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752845</v>
+        <v>752809</v>
       </c>
       <c r="R237" t="n">
-        <v>7092505</v>
+        <v>7092467</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25779,11 +25803,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25810,7 +25829,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934809</v>
+        <v>119934812</v>
       </c>
       <c r="B238" t="n">
         <v>91858</v>
@@ -25843,21 +25862,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752817</v>
+        <v>752796</v>
       </c>
       <c r="R238" t="n">
-        <v>7092378</v>
+        <v>7092694</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25916,10 +25931,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934748</v>
+        <v>119934772</v>
       </c>
       <c r="B239" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25928,25 +25943,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25956,10 +25971,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752762</v>
+        <v>752757</v>
       </c>
       <c r="R239" t="n">
-        <v>7092586</v>
+        <v>7092617</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -25996,7 +26011,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Undersida knäckt talltopp i mossa</t>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26007,21 +26022,6 @@
       </c>
       <c r="AG239" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
@@ -26038,7 +26038,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934795</v>
+        <v>119934789</v>
       </c>
       <c r="B240" t="n">
         <v>91850</v>
@@ -26073,7 +26073,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26082,10 +26082,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752996</v>
+        <v>752803</v>
       </c>
       <c r="R240" t="n">
-        <v>7092398</v>
+        <v>7092378</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26118,11 +26118,6 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26149,10 +26144,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934782</v>
+        <v>119934773</v>
       </c>
       <c r="B241" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26161,25 +26156,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -26193,10 +26188,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752743</v>
+        <v>752853</v>
       </c>
       <c r="R241" t="n">
-        <v>7092544</v>
+        <v>7092405</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26229,6 +26224,11 @@
       <c r="AA241" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC241" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD241" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -19525,10 +19525,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119893301</v>
+        <v>119893175</v>
       </c>
       <c r="B178" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19541,21 +19541,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752892</v>
+        <v>752982</v>
       </c>
       <c r="R178" t="n">
-        <v>7092280</v>
+        <v>7092371</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19627,7 +19627,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119893175</v>
+        <v>119892970</v>
       </c>
       <c r="B179" t="n">
         <v>91902</v>
@@ -19667,10 +19667,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752982</v>
+        <v>752853</v>
       </c>
       <c r="R179" t="n">
-        <v>7092371</v>
+        <v>7092386</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19729,10 +19729,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119892970</v>
+        <v>119893301</v>
       </c>
       <c r="B180" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19745,21 +19745,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19769,10 +19769,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752853</v>
+        <v>752892</v>
       </c>
       <c r="R180" t="n">
-        <v>7092386</v>
+        <v>7092280</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -22334,10 +22334,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934763</v>
+        <v>119934785</v>
       </c>
       <c r="B205" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22350,26 +22350,26 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -22378,10 +22378,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752788</v>
+        <v>752721</v>
       </c>
       <c r="R205" t="n">
-        <v>7092548</v>
+        <v>7092493</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22440,10 +22440,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934785</v>
+        <v>119934763</v>
       </c>
       <c r="B206" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22456,26 +22456,26 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -22484,10 +22484,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752721</v>
+        <v>752788</v>
       </c>
       <c r="R206" t="n">
-        <v>7092493</v>
+        <v>7092548</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22546,10 +22546,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934808</v>
+        <v>119934790</v>
       </c>
       <c r="B207" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22558,25 +22558,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -22590,10 +22590,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752819</v>
+        <v>752853</v>
       </c>
       <c r="R207" t="n">
-        <v>7092515</v>
+        <v>7092405</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22652,7 +22652,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934790</v>
+        <v>119934787</v>
       </c>
       <c r="B208" t="n">
         <v>91850</v>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -22696,10 +22696,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752853</v>
+        <v>752738</v>
       </c>
       <c r="R208" t="n">
-        <v>7092405</v>
+        <v>7092548</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22732,6 +22732,11 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22758,10 +22763,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934787</v>
+        <v>119934808</v>
       </c>
       <c r="B209" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22770,30 +22775,30 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -22802,10 +22807,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752738</v>
+        <v>752819</v>
       </c>
       <c r="R209" t="n">
-        <v>7092548</v>
+        <v>7092515</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22838,11 +22843,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24150,7 +24150,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934788</v>
+        <v>119934796</v>
       </c>
       <c r="B222" t="n">
         <v>91850</v>
@@ -24183,21 +24183,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752781</v>
+        <v>752805</v>
       </c>
       <c r="R222" t="n">
-        <v>7092640</v>
+        <v>7092505</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24256,7 +24252,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934796</v>
+        <v>119934795</v>
       </c>
       <c r="B223" t="n">
         <v>91850</v>
@@ -24289,17 +24285,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752805</v>
+        <v>752996</v>
       </c>
       <c r="R223" t="n">
-        <v>7092505</v>
+        <v>7092398</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24332,6 +24332,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24358,7 +24363,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934795</v>
+        <v>119934788</v>
       </c>
       <c r="B224" t="n">
         <v>91850</v>
@@ -24393,7 +24398,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24402,10 +24407,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752996</v>
+        <v>752781</v>
       </c>
       <c r="R224" t="n">
-        <v>7092398</v>
+        <v>7092640</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24438,11 +24443,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24469,10 +24469,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934766</v>
+        <v>119934823</v>
       </c>
       <c r="B225" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24485,26 +24485,26 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24513,10 +24513,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752751</v>
+        <v>752959</v>
       </c>
       <c r="R225" t="n">
-        <v>7092507</v>
+        <v>7092467</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24575,7 +24575,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934759</v>
+        <v>119934766</v>
       </c>
       <c r="B226" t="n">
         <v>91902</v>
@@ -24608,17 +24608,21 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752845</v>
+        <v>752751</v>
       </c>
       <c r="R226" t="n">
-        <v>7092505</v>
+        <v>7092507</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24651,11 +24655,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24682,10 +24681,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934823</v>
+        <v>119934759</v>
       </c>
       <c r="B227" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24698,38 +24697,34 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752959</v>
+        <v>752845</v>
       </c>
       <c r="R227" t="n">
-        <v>7092467</v>
+        <v>7092505</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24762,6 +24757,11 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD227" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -17982,10 +17982,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119891898</v>
+        <v>119893208</v>
       </c>
       <c r="B163" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17994,38 +17994,38 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>752740</v>
+        <v>752928</v>
       </c>
       <c r="R163" t="n">
-        <v>7092396</v>
+        <v>7092309</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18084,10 +18084,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119893423</v>
+        <v>119893348</v>
       </c>
       <c r="B164" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18100,34 +18100,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752740</v>
+        <v>752893</v>
       </c>
       <c r="R164" t="n">
-        <v>7092396</v>
+        <v>7092272</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18186,10 +18186,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119891959</v>
+        <v>119893598</v>
       </c>
       <c r="B165" t="n">
-        <v>91870</v>
+        <v>89292</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18198,25 +18198,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4366</v>
+        <v>6286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18226,10 +18226,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752740</v>
+        <v>752767</v>
       </c>
       <c r="R165" t="n">
-        <v>7092396</v>
+        <v>7092395</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18288,10 +18288,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119893016</v>
+        <v>119893430</v>
       </c>
       <c r="B166" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18304,21 +18304,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752901</v>
+        <v>752897</v>
       </c>
       <c r="R166" t="n">
-        <v>7092374</v>
+        <v>7092235</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18390,10 +18390,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119893208</v>
+        <v>119893466</v>
       </c>
       <c r="B167" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18406,21 +18406,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18430,10 +18430,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752928</v>
+        <v>752823</v>
       </c>
       <c r="R167" t="n">
-        <v>7092309</v>
+        <v>7092228</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18492,10 +18492,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119892909</v>
+        <v>119893225</v>
       </c>
       <c r="B168" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18508,21 +18508,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18532,10 +18532,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752854</v>
+        <v>752927</v>
       </c>
       <c r="R168" t="n">
-        <v>7092368</v>
+        <v>7092298</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18594,10 +18594,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119891991</v>
+        <v>119893537</v>
       </c>
       <c r="B169" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18610,21 +18610,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18634,10 +18634,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752740</v>
+        <v>752759</v>
       </c>
       <c r="R169" t="n">
-        <v>7092396</v>
+        <v>7092324</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18696,10 +18696,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119893626</v>
+        <v>119797563</v>
       </c>
       <c r="B170" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18708,38 +18708,45 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752767</v>
+        <v>752807</v>
       </c>
       <c r="R170" t="n">
-        <v>7092396</v>
+        <v>7092367</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18766,12 +18773,17 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18780,28 +18792,29 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119797563</v>
+        <v>119893483</v>
       </c>
       <c r="B171" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18810,45 +18823,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752807</v>
+        <v>752795</v>
       </c>
       <c r="R171" t="n">
-        <v>7092367</v>
+        <v>7092265</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18875,17 +18881,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18894,29 +18895,28 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893466</v>
+        <v>119893423</v>
       </c>
       <c r="B172" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18929,34 +18929,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752823</v>
+        <v>752740</v>
       </c>
       <c r="R172" t="n">
-        <v>7092228</v>
+        <v>7092396</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19015,7 +19015,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119893329</v>
+        <v>119893626</v>
       </c>
       <c r="B173" t="n">
         <v>91902</v>
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752893</v>
+        <v>752767</v>
       </c>
       <c r="R173" t="n">
-        <v>7092272</v>
+        <v>7092396</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19117,10 +19117,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119893473</v>
+        <v>119893016</v>
       </c>
       <c r="B174" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19133,21 +19133,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19157,10 +19157,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752827</v>
+        <v>752901</v>
       </c>
       <c r="R174" t="n">
-        <v>7092232</v>
+        <v>7092374</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19219,7 +19219,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119893598</v>
+        <v>119892118</v>
       </c>
       <c r="B175" t="n">
         <v>89292</v>
@@ -19259,10 +19259,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752767</v>
+        <v>752838</v>
       </c>
       <c r="R175" t="n">
-        <v>7092395</v>
+        <v>7092399</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19321,10 +19321,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119893537</v>
+        <v>119893175</v>
       </c>
       <c r="B176" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19337,21 +19337,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752759</v>
+        <v>752982</v>
       </c>
       <c r="R176" t="n">
-        <v>7092324</v>
+        <v>7092371</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19423,7 +19423,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119893483</v>
+        <v>119893329</v>
       </c>
       <c r="B177" t="n">
         <v>91902</v>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752795</v>
+        <v>752893</v>
       </c>
       <c r="R177" t="n">
-        <v>7092265</v>
+        <v>7092272</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19525,7 +19525,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119893175</v>
+        <v>119892970</v>
       </c>
       <c r="B178" t="n">
         <v>91902</v>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752982</v>
+        <v>752853</v>
       </c>
       <c r="R178" t="n">
-        <v>7092371</v>
+        <v>7092386</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19627,10 +19627,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119892970</v>
+        <v>119891898</v>
       </c>
       <c r="B179" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19639,38 +19639,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752853</v>
+        <v>752740</v>
       </c>
       <c r="R179" t="n">
-        <v>7092386</v>
+        <v>7092396</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19729,10 +19729,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119893301</v>
+        <v>119891991</v>
       </c>
       <c r="B180" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19745,21 +19745,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19769,10 +19769,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752892</v>
+        <v>752740</v>
       </c>
       <c r="R180" t="n">
-        <v>7092280</v>
+        <v>7092396</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19831,10 +19831,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119892875</v>
+        <v>119893301</v>
       </c>
       <c r="B181" t="n">
-        <v>88170</v>
+        <v>91850</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19847,21 +19847,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4962</v>
+        <v>4361</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752854</v>
+        <v>752892</v>
       </c>
       <c r="R181" t="n">
-        <v>7092368</v>
+        <v>7092280</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119893225</v>
+        <v>119892875</v>
       </c>
       <c r="B182" t="n">
-        <v>91902</v>
+        <v>88170</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19949,21 +19949,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5449</v>
+        <v>4962</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19973,10 +19973,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752927</v>
+        <v>752854</v>
       </c>
       <c r="R182" t="n">
-        <v>7092298</v>
+        <v>7092368</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20035,10 +20035,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119893430</v>
+        <v>119891959</v>
       </c>
       <c r="B183" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20047,25 +20047,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752897</v>
+        <v>752740</v>
       </c>
       <c r="R183" t="n">
-        <v>7092235</v>
+        <v>7092396</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119893348</v>
+        <v>119892909</v>
       </c>
       <c r="B184" t="n">
-        <v>91901</v>
+        <v>91844</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20153,21 +20153,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5448</v>
+        <v>3100</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752893</v>
+        <v>752854</v>
       </c>
       <c r="R184" t="n">
-        <v>7092272</v>
+        <v>7092368</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20239,10 +20239,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119892118</v>
+        <v>119893473</v>
       </c>
       <c r="B185" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20251,25 +20251,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752838</v>
+        <v>752827</v>
       </c>
       <c r="R185" t="n">
-        <v>7092399</v>
+        <v>7092232</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934775</v>
+        <v>119934811</v>
       </c>
       <c r="B186" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,42 +20353,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752777</v>
+        <v>752853</v>
       </c>
       <c r="R186" t="n">
-        <v>7092577</v>
+        <v>7092405</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20447,10 +20443,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934809</v>
+        <v>119934756</v>
       </c>
       <c r="B187" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20459,30 +20455,30 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -20491,10 +20487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752817</v>
+        <v>752783</v>
       </c>
       <c r="R187" t="n">
-        <v>7092378</v>
+        <v>7092657</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20553,7 +20549,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934765</v>
+        <v>119934762</v>
       </c>
       <c r="B188" t="n">
         <v>91902</v>
@@ -20588,7 +20584,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20597,10 +20593,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752760</v>
+        <v>752732</v>
       </c>
       <c r="R188" t="n">
-        <v>7092524</v>
+        <v>7092502</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20659,10 +20655,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934768</v>
+        <v>119934795</v>
       </c>
       <c r="B189" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20675,34 +20671,38 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752771</v>
+        <v>752996</v>
       </c>
       <c r="R189" t="n">
-        <v>7092668</v>
+        <v>7092398</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20735,6 +20735,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20761,10 +20766,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934778</v>
+        <v>119934796</v>
       </c>
       <c r="B190" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20777,21 +20782,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20801,10 +20806,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752778</v>
+        <v>752805</v>
       </c>
       <c r="R190" t="n">
-        <v>7092476</v>
+        <v>7092505</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20863,7 +20868,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934792</v>
+        <v>119934789</v>
       </c>
       <c r="B191" t="n">
         <v>91850</v>
@@ -20907,10 +20912,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752867</v>
+        <v>752803</v>
       </c>
       <c r="R191" t="n">
-        <v>7092495</v>
+        <v>7092378</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20969,10 +20974,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934817</v>
+        <v>119934772</v>
       </c>
       <c r="B192" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20981,25 +20986,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21009,10 +21014,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752778</v>
+        <v>752757</v>
       </c>
       <c r="R192" t="n">
-        <v>7092478</v>
+        <v>7092617</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21045,6 +21050,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21071,10 +21081,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934821</v>
+        <v>119934798</v>
       </c>
       <c r="B193" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21087,38 +21097,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752994</v>
+        <v>752945</v>
       </c>
       <c r="R193" t="n">
-        <v>7092431</v>
+        <v>7092339</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21177,10 +21183,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934819</v>
+        <v>119934799</v>
       </c>
       <c r="B194" t="n">
-        <v>91858</v>
+        <v>91881</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21189,38 +21195,42 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752979</v>
+        <v>752754</v>
       </c>
       <c r="R194" t="n">
-        <v>7092382</v>
+        <v>7092559</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21279,10 +21289,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934767</v>
+        <v>119934775</v>
       </c>
       <c r="B195" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21295,34 +21305,38 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752720</v>
+        <v>752777</v>
       </c>
       <c r="R195" t="n">
-        <v>7092493</v>
+        <v>7092577</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21381,7 +21395,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934774</v>
+        <v>119934777</v>
       </c>
       <c r="B196" t="n">
         <v>91874</v>
@@ -21414,21 +21428,17 @@
           <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752891</v>
+        <v>752809</v>
       </c>
       <c r="R196" t="n">
-        <v>7092444</v>
+        <v>7092467</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21487,10 +21497,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934818</v>
+        <v>119934761</v>
       </c>
       <c r="B197" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21499,38 +21509,42 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>753030</v>
+        <v>752772</v>
       </c>
       <c r="R197" t="n">
-        <v>7092403</v>
+        <v>7092487</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21589,10 +21603,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934783</v>
+        <v>119934773</v>
       </c>
       <c r="B198" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21601,30 +21615,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21633,10 +21647,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752771</v>
+        <v>752853</v>
       </c>
       <c r="R198" t="n">
-        <v>7092674</v>
+        <v>7092405</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21673,7 +21687,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Invid silverlåga</t>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21700,10 +21714,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934806</v>
+        <v>119934797</v>
       </c>
       <c r="B199" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21712,42 +21726,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752816</v>
+        <v>752806</v>
       </c>
       <c r="R199" t="n">
-        <v>7092714</v>
+        <v>7092716</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21806,7 +21816,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934810</v>
+        <v>119934812</v>
       </c>
       <c r="B200" t="n">
         <v>91858</v>
@@ -21839,21 +21849,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752803</v>
+        <v>752796</v>
       </c>
       <c r="R200" t="n">
-        <v>7092670</v>
+        <v>7092694</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21912,10 +21918,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934752</v>
+        <v>119934819</v>
       </c>
       <c r="B201" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21924,25 +21930,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21952,10 +21958,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752794</v>
+        <v>752979</v>
       </c>
       <c r="R201" t="n">
-        <v>7092570</v>
+        <v>7092382</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21988,11 +21994,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22019,10 +22020,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934813</v>
+        <v>119934782</v>
       </c>
       <c r="B202" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22031,38 +22032,42 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752857</v>
+        <v>752743</v>
       </c>
       <c r="R202" t="n">
-        <v>7092672</v>
+        <v>7092544</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22121,7 +22126,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934781</v>
+        <v>119934783</v>
       </c>
       <c r="B203" t="n">
         <v>91850</v>
@@ -22165,10 +22170,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752766</v>
+        <v>752771</v>
       </c>
       <c r="R203" t="n">
-        <v>7092643</v>
+        <v>7092674</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22205,7 +22210,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22232,10 +22237,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934814</v>
+        <v>119934790</v>
       </c>
       <c r="B204" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22244,38 +22249,42 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752764</v>
+        <v>752853</v>
       </c>
       <c r="R204" t="n">
-        <v>7092560</v>
+        <v>7092405</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22334,10 +22343,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934785</v>
+        <v>119934753</v>
       </c>
       <c r="B205" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22346,42 +22355,38 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752721</v>
+        <v>752888</v>
       </c>
       <c r="R205" t="n">
-        <v>7092493</v>
+        <v>7092677</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22440,7 +22445,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934763</v>
+        <v>119934765</v>
       </c>
       <c r="B206" t="n">
         <v>91902</v>
@@ -22475,7 +22480,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -22484,10 +22489,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752788</v>
+        <v>752760</v>
       </c>
       <c r="R206" t="n">
-        <v>7092548</v>
+        <v>7092524</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22546,10 +22551,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934790</v>
+        <v>119934755</v>
       </c>
       <c r="B207" t="n">
-        <v>91850</v>
+        <v>91481</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22562,38 +22567,34 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752853</v>
+        <v>752777</v>
       </c>
       <c r="R207" t="n">
-        <v>7092405</v>
+        <v>7092472</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22652,7 +22653,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934787</v>
+        <v>119934786</v>
       </c>
       <c r="B208" t="n">
         <v>91850</v>
@@ -22687,7 +22688,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -22696,10 +22697,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752738</v>
+        <v>752833</v>
       </c>
       <c r="R208" t="n">
-        <v>7092548</v>
+        <v>7092510</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22732,11 +22733,6 @@
       <c r="AA208" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22763,10 +22759,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934808</v>
+        <v>119934771</v>
       </c>
       <c r="B209" t="n">
-        <v>89269</v>
+        <v>91862</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22779,38 +22775,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752819</v>
+        <v>752765</v>
       </c>
       <c r="R209" t="n">
-        <v>7092515</v>
+        <v>7092632</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22843,6 +22835,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22869,10 +22866,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934755</v>
+        <v>119934814</v>
       </c>
       <c r="B210" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22881,25 +22878,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -22909,10 +22906,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752777</v>
+        <v>752764</v>
       </c>
       <c r="R210" t="n">
-        <v>7092472</v>
+        <v>7092560</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22971,10 +22968,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934756</v>
+        <v>119934776</v>
       </c>
       <c r="B211" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22983,30 +22980,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23015,10 +23012,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752783</v>
+        <v>752759</v>
       </c>
       <c r="R211" t="n">
-        <v>7092657</v>
+        <v>7092525</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23077,10 +23074,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934776</v>
+        <v>119934758</v>
       </c>
       <c r="B212" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23093,38 +23090,34 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752759</v>
+        <v>752979</v>
       </c>
       <c r="R212" t="n">
-        <v>7092525</v>
+        <v>7092382</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23157,6 +23150,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23183,10 +23181,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934786</v>
+        <v>119934809</v>
       </c>
       <c r="B213" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23195,30 +23193,30 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23227,10 +23225,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752833</v>
+        <v>752817</v>
       </c>
       <c r="R213" t="n">
-        <v>7092510</v>
+        <v>7092378</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23289,7 +23287,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934797</v>
+        <v>119934784</v>
       </c>
       <c r="B214" t="n">
         <v>91850</v>
@@ -23322,17 +23320,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752806</v>
+        <v>752891</v>
       </c>
       <c r="R214" t="n">
-        <v>7092716</v>
+        <v>7092445</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23391,10 +23393,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934782</v>
+        <v>119934810</v>
       </c>
       <c r="B215" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23403,30 +23405,30 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -23435,10 +23437,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752743</v>
+        <v>752803</v>
       </c>
       <c r="R215" t="n">
-        <v>7092544</v>
+        <v>7092670</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23497,10 +23499,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934761</v>
+        <v>119934791</v>
       </c>
       <c r="B216" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23513,26 +23515,26 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -23541,10 +23543,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752772</v>
+        <v>752777</v>
       </c>
       <c r="R216" t="n">
-        <v>7092487</v>
+        <v>7092488</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23603,10 +23605,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934760</v>
+        <v>119934785</v>
       </c>
       <c r="B217" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23619,26 +23621,26 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -23647,10 +23649,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752896</v>
+        <v>752721</v>
       </c>
       <c r="R217" t="n">
-        <v>7092456</v>
+        <v>7092493</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23709,10 +23711,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934791</v>
+        <v>119934760</v>
       </c>
       <c r="B218" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23725,26 +23727,26 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -23753,10 +23755,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752777</v>
+        <v>752896</v>
       </c>
       <c r="R218" t="n">
-        <v>7092488</v>
+        <v>7092456</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23815,10 +23817,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934799</v>
+        <v>119934787</v>
       </c>
       <c r="B219" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23831,26 +23833,26 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -23859,10 +23861,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752754</v>
+        <v>752738</v>
       </c>
       <c r="R219" t="n">
-        <v>7092559</v>
+        <v>7092548</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23895,6 +23897,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23921,10 +23928,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934748</v>
+        <v>119934794</v>
       </c>
       <c r="B220" t="n">
-        <v>89650</v>
+        <v>91850</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23937,34 +23944,38 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752762</v>
+        <v>752999</v>
       </c>
       <c r="R220" t="n">
-        <v>7092586</v>
+        <v>7092455</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23999,11 +24010,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD220" t="b">
         <v>0</v>
       </c>
@@ -24012,21 +24018,6 @@
       </c>
       <c r="AG220" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
@@ -24043,10 +24034,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934758</v>
+        <v>119934813</v>
       </c>
       <c r="B221" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24055,25 +24046,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24083,10 +24074,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752979</v>
+        <v>752857</v>
       </c>
       <c r="R221" t="n">
-        <v>7092382</v>
+        <v>7092672</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24119,11 +24110,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24150,10 +24136,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934796</v>
+        <v>119934766</v>
       </c>
       <c r="B222" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24166,34 +24152,38 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752805</v>
+        <v>752751</v>
       </c>
       <c r="R222" t="n">
-        <v>7092505</v>
+        <v>7092507</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24252,10 +24242,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934795</v>
+        <v>119934821</v>
       </c>
       <c r="B223" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24268,26 +24258,26 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -24296,10 +24286,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752996</v>
+        <v>752994</v>
       </c>
       <c r="R223" t="n">
-        <v>7092398</v>
+        <v>7092431</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24332,11 +24322,6 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC223" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24363,10 +24348,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934788</v>
+        <v>119934806</v>
       </c>
       <c r="B224" t="n">
-        <v>91850</v>
+        <v>89269</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24375,25 +24360,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -24407,10 +24392,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752781</v>
+        <v>752816</v>
       </c>
       <c r="R224" t="n">
-        <v>7092640</v>
+        <v>7092714</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24469,10 +24454,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934823</v>
+        <v>119934808</v>
       </c>
       <c r="B225" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24481,25 +24466,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -24513,10 +24498,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752959</v>
+        <v>752819</v>
       </c>
       <c r="R225" t="n">
-        <v>7092467</v>
+        <v>7092515</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24575,10 +24560,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934766</v>
+        <v>119934792</v>
       </c>
       <c r="B226" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24591,26 +24576,26 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -24619,10 +24604,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752751</v>
+        <v>752867</v>
       </c>
       <c r="R226" t="n">
-        <v>7092507</v>
+        <v>7092495</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24681,10 +24666,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934759</v>
+        <v>119934748</v>
       </c>
       <c r="B227" t="n">
-        <v>91902</v>
+        <v>89650</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24697,21 +24682,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24721,10 +24706,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752845</v>
+        <v>752762</v>
       </c>
       <c r="R227" t="n">
-        <v>7092505</v>
+        <v>7092586</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24761,7 +24746,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Undersida knäckt talltopp i mossa</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24772,6 +24757,21 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -24788,10 +24788,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934771</v>
+        <v>119934815</v>
       </c>
       <c r="B228" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24800,25 +24800,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -24828,10 +24828,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752765</v>
+        <v>752779</v>
       </c>
       <c r="R228" t="n">
-        <v>7092632</v>
+        <v>7092482</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24864,11 +24864,6 @@
       <c r="AA228" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -24895,10 +24890,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934798</v>
+        <v>119934763</v>
       </c>
       <c r="B229" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24911,34 +24906,38 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752945</v>
+        <v>752788</v>
       </c>
       <c r="R229" t="n">
-        <v>7092339</v>
+        <v>7092548</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24997,10 +24996,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934753</v>
+        <v>119934818</v>
       </c>
       <c r="B230" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25009,25 +25008,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25037,10 +25036,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>752888</v>
+        <v>753030</v>
       </c>
       <c r="R230" t="n">
-        <v>7092677</v>
+        <v>7092403</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25099,10 +25098,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934784</v>
+        <v>119934774</v>
       </c>
       <c r="B231" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25115,26 +25114,26 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25146,7 +25145,7 @@
         <v>752891</v>
       </c>
       <c r="R231" t="n">
-        <v>7092445</v>
+        <v>7092444</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25205,10 +25204,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934815</v>
+        <v>119934778</v>
       </c>
       <c r="B232" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25217,25 +25216,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -25245,10 +25244,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752779</v>
+        <v>752778</v>
       </c>
       <c r="R232" t="n">
-        <v>7092482</v>
+        <v>7092476</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25307,7 +25306,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934764</v>
+        <v>119934768</v>
       </c>
       <c r="B233" t="n">
         <v>91902</v>
@@ -25340,21 +25339,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752759</v>
+        <v>752771</v>
       </c>
       <c r="R233" t="n">
-        <v>7092478</v>
+        <v>7092668</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25413,10 +25408,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934811</v>
+        <v>119934767</v>
       </c>
       <c r="B234" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25425,25 +25420,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -25453,10 +25448,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752853</v>
+        <v>752720</v>
       </c>
       <c r="R234" t="n">
-        <v>7092405</v>
+        <v>7092493</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25515,10 +25510,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934794</v>
+        <v>119934752</v>
       </c>
       <c r="B235" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25527,42 +25522,38 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752999</v>
+        <v>752794</v>
       </c>
       <c r="R235" t="n">
-        <v>7092455</v>
+        <v>7092570</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25595,6 +25586,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25621,10 +25617,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934762</v>
+        <v>119934781</v>
       </c>
       <c r="B236" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25637,21 +25633,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -25665,10 +25661,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752732</v>
+        <v>752766</v>
       </c>
       <c r="R236" t="n">
-        <v>7092502</v>
+        <v>7092643</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25701,6 +25697,11 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC236" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25727,10 +25728,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934777</v>
+        <v>119934759</v>
       </c>
       <c r="B237" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25743,21 +25744,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -25767,10 +25768,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752809</v>
+        <v>752845</v>
       </c>
       <c r="R237" t="n">
-        <v>7092467</v>
+        <v>7092505</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25803,6 +25804,11 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25829,10 +25835,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934812</v>
+        <v>119934823</v>
       </c>
       <c r="B238" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25841,38 +25847,42 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752796</v>
+        <v>752959</v>
       </c>
       <c r="R238" t="n">
-        <v>7092694</v>
+        <v>7092467</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25931,10 +25941,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934772</v>
+        <v>119934817</v>
       </c>
       <c r="B239" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25943,25 +25953,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -25971,10 +25981,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752757</v>
+        <v>752778</v>
       </c>
       <c r="R239" t="n">
-        <v>7092617</v>
+        <v>7092478</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26007,11 +26017,6 @@
       <c r="AA239" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26038,10 +26043,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934789</v>
+        <v>119934764</v>
       </c>
       <c r="B240" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -26054,26 +26059,26 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26082,10 +26087,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752803</v>
+        <v>752759</v>
       </c>
       <c r="R240" t="n">
-        <v>7092378</v>
+        <v>7092478</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26144,10 +26149,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934773</v>
+        <v>119934788</v>
       </c>
       <c r="B241" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26156,30 +26161,30 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -26188,10 +26193,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752853</v>
+        <v>752781</v>
       </c>
       <c r="R241" t="n">
-        <v>7092405</v>
+        <v>7092640</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -26224,11 +26229,6 @@
       <c r="AA241" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD241" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -17982,10 +17982,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119893208</v>
+        <v>119893537</v>
       </c>
       <c r="B163" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17998,21 +17998,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18022,10 +18022,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>752928</v>
+        <v>752759</v>
       </c>
       <c r="R163" t="n">
-        <v>7092309</v>
+        <v>7092324</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18084,10 +18084,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119893348</v>
+        <v>119893423</v>
       </c>
       <c r="B164" t="n">
-        <v>91901</v>
+        <v>91874</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -18100,34 +18100,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5448</v>
+        <v>2059</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752893</v>
+        <v>752740</v>
       </c>
       <c r="R164" t="n">
-        <v>7092272</v>
+        <v>7092396</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18186,10 +18186,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119893598</v>
+        <v>119893473</v>
       </c>
       <c r="B165" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18198,25 +18198,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18226,10 +18226,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752767</v>
+        <v>752827</v>
       </c>
       <c r="R165" t="n">
-        <v>7092395</v>
+        <v>7092232</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18288,10 +18288,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119893430</v>
+        <v>119892875</v>
       </c>
       <c r="B166" t="n">
-        <v>91902</v>
+        <v>88170</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18304,21 +18304,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5449</v>
+        <v>4962</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18328,10 +18328,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752897</v>
+        <v>752854</v>
       </c>
       <c r="R166" t="n">
-        <v>7092235</v>
+        <v>7092368</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18390,10 +18390,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119893466</v>
+        <v>119891898</v>
       </c>
       <c r="B167" t="n">
-        <v>91852</v>
+        <v>89292</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18402,38 +18402,38 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4362</v>
+        <v>6286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752823</v>
+        <v>752740</v>
       </c>
       <c r="R167" t="n">
-        <v>7092228</v>
+        <v>7092396</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18492,7 +18492,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119893225</v>
+        <v>119891991</v>
       </c>
       <c r="B168" t="n">
         <v>91902</v>
@@ -18532,10 +18532,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752927</v>
+        <v>752740</v>
       </c>
       <c r="R168" t="n">
-        <v>7092298</v>
+        <v>7092396</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18594,10 +18594,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119893537</v>
+        <v>119893598</v>
       </c>
       <c r="B169" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18606,25 +18606,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18634,10 +18634,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752759</v>
+        <v>752767</v>
       </c>
       <c r="R169" t="n">
-        <v>7092324</v>
+        <v>7092395</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18696,10 +18696,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119797563</v>
+        <v>119893329</v>
       </c>
       <c r="B170" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18708,45 +18708,38 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752807</v>
+        <v>752893</v>
       </c>
       <c r="R170" t="n">
-        <v>7092367</v>
+        <v>7092272</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18773,17 +18766,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18792,29 +18780,28 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119893483</v>
+        <v>119797563</v>
       </c>
       <c r="B171" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18823,38 +18810,45 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752795</v>
+        <v>752807</v>
       </c>
       <c r="R171" t="n">
-        <v>7092265</v>
+        <v>7092367</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18881,12 +18875,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18895,28 +18894,29 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893423</v>
+        <v>119893175</v>
       </c>
       <c r="B172" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18929,34 +18929,34 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752740</v>
+        <v>752982</v>
       </c>
       <c r="R172" t="n">
-        <v>7092396</v>
+        <v>7092371</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19015,7 +19015,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119893626</v>
+        <v>119893208</v>
       </c>
       <c r="B173" t="n">
         <v>91902</v>
@@ -19055,10 +19055,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752767</v>
+        <v>752928</v>
       </c>
       <c r="R173" t="n">
-        <v>7092396</v>
+        <v>7092309</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19117,10 +19117,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119893016</v>
+        <v>119893430</v>
       </c>
       <c r="B174" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19133,21 +19133,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19157,10 +19157,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752901</v>
+        <v>752897</v>
       </c>
       <c r="R174" t="n">
-        <v>7092374</v>
+        <v>7092235</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19219,10 +19219,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119892118</v>
+        <v>119893225</v>
       </c>
       <c r="B175" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19231,25 +19231,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19259,10 +19259,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752838</v>
+        <v>752927</v>
       </c>
       <c r="R175" t="n">
-        <v>7092399</v>
+        <v>7092298</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19321,7 +19321,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119893175</v>
+        <v>119893626</v>
       </c>
       <c r="B176" t="n">
         <v>91902</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752982</v>
+        <v>752767</v>
       </c>
       <c r="R176" t="n">
-        <v>7092371</v>
+        <v>7092396</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19423,7 +19423,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119893329</v>
+        <v>119892970</v>
       </c>
       <c r="B177" t="n">
         <v>91902</v>
@@ -19463,10 +19463,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752893</v>
+        <v>752853</v>
       </c>
       <c r="R177" t="n">
-        <v>7092272</v>
+        <v>7092386</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19525,10 +19525,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119892970</v>
+        <v>119891959</v>
       </c>
       <c r="B178" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19537,25 +19537,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19565,10 +19565,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752853</v>
+        <v>752740</v>
       </c>
       <c r="R178" t="n">
-        <v>7092386</v>
+        <v>7092396</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19627,10 +19627,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119891898</v>
+        <v>119892909</v>
       </c>
       <c r="B179" t="n">
-        <v>89292</v>
+        <v>91844</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19639,38 +19639,38 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6286</v>
+        <v>3100</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752740</v>
+        <v>752854</v>
       </c>
       <c r="R179" t="n">
-        <v>7092396</v>
+        <v>7092368</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19729,10 +19729,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119891991</v>
+        <v>119893016</v>
       </c>
       <c r="B180" t="n">
-        <v>91902</v>
+        <v>91844</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19745,21 +19745,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19769,10 +19769,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752740</v>
+        <v>752901</v>
       </c>
       <c r="R180" t="n">
-        <v>7092396</v>
+        <v>7092374</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19831,10 +19831,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119893301</v>
+        <v>119892118</v>
       </c>
       <c r="B181" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19843,25 +19843,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19871,10 +19871,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752892</v>
+        <v>752838</v>
       </c>
       <c r="R181" t="n">
-        <v>7092280</v>
+        <v>7092399</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119892875</v>
+        <v>119893348</v>
       </c>
       <c r="B182" t="n">
-        <v>88170</v>
+        <v>91901</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19949,21 +19949,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4962</v>
+        <v>5448</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19973,10 +19973,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752854</v>
+        <v>752893</v>
       </c>
       <c r="R182" t="n">
-        <v>7092368</v>
+        <v>7092272</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20035,10 +20035,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119891959</v>
+        <v>119893466</v>
       </c>
       <c r="B183" t="n">
-        <v>91870</v>
+        <v>91852</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20047,25 +20047,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752740</v>
+        <v>752823</v>
       </c>
       <c r="R183" t="n">
-        <v>7092396</v>
+        <v>7092228</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119892909</v>
+        <v>119893301</v>
       </c>
       <c r="B184" t="n">
-        <v>91844</v>
+        <v>91850</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20153,21 +20153,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20177,10 +20177,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752854</v>
+        <v>752892</v>
       </c>
       <c r="R184" t="n">
-        <v>7092368</v>
+        <v>7092280</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20239,7 +20239,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119893473</v>
+        <v>119893483</v>
       </c>
       <c r="B185" t="n">
         <v>91902</v>
@@ -20279,10 +20279,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752827</v>
+        <v>752795</v>
       </c>
       <c r="R185" t="n">
-        <v>7092232</v>
+        <v>7092265</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934811</v>
+        <v>119934762</v>
       </c>
       <c r="B186" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20353,38 +20353,42 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752853</v>
+        <v>752732</v>
       </c>
       <c r="R186" t="n">
-        <v>7092405</v>
+        <v>7092502</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20443,10 +20447,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934756</v>
+        <v>119934808</v>
       </c>
       <c r="B187" t="n">
-        <v>89292</v>
+        <v>89269</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20459,26 +20463,26 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -20487,10 +20491,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752783</v>
+        <v>752819</v>
       </c>
       <c r="R187" t="n">
-        <v>7092657</v>
+        <v>7092515</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20549,10 +20553,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934762</v>
+        <v>119934753</v>
       </c>
       <c r="B188" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20561,42 +20565,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752732</v>
+        <v>752888</v>
       </c>
       <c r="R188" t="n">
-        <v>7092502</v>
+        <v>7092677</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20655,7 +20655,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934795</v>
+        <v>119934792</v>
       </c>
       <c r="B189" t="n">
         <v>91850</v>
@@ -20690,7 +20690,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20699,10 +20699,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752996</v>
+        <v>752867</v>
       </c>
       <c r="R189" t="n">
-        <v>7092398</v>
+        <v>7092495</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20735,11 +20735,6 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20766,10 +20761,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934796</v>
+        <v>119934777</v>
       </c>
       <c r="B190" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20782,21 +20777,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20806,10 +20801,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752805</v>
+        <v>752809</v>
       </c>
       <c r="R190" t="n">
-        <v>7092505</v>
+        <v>7092467</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20868,7 +20863,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934789</v>
+        <v>119934796</v>
       </c>
       <c r="B191" t="n">
         <v>91850</v>
@@ -20901,21 +20896,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752803</v>
+        <v>752805</v>
       </c>
       <c r="R191" t="n">
-        <v>7092378</v>
+        <v>7092505</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20974,10 +20965,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934772</v>
+        <v>119934787</v>
       </c>
       <c r="B192" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20986,38 +20977,42 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752757</v>
+        <v>752738</v>
       </c>
       <c r="R192" t="n">
-        <v>7092617</v>
+        <v>7092548</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21054,7 +21049,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i mossmatta</t>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21081,10 +21076,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934798</v>
+        <v>119934772</v>
       </c>
       <c r="B193" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21093,25 +21088,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21121,10 +21116,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752945</v>
+        <v>752757</v>
       </c>
       <c r="R193" t="n">
-        <v>7092339</v>
+        <v>7092617</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21157,6 +21152,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21183,10 +21183,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934799</v>
+        <v>119934795</v>
       </c>
       <c r="B194" t="n">
-        <v>91881</v>
+        <v>91850</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21199,26 +21199,26 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -21227,10 +21227,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752754</v>
+        <v>752996</v>
       </c>
       <c r="R194" t="n">
-        <v>7092559</v>
+        <v>7092398</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21263,6 +21263,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21289,10 +21294,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934775</v>
+        <v>119934806</v>
       </c>
       <c r="B195" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21301,30 +21306,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -21333,10 +21338,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752777</v>
+        <v>752816</v>
       </c>
       <c r="R195" t="n">
-        <v>7092577</v>
+        <v>7092714</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21395,10 +21400,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934777</v>
+        <v>119934763</v>
       </c>
       <c r="B196" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21411,34 +21416,38 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752809</v>
+        <v>752788</v>
       </c>
       <c r="R196" t="n">
-        <v>7092467</v>
+        <v>7092548</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21497,7 +21506,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934761</v>
+        <v>119934767</v>
       </c>
       <c r="B197" t="n">
         <v>91902</v>
@@ -21530,21 +21539,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752772</v>
+        <v>752720</v>
       </c>
       <c r="R197" t="n">
-        <v>7092487</v>
+        <v>7092493</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21603,7 +21608,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934773</v>
+        <v>119934771</v>
       </c>
       <c r="B198" t="n">
         <v>91862</v>
@@ -21636,21 +21641,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752853</v>
+        <v>752765</v>
       </c>
       <c r="R198" t="n">
-        <v>7092405</v>
+        <v>7092632</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21687,7 +21688,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21714,7 +21715,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934797</v>
+        <v>119934798</v>
       </c>
       <c r="B199" t="n">
         <v>91850</v>
@@ -21754,10 +21755,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752806</v>
+        <v>752945</v>
       </c>
       <c r="R199" t="n">
-        <v>7092716</v>
+        <v>7092339</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21918,10 +21919,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934819</v>
+        <v>119934766</v>
       </c>
       <c r="B201" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21930,38 +21931,42 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752979</v>
+        <v>752751</v>
       </c>
       <c r="R201" t="n">
-        <v>7092382</v>
+        <v>7092507</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22020,7 +22025,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934782</v>
+        <v>119934797</v>
       </c>
       <c r="B202" t="n">
         <v>91850</v>
@@ -22053,21 +22058,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752743</v>
+        <v>752806</v>
       </c>
       <c r="R202" t="n">
-        <v>7092544</v>
+        <v>7092716</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22126,10 +22127,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934783</v>
+        <v>119934756</v>
       </c>
       <c r="B203" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22138,30 +22139,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -22170,10 +22171,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752771</v>
+        <v>752783</v>
       </c>
       <c r="R203" t="n">
-        <v>7092674</v>
+        <v>7092657</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22206,11 +22207,6 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22237,10 +22233,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934790</v>
+        <v>119934755</v>
       </c>
       <c r="B204" t="n">
-        <v>91850</v>
+        <v>91481</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22253,38 +22249,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752853</v>
+        <v>752777</v>
       </c>
       <c r="R204" t="n">
-        <v>7092405</v>
+        <v>7092472</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22343,10 +22335,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934753</v>
+        <v>119934814</v>
       </c>
       <c r="B205" t="n">
-        <v>89292</v>
+        <v>91858</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22355,25 +22347,25 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6286</v>
+        <v>4364</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22383,10 +22375,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752888</v>
+        <v>752764</v>
       </c>
       <c r="R205" t="n">
-        <v>7092677</v>
+        <v>7092560</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22551,10 +22543,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934755</v>
+        <v>119934775</v>
       </c>
       <c r="B207" t="n">
-        <v>91481</v>
+        <v>91874</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22567,24 +22559,28 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
@@ -22594,7 +22590,7 @@
         <v>752777</v>
       </c>
       <c r="R207" t="n">
-        <v>7092472</v>
+        <v>7092577</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22653,10 +22649,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934786</v>
+        <v>119934817</v>
       </c>
       <c r="B208" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22665,42 +22661,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752833</v>
+        <v>752778</v>
       </c>
       <c r="R208" t="n">
-        <v>7092510</v>
+        <v>7092478</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22759,10 +22751,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934771</v>
+        <v>119934818</v>
       </c>
       <c r="B209" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22771,25 +22763,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22799,10 +22791,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752765</v>
+        <v>753030</v>
       </c>
       <c r="R209" t="n">
-        <v>7092632</v>
+        <v>7092403</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22835,11 +22827,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22866,7 +22853,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934814</v>
+        <v>119934815</v>
       </c>
       <c r="B210" t="n">
         <v>91858</v>
@@ -22906,10 +22893,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752764</v>
+        <v>752779</v>
       </c>
       <c r="R210" t="n">
-        <v>7092560</v>
+        <v>7092482</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22968,10 +22955,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934776</v>
+        <v>119934760</v>
       </c>
       <c r="B211" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22984,26 +22971,26 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -23012,10 +22999,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752759</v>
+        <v>752896</v>
       </c>
       <c r="R211" t="n">
-        <v>7092525</v>
+        <v>7092456</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23074,10 +23061,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934758</v>
+        <v>119934823</v>
       </c>
       <c r="B212" t="n">
-        <v>91901</v>
+        <v>91852</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23090,34 +23077,38 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752979</v>
+        <v>752959</v>
       </c>
       <c r="R212" t="n">
-        <v>7092382</v>
+        <v>7092467</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23150,11 +23141,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23181,10 +23167,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934809</v>
+        <v>119934791</v>
       </c>
       <c r="B213" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23193,30 +23179,30 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23225,10 +23211,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752817</v>
+        <v>752777</v>
       </c>
       <c r="R213" t="n">
-        <v>7092378</v>
+        <v>7092488</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23287,10 +23273,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934784</v>
+        <v>119934811</v>
       </c>
       <c r="B214" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23299,42 +23285,38 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R214" t="n">
-        <v>7092445</v>
+        <v>7092405</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23393,10 +23375,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934810</v>
+        <v>119934821</v>
       </c>
       <c r="B215" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23405,30 +23387,30 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -23437,10 +23419,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752803</v>
+        <v>752994</v>
       </c>
       <c r="R215" t="n">
-        <v>7092670</v>
+        <v>7092431</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23499,7 +23481,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934791</v>
+        <v>119934788</v>
       </c>
       <c r="B216" t="n">
         <v>91850</v>
@@ -23543,10 +23525,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752777</v>
+        <v>752781</v>
       </c>
       <c r="R216" t="n">
-        <v>7092488</v>
+        <v>7092640</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23605,7 +23587,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934785</v>
+        <v>119934782</v>
       </c>
       <c r="B217" t="n">
         <v>91850</v>
@@ -23640,7 +23622,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -23649,10 +23631,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752721</v>
+        <v>752743</v>
       </c>
       <c r="R217" t="n">
-        <v>7092493</v>
+        <v>7092544</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23711,7 +23693,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934760</v>
+        <v>119934764</v>
       </c>
       <c r="B218" t="n">
         <v>91902</v>
@@ -23746,7 +23728,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -23755,10 +23737,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752896</v>
+        <v>752759</v>
       </c>
       <c r="R218" t="n">
-        <v>7092456</v>
+        <v>7092478</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23817,10 +23799,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934787</v>
+        <v>119934748</v>
       </c>
       <c r="B219" t="n">
-        <v>91850</v>
+        <v>89650</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23833,38 +23815,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752738</v>
+        <v>752762</v>
       </c>
       <c r="R219" t="n">
-        <v>7092548</v>
+        <v>7092586</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23901,7 +23879,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Vid stig</t>
+          <t>Undersida knäckt talltopp i mossa</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23912,6 +23890,21 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
@@ -23928,7 +23921,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934794</v>
+        <v>119934781</v>
       </c>
       <c r="B220" t="n">
         <v>91850</v>
@@ -23963,7 +23956,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -23972,10 +23965,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752999</v>
+        <v>752766</v>
       </c>
       <c r="R220" t="n">
-        <v>7092455</v>
+        <v>7092643</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24008,6 +24001,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24034,10 +24032,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934813</v>
+        <v>119934783</v>
       </c>
       <c r="B221" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24046,38 +24044,42 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752857</v>
+        <v>752771</v>
       </c>
       <c r="R221" t="n">
-        <v>7092672</v>
+        <v>7092674</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24110,6 +24112,11 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24136,10 +24143,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934766</v>
+        <v>119934799</v>
       </c>
       <c r="B222" t="n">
-        <v>91902</v>
+        <v>91881</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24152,26 +24159,26 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5449</v>
+        <v>5966</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -24180,10 +24187,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752751</v>
+        <v>752754</v>
       </c>
       <c r="R222" t="n">
-        <v>7092507</v>
+        <v>7092559</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24242,10 +24249,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934821</v>
+        <v>119934776</v>
       </c>
       <c r="B223" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24258,26 +24265,26 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -24286,10 +24293,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752994</v>
+        <v>752759</v>
       </c>
       <c r="R223" t="n">
-        <v>7092431</v>
+        <v>7092525</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24348,10 +24355,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934806</v>
+        <v>119934784</v>
       </c>
       <c r="B224" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24360,30 +24367,30 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
@@ -24392,10 +24399,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752816</v>
+        <v>752891</v>
       </c>
       <c r="R224" t="n">
-        <v>7092714</v>
+        <v>7092445</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24454,10 +24461,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934808</v>
+        <v>119934786</v>
       </c>
       <c r="B225" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24466,30 +24473,30 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24498,10 +24505,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752819</v>
+        <v>752833</v>
       </c>
       <c r="R225" t="n">
-        <v>7092515</v>
+        <v>7092510</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24560,10 +24567,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934792</v>
+        <v>119934759</v>
       </c>
       <c r="B226" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24576,38 +24583,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752867</v>
+        <v>752845</v>
       </c>
       <c r="R226" t="n">
-        <v>7092495</v>
+        <v>7092505</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24640,6 +24643,11 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24666,10 +24674,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934748</v>
+        <v>119934752</v>
       </c>
       <c r="B227" t="n">
-        <v>89650</v>
+        <v>89292</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24678,25 +24686,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>1962</v>
+        <v>6286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24706,10 +24714,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752762</v>
+        <v>752794</v>
       </c>
       <c r="R227" t="n">
-        <v>7092586</v>
+        <v>7092570</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24746,7 +24754,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Undersida knäckt talltopp i mossa</t>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24757,21 +24765,6 @@
       </c>
       <c r="AG227" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
@@ -24788,10 +24781,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934815</v>
+        <v>119934774</v>
       </c>
       <c r="B228" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24800,38 +24793,42 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752779</v>
+        <v>752891</v>
       </c>
       <c r="R228" t="n">
-        <v>7092482</v>
+        <v>7092444</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24890,10 +24887,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934763</v>
+        <v>119934813</v>
       </c>
       <c r="B229" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24902,42 +24899,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752788</v>
+        <v>752857</v>
       </c>
       <c r="R229" t="n">
-        <v>7092548</v>
+        <v>7092672</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24996,10 +24989,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934818</v>
+        <v>119934761</v>
       </c>
       <c r="B230" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25008,38 +25001,42 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I230" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>753030</v>
+        <v>752772</v>
       </c>
       <c r="R230" t="n">
-        <v>7092403</v>
+        <v>7092487</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25098,10 +25095,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934774</v>
+        <v>119934810</v>
       </c>
       <c r="B231" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25110,30 +25107,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -25142,10 +25139,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752891</v>
+        <v>752803</v>
       </c>
       <c r="R231" t="n">
-        <v>7092444</v>
+        <v>7092670</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25204,10 +25201,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934778</v>
+        <v>119934789</v>
       </c>
       <c r="B232" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25220,34 +25217,38 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752778</v>
+        <v>752803</v>
       </c>
       <c r="R232" t="n">
-        <v>7092476</v>
+        <v>7092378</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25306,10 +25307,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934768</v>
+        <v>119934809</v>
       </c>
       <c r="B233" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25318,38 +25319,42 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752771</v>
+        <v>752817</v>
       </c>
       <c r="R233" t="n">
-        <v>7092668</v>
+        <v>7092378</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25408,10 +25413,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934767</v>
+        <v>119934794</v>
       </c>
       <c r="B234" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25424,34 +25429,38 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752720</v>
+        <v>752999</v>
       </c>
       <c r="R234" t="n">
-        <v>7092493</v>
+        <v>7092455</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25510,10 +25519,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934752</v>
+        <v>119934758</v>
       </c>
       <c r="B235" t="n">
-        <v>89292</v>
+        <v>91901</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25522,25 +25531,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6286</v>
+        <v>5448</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -25550,10 +25559,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752794</v>
+        <v>752979</v>
       </c>
       <c r="R235" t="n">
-        <v>7092570</v>
+        <v>7092382</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25590,7 +25599,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25617,10 +25626,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934781</v>
+        <v>119934778</v>
       </c>
       <c r="B236" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25633,38 +25642,34 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752766</v>
+        <v>752778</v>
       </c>
       <c r="R236" t="n">
-        <v>7092643</v>
+        <v>7092476</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25697,11 +25702,6 @@
       <c r="AA236" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC236" t="inlineStr">
-        <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -25728,10 +25728,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934759</v>
+        <v>119934785</v>
       </c>
       <c r="B237" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25744,34 +25744,38 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752845</v>
+        <v>752721</v>
       </c>
       <c r="R237" t="n">
-        <v>7092505</v>
+        <v>7092493</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25804,11 +25808,6 @@
       <c r="AA237" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -25835,10 +25834,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934823</v>
+        <v>119934773</v>
       </c>
       <c r="B238" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25847,30 +25846,30 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P238" t="inlineStr">
@@ -25879,10 +25878,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752959</v>
+        <v>752853</v>
       </c>
       <c r="R238" t="n">
-        <v>7092467</v>
+        <v>7092405</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25915,6 +25914,11 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC238" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25941,7 +25945,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934817</v>
+        <v>119934819</v>
       </c>
       <c r="B239" t="n">
         <v>91858</v>
@@ -25981,10 +25985,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752778</v>
+        <v>752979</v>
       </c>
       <c r="R239" t="n">
-        <v>7092478</v>
+        <v>7092382</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26043,10 +26047,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934764</v>
+        <v>119934790</v>
       </c>
       <c r="B240" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -26059,26 +26063,26 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26087,10 +26091,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752759</v>
+        <v>752853</v>
       </c>
       <c r="R240" t="n">
-        <v>7092478</v>
+        <v>7092405</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26149,10 +26153,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934788</v>
+        <v>119934768</v>
       </c>
       <c r="B241" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26165,38 +26169,34 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752781</v>
+        <v>752771</v>
       </c>
       <c r="R241" t="n">
-        <v>7092640</v>
+        <v>7092668</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -18798,10 +18798,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119797563</v>
+        <v>119893175</v>
       </c>
       <c r="B171" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18810,45 +18810,38 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752807</v>
+        <v>752982</v>
       </c>
       <c r="R171" t="n">
-        <v>7092367</v>
+        <v>7092371</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18875,17 +18868,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18894,29 +18882,28 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119893175</v>
+        <v>119797563</v>
       </c>
       <c r="B172" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18925,38 +18912,45 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752982</v>
+        <v>752807</v>
       </c>
       <c r="R172" t="n">
-        <v>7092371</v>
+        <v>7092367</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18983,12 +18977,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18997,18 +18996,19 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
@@ -19117,7 +19117,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119893430</v>
+        <v>119893225</v>
       </c>
       <c r="B174" t="n">
         <v>91902</v>
@@ -19157,10 +19157,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752897</v>
+        <v>752927</v>
       </c>
       <c r="R174" t="n">
-        <v>7092235</v>
+        <v>7092298</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19219,7 +19219,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119893225</v>
+        <v>119893626</v>
       </c>
       <c r="B175" t="n">
         <v>91902</v>
@@ -19259,10 +19259,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752927</v>
+        <v>752767</v>
       </c>
       <c r="R175" t="n">
-        <v>7092298</v>
+        <v>7092396</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19321,7 +19321,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119893626</v>
+        <v>119893430</v>
       </c>
       <c r="B176" t="n">
         <v>91902</v>
@@ -19361,10 +19361,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752767</v>
+        <v>752897</v>
       </c>
       <c r="R176" t="n">
-        <v>7092396</v>
+        <v>7092235</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19933,10 +19933,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119893348</v>
+        <v>119893466</v>
       </c>
       <c r="B182" t="n">
-        <v>91901</v>
+        <v>91852</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19949,21 +19949,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19973,10 +19973,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752893</v>
+        <v>752823</v>
       </c>
       <c r="R182" t="n">
-        <v>7092272</v>
+        <v>7092228</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20035,10 +20035,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119893466</v>
+        <v>119893348</v>
       </c>
       <c r="B183" t="n">
-        <v>91852</v>
+        <v>91901</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20051,21 +20051,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752823</v>
+        <v>752893</v>
       </c>
       <c r="R183" t="n">
-        <v>7092228</v>
+        <v>7092272</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21076,10 +21076,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934772</v>
+        <v>119934795</v>
       </c>
       <c r="B193" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21088,38 +21088,42 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752757</v>
+        <v>752996</v>
       </c>
       <c r="R193" t="n">
-        <v>7092617</v>
+        <v>7092398</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21156,7 +21160,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i mossmatta</t>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21183,10 +21187,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934795</v>
+        <v>119934763</v>
       </c>
       <c r="B194" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21199,26 +21203,26 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -21227,10 +21231,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752996</v>
+        <v>752788</v>
       </c>
       <c r="R194" t="n">
-        <v>7092398</v>
+        <v>7092548</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21263,11 +21267,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21294,10 +21293,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934806</v>
+        <v>119934772</v>
       </c>
       <c r="B195" t="n">
-        <v>89269</v>
+        <v>91862</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21310,38 +21309,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6276</v>
+        <v>4365</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752816</v>
+        <v>752757</v>
       </c>
       <c r="R195" t="n">
-        <v>7092714</v>
+        <v>7092617</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21374,6 +21369,11 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21400,10 +21400,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934763</v>
+        <v>119934806</v>
       </c>
       <c r="B196" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21412,30 +21412,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21444,10 +21444,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752788</v>
+        <v>752816</v>
       </c>
       <c r="R196" t="n">
-        <v>7092548</v>
+        <v>7092714</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -24355,10 +24355,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934784</v>
+        <v>119934752</v>
       </c>
       <c r="B224" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24367,42 +24367,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752891</v>
+        <v>752794</v>
       </c>
       <c r="R224" t="n">
-        <v>7092445</v>
+        <v>7092570</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24435,6 +24431,11 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24461,7 +24462,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934786</v>
+        <v>119934784</v>
       </c>
       <c r="B225" t="n">
         <v>91850</v>
@@ -24496,7 +24497,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24505,10 +24506,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752833</v>
+        <v>752891</v>
       </c>
       <c r="R225" t="n">
-        <v>7092510</v>
+        <v>7092445</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24567,10 +24568,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934759</v>
+        <v>119934786</v>
       </c>
       <c r="B226" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24583,34 +24584,38 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752845</v>
+        <v>752833</v>
       </c>
       <c r="R226" t="n">
-        <v>7092505</v>
+        <v>7092510</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24643,11 +24648,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -24674,10 +24674,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934752</v>
+        <v>119934759</v>
       </c>
       <c r="B227" t="n">
-        <v>89292</v>
+        <v>91902</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24686,25 +24686,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -24714,10 +24714,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752794</v>
+        <v>752845</v>
       </c>
       <c r="R227" t="n">
-        <v>7092570</v>
+        <v>7092505</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Äldre fruktkroppar</t>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD227" t="b">

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -20341,10 +20341,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934762</v>
+        <v>119934781</v>
       </c>
       <c r="B186" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20357,21 +20357,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -20385,10 +20385,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752732</v>
+        <v>752766</v>
       </c>
       <c r="R186" t="n">
-        <v>7092502</v>
+        <v>7092643</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20421,6 +20421,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20447,10 +20452,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934808</v>
+        <v>119934790</v>
       </c>
       <c r="B187" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20459,25 +20464,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -20491,10 +20496,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752819</v>
+        <v>752853</v>
       </c>
       <c r="R187" t="n">
-        <v>7092515</v>
+        <v>7092405</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20553,10 +20558,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934753</v>
+        <v>119934799</v>
       </c>
       <c r="B188" t="n">
-        <v>89292</v>
+        <v>91881</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20565,38 +20570,42 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6286</v>
+        <v>5966</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752888</v>
+        <v>752754</v>
       </c>
       <c r="R188" t="n">
-        <v>7092677</v>
+        <v>7092559</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20655,10 +20664,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934792</v>
+        <v>119934764</v>
       </c>
       <c r="B189" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20671,26 +20680,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20699,10 +20708,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752867</v>
+        <v>752759</v>
       </c>
       <c r="R189" t="n">
-        <v>7092495</v>
+        <v>7092478</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20761,10 +20770,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934777</v>
+        <v>119934791</v>
       </c>
       <c r="B190" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20777,34 +20786,38 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752809</v>
+        <v>752777</v>
       </c>
       <c r="R190" t="n">
-        <v>7092467</v>
+        <v>7092488</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20863,10 +20876,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934796</v>
+        <v>119934758</v>
       </c>
       <c r="B191" t="n">
-        <v>91850</v>
+        <v>91901</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20879,21 +20892,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20903,10 +20916,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752805</v>
+        <v>752979</v>
       </c>
       <c r="R191" t="n">
-        <v>7092505</v>
+        <v>7092382</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20939,6 +20952,11 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20965,10 +20983,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934787</v>
+        <v>119934752</v>
       </c>
       <c r="B192" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20977,42 +20995,38 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752738</v>
+        <v>752794</v>
       </c>
       <c r="R192" t="n">
-        <v>7092548</v>
+        <v>7092570</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21049,7 +21063,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Vid stig</t>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21076,10 +21090,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934795</v>
+        <v>119934814</v>
       </c>
       <c r="B193" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21088,42 +21102,38 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752996</v>
+        <v>752764</v>
       </c>
       <c r="R193" t="n">
-        <v>7092398</v>
+        <v>7092560</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21156,11 +21166,6 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21187,10 +21192,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934763</v>
+        <v>119934772</v>
       </c>
       <c r="B194" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21199,42 +21204,38 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752788</v>
+        <v>752757</v>
       </c>
       <c r="R194" t="n">
-        <v>7092548</v>
+        <v>7092617</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21267,6 +21268,11 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21293,10 +21299,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934772</v>
+        <v>119934785</v>
       </c>
       <c r="B195" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21305,38 +21311,42 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752757</v>
+        <v>752721</v>
       </c>
       <c r="R195" t="n">
-        <v>7092617</v>
+        <v>7092493</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21369,11 +21379,6 @@
       <c r="AA195" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21400,10 +21405,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934806</v>
+        <v>119934766</v>
       </c>
       <c r="B196" t="n">
-        <v>89269</v>
+        <v>91902</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21412,30 +21417,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21444,10 +21449,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752816</v>
+        <v>752751</v>
       </c>
       <c r="R196" t="n">
-        <v>7092714</v>
+        <v>7092507</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21506,10 +21511,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934767</v>
+        <v>119934809</v>
       </c>
       <c r="B197" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21518,38 +21523,42 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752720</v>
+        <v>752817</v>
       </c>
       <c r="R197" t="n">
-        <v>7092493</v>
+        <v>7092378</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21608,10 +21617,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934771</v>
+        <v>119934792</v>
       </c>
       <c r="B198" t="n">
-        <v>91862</v>
+        <v>91850</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21620,38 +21629,42 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4365</v>
+        <v>4361</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752765</v>
+        <v>752867</v>
       </c>
       <c r="R198" t="n">
-        <v>7092632</v>
+        <v>7092495</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21684,11 +21697,6 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21715,7 +21723,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934798</v>
+        <v>119934797</v>
       </c>
       <c r="B199" t="n">
         <v>91850</v>
@@ -21755,10 +21763,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752945</v>
+        <v>752806</v>
       </c>
       <c r="R199" t="n">
-        <v>7092339</v>
+        <v>7092716</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21817,10 +21825,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934812</v>
+        <v>119934748</v>
       </c>
       <c r="B200" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21829,25 +21837,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21857,10 +21865,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752796</v>
+        <v>752762</v>
       </c>
       <c r="R200" t="n">
-        <v>7092694</v>
+        <v>7092586</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21895,6 +21903,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -21903,6 +21916,21 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21919,10 +21947,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934766</v>
+        <v>119934810</v>
       </c>
       <c r="B201" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21931,30 +21959,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21963,10 +21991,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752751</v>
+        <v>752803</v>
       </c>
       <c r="R201" t="n">
-        <v>7092507</v>
+        <v>7092670</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22025,7 +22053,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934797</v>
+        <v>119934787</v>
       </c>
       <c r="B202" t="n">
         <v>91850</v>
@@ -22058,17 +22086,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752806</v>
+        <v>752738</v>
       </c>
       <c r="R202" t="n">
-        <v>7092716</v>
+        <v>7092548</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22101,6 +22133,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22127,10 +22164,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934756</v>
+        <v>119934778</v>
       </c>
       <c r="B203" t="n">
-        <v>89292</v>
+        <v>91874</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22139,42 +22176,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6286</v>
+        <v>2059</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752783</v>
+        <v>752778</v>
       </c>
       <c r="R203" t="n">
-        <v>7092657</v>
+        <v>7092476</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22233,10 +22266,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934755</v>
+        <v>119934773</v>
       </c>
       <c r="B204" t="n">
-        <v>91481</v>
+        <v>91862</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22245,38 +22278,42 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752777</v>
+        <v>752853</v>
       </c>
       <c r="R204" t="n">
-        <v>7092472</v>
+        <v>7092405</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22309,6 +22346,11 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22335,10 +22377,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934814</v>
+        <v>119934808</v>
       </c>
       <c r="B205" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22347,38 +22389,42 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752764</v>
+        <v>752819</v>
       </c>
       <c r="R205" t="n">
-        <v>7092560</v>
+        <v>7092515</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22437,10 +22483,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934765</v>
+        <v>119934811</v>
       </c>
       <c r="B206" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22449,42 +22495,38 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752760</v>
+        <v>752853</v>
       </c>
       <c r="R206" t="n">
-        <v>7092524</v>
+        <v>7092405</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22543,7 +22585,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934775</v>
+        <v>119934776</v>
       </c>
       <c r="B207" t="n">
         <v>91874</v>
@@ -22578,7 +22620,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -22587,10 +22629,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752777</v>
+        <v>752759</v>
       </c>
       <c r="R207" t="n">
-        <v>7092577</v>
+        <v>7092525</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22649,10 +22691,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934817</v>
+        <v>119934798</v>
       </c>
       <c r="B208" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -22661,25 +22703,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -22689,10 +22731,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752778</v>
+        <v>752945</v>
       </c>
       <c r="R208" t="n">
-        <v>7092478</v>
+        <v>7092339</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22751,10 +22793,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934818</v>
+        <v>119934753</v>
       </c>
       <c r="B209" t="n">
-        <v>91858</v>
+        <v>89292</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22763,25 +22805,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4364</v>
+        <v>6286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22791,10 +22833,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>753030</v>
+        <v>752888</v>
       </c>
       <c r="R209" t="n">
-        <v>7092403</v>
+        <v>7092677</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22853,10 +22895,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934815</v>
+        <v>119934775</v>
       </c>
       <c r="B210" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22865,38 +22907,42 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752779</v>
+        <v>752777</v>
       </c>
       <c r="R210" t="n">
-        <v>7092482</v>
+        <v>7092577</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22955,10 +23001,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934760</v>
+        <v>119934818</v>
       </c>
       <c r="B211" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22967,42 +23013,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752896</v>
+        <v>753030</v>
       </c>
       <c r="R211" t="n">
-        <v>7092456</v>
+        <v>7092403</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23061,10 +23103,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934823</v>
+        <v>119934788</v>
       </c>
       <c r="B212" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23077,21 +23119,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -23105,10 +23147,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752959</v>
+        <v>752781</v>
       </c>
       <c r="R212" t="n">
-        <v>7092467</v>
+        <v>7092640</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23167,7 +23209,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934791</v>
+        <v>119934795</v>
       </c>
       <c r="B213" t="n">
         <v>91850</v>
@@ -23202,7 +23244,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -23211,10 +23253,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752777</v>
+        <v>752996</v>
       </c>
       <c r="R213" t="n">
-        <v>7092488</v>
+        <v>7092398</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23247,6 +23289,11 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23273,7 +23320,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934811</v>
+        <v>119934815</v>
       </c>
       <c r="B214" t="n">
         <v>91858</v>
@@ -23313,10 +23360,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752853</v>
+        <v>752779</v>
       </c>
       <c r="R214" t="n">
-        <v>7092405</v>
+        <v>7092482</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23375,10 +23422,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934821</v>
+        <v>119934768</v>
       </c>
       <c r="B215" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23391,38 +23438,34 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752994</v>
+        <v>752771</v>
       </c>
       <c r="R215" t="n">
-        <v>7092431</v>
+        <v>7092668</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23481,10 +23524,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934788</v>
+        <v>119934771</v>
       </c>
       <c r="B216" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23493,42 +23536,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752781</v>
+        <v>752765</v>
       </c>
       <c r="R216" t="n">
-        <v>7092640</v>
+        <v>7092632</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23561,6 +23600,11 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23693,10 +23737,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934764</v>
+        <v>119934823</v>
       </c>
       <c r="B218" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23709,26 +23753,26 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -23737,10 +23781,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752759</v>
+        <v>752959</v>
       </c>
       <c r="R218" t="n">
-        <v>7092478</v>
+        <v>7092467</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23799,10 +23843,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934748</v>
+        <v>119934783</v>
       </c>
       <c r="B219" t="n">
-        <v>89650</v>
+        <v>91850</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -23815,34 +23859,38 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I219" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752762</v>
+        <v>752771</v>
       </c>
       <c r="R219" t="n">
-        <v>7092586</v>
+        <v>7092674</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23879,7 +23927,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Undersida knäckt talltopp i mossa</t>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23890,21 +23938,6 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
@@ -23921,10 +23954,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934781</v>
+        <v>119934812</v>
       </c>
       <c r="B220" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23933,42 +23966,38 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752766</v>
+        <v>752796</v>
       </c>
       <c r="R220" t="n">
-        <v>7092643</v>
+        <v>7092694</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24001,11 +24030,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24032,10 +24056,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934783</v>
+        <v>119934755</v>
       </c>
       <c r="B221" t="n">
-        <v>91850</v>
+        <v>91481</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24048,38 +24072,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752771</v>
+        <v>752777</v>
       </c>
       <c r="R221" t="n">
-        <v>7092674</v>
+        <v>7092472</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24112,11 +24132,6 @@
       <c r="AA221" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24143,10 +24158,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934799</v>
+        <v>119934819</v>
       </c>
       <c r="B222" t="n">
-        <v>91881</v>
+        <v>91858</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24155,42 +24170,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752754</v>
+        <v>752979</v>
       </c>
       <c r="R222" t="n">
-        <v>7092559</v>
+        <v>7092382</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24249,10 +24260,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934776</v>
+        <v>119934765</v>
       </c>
       <c r="B223" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24265,21 +24276,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -24293,10 +24304,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752759</v>
+        <v>752760</v>
       </c>
       <c r="R223" t="n">
-        <v>7092525</v>
+        <v>7092524</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24355,10 +24366,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934752</v>
+        <v>119934784</v>
       </c>
       <c r="B224" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24367,38 +24378,42 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752794</v>
+        <v>752891</v>
       </c>
       <c r="R224" t="n">
-        <v>7092570</v>
+        <v>7092445</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24431,11 +24446,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24462,7 +24472,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934784</v>
+        <v>119934786</v>
       </c>
       <c r="B225" t="n">
         <v>91850</v>
@@ -24497,7 +24507,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -24506,10 +24516,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752891</v>
+        <v>752833</v>
       </c>
       <c r="R225" t="n">
-        <v>7092445</v>
+        <v>7092510</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24568,10 +24578,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934786</v>
+        <v>119934763</v>
       </c>
       <c r="B226" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24584,26 +24594,26 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -24612,10 +24622,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752833</v>
+        <v>752788</v>
       </c>
       <c r="R226" t="n">
-        <v>7092510</v>
+        <v>7092548</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24674,10 +24684,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934759</v>
+        <v>119934774</v>
       </c>
       <c r="B227" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24690,34 +24700,38 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752845</v>
+        <v>752891</v>
       </c>
       <c r="R227" t="n">
-        <v>7092505</v>
+        <v>7092444</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24750,11 +24764,6 @@
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -24781,10 +24790,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934774</v>
+        <v>119934789</v>
       </c>
       <c r="B228" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24797,26 +24806,26 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -24825,10 +24834,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752891</v>
+        <v>752803</v>
       </c>
       <c r="R228" t="n">
-        <v>7092444</v>
+        <v>7092378</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24887,10 +24896,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934813</v>
+        <v>119934806</v>
       </c>
       <c r="B229" t="n">
-        <v>91858</v>
+        <v>89269</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24899,38 +24908,42 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I229" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752857</v>
+        <v>752816</v>
       </c>
       <c r="R229" t="n">
-        <v>7092672</v>
+        <v>7092714</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25095,10 +25108,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934810</v>
+        <v>119934759</v>
       </c>
       <c r="B231" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25107,42 +25120,38 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752803</v>
+        <v>752845</v>
       </c>
       <c r="R231" t="n">
-        <v>7092670</v>
+        <v>7092505</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25175,6 +25184,11 @@
       <c r="AA231" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25201,10 +25215,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934789</v>
+        <v>119934767</v>
       </c>
       <c r="B232" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -25217,38 +25231,34 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I232" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752803</v>
+        <v>752720</v>
       </c>
       <c r="R232" t="n">
-        <v>7092378</v>
+        <v>7092493</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25307,10 +25317,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934809</v>
+        <v>119934762</v>
       </c>
       <c r="B233" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -25319,30 +25329,30 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25351,10 +25361,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752817</v>
+        <v>752732</v>
       </c>
       <c r="R233" t="n">
-        <v>7092378</v>
+        <v>7092502</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25413,10 +25423,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>119934794</v>
+        <v>119934813</v>
       </c>
       <c r="B234" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -25425,42 +25435,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>752999</v>
+        <v>752857</v>
       </c>
       <c r="R234" t="n">
-        <v>7092455</v>
+        <v>7092672</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -25519,10 +25525,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934758</v>
+        <v>119934796</v>
       </c>
       <c r="B235" t="n">
-        <v>91901</v>
+        <v>91850</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25535,21 +25541,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -25559,10 +25565,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752979</v>
+        <v>752805</v>
       </c>
       <c r="R235" t="n">
-        <v>7092382</v>
+        <v>7092505</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25595,11 +25601,6 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC235" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25626,10 +25627,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934778</v>
+        <v>119934821</v>
       </c>
       <c r="B236" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25642,34 +25643,38 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P236" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752778</v>
+        <v>752994</v>
       </c>
       <c r="R236" t="n">
-        <v>7092476</v>
+        <v>7092431</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25728,10 +25733,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934785</v>
+        <v>119934817</v>
       </c>
       <c r="B237" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -25740,42 +25745,38 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752721</v>
+        <v>752778</v>
       </c>
       <c r="R237" t="n">
-        <v>7092493</v>
+        <v>7092478</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25834,10 +25835,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934773</v>
+        <v>119934777</v>
       </c>
       <c r="B238" t="n">
-        <v>91862</v>
+        <v>91874</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25846,42 +25847,38 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4365</v>
+        <v>2059</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752853</v>
+        <v>752809</v>
       </c>
       <c r="R238" t="n">
-        <v>7092405</v>
+        <v>7092467</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25914,11 +25911,6 @@
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC238" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -25945,10 +25937,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934819</v>
+        <v>119934794</v>
       </c>
       <c r="B239" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25957,38 +25949,42 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752979</v>
+        <v>752999</v>
       </c>
       <c r="R239" t="n">
-        <v>7092382</v>
+        <v>7092455</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26047,10 +26043,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934790</v>
+        <v>119934760</v>
       </c>
       <c r="B240" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -26063,26 +26059,26 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P240" t="inlineStr">
@@ -26091,10 +26087,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752853</v>
+        <v>752896</v>
       </c>
       <c r="R240" t="n">
-        <v>7092405</v>
+        <v>7092456</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26153,10 +26149,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934768</v>
+        <v>119934756</v>
       </c>
       <c r="B241" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26165,38 +26161,42 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752771</v>
+        <v>752783</v>
       </c>
       <c r="R241" t="n">
-        <v>7092668</v>
+        <v>7092657</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -20341,7 +20341,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119934781</v>
+        <v>119934797</v>
       </c>
       <c r="B186" t="n">
         <v>91850</v>
@@ -20374,21 +20374,17 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752766</v>
+        <v>752806</v>
       </c>
       <c r="R186" t="n">
-        <v>7092643</v>
+        <v>7092716</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20421,11 +20417,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20452,7 +20443,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119934790</v>
+        <v>119934782</v>
       </c>
       <c r="B187" t="n">
         <v>91850</v>
@@ -20487,7 +20478,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P187" t="inlineStr">
@@ -20496,10 +20487,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752853</v>
+        <v>752743</v>
       </c>
       <c r="R187" t="n">
-        <v>7092405</v>
+        <v>7092544</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20558,10 +20549,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119934799</v>
+        <v>119934761</v>
       </c>
       <c r="B188" t="n">
-        <v>91881</v>
+        <v>91902</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20574,26 +20565,26 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5966</v>
+        <v>5449</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -20602,10 +20593,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752754</v>
+        <v>752772</v>
       </c>
       <c r="R188" t="n">
-        <v>7092559</v>
+        <v>7092487</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20664,10 +20655,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119934764</v>
+        <v>119934781</v>
       </c>
       <c r="B189" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20680,26 +20671,26 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -20708,10 +20699,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752759</v>
+        <v>752766</v>
       </c>
       <c r="R189" t="n">
-        <v>7092478</v>
+        <v>7092643</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20744,6 +20735,11 @@
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Inte typiskt orange på hatten, men orange "solnedgång" vid delning. Yngre granar i närheten</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20770,10 +20766,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119934791</v>
+        <v>119934817</v>
       </c>
       <c r="B190" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20782,42 +20778,38 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752777</v>
+        <v>752778</v>
       </c>
       <c r="R190" t="n">
-        <v>7092488</v>
+        <v>7092478</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20876,10 +20868,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119934758</v>
+        <v>119934799</v>
       </c>
       <c r="B191" t="n">
-        <v>91901</v>
+        <v>91881</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20892,34 +20884,38 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5448</v>
+        <v>5966</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752979</v>
+        <v>752754</v>
       </c>
       <c r="R191" t="n">
-        <v>7092382</v>
+        <v>7092559</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20952,11 +20948,6 @@
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20983,10 +20974,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119934752</v>
+        <v>119934788</v>
       </c>
       <c r="B192" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20995,38 +20986,42 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752794</v>
+        <v>752781</v>
       </c>
       <c r="R192" t="n">
-        <v>7092570</v>
+        <v>7092640</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21059,11 +21054,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21090,10 +21080,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119934814</v>
+        <v>119934786</v>
       </c>
       <c r="B193" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21102,38 +21092,42 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752764</v>
+        <v>752833</v>
       </c>
       <c r="R193" t="n">
-        <v>7092560</v>
+        <v>7092510</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21192,10 +21186,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119934772</v>
+        <v>119934811</v>
       </c>
       <c r="B194" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21204,25 +21198,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21232,10 +21226,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752757</v>
+        <v>752853</v>
       </c>
       <c r="R194" t="n">
-        <v>7092617</v>
+        <v>7092405</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21268,11 +21262,6 @@
       <c r="AA194" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21299,10 +21288,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119934785</v>
+        <v>119934756</v>
       </c>
       <c r="B195" t="n">
-        <v>91850</v>
+        <v>89292</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21311,30 +21300,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4361</v>
+        <v>6286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -21343,10 +21332,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752721</v>
+        <v>752783</v>
       </c>
       <c r="R195" t="n">
-        <v>7092493</v>
+        <v>7092657</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21405,10 +21394,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119934766</v>
+        <v>119934808</v>
       </c>
       <c r="B196" t="n">
-        <v>91902</v>
+        <v>89269</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21417,30 +21406,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
@@ -21449,10 +21438,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752751</v>
+        <v>752819</v>
       </c>
       <c r="R196" t="n">
-        <v>7092507</v>
+        <v>7092515</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21511,10 +21500,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934809</v>
+        <v>119934791</v>
       </c>
       <c r="B197" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -21523,30 +21512,30 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P197" t="inlineStr">
@@ -21555,10 +21544,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752817</v>
+        <v>752777</v>
       </c>
       <c r="R197" t="n">
-        <v>7092378</v>
+        <v>7092488</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21617,10 +21606,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934792</v>
+        <v>119934777</v>
       </c>
       <c r="B198" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21633,38 +21622,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752867</v>
+        <v>752809</v>
       </c>
       <c r="R198" t="n">
-        <v>7092495</v>
+        <v>7092467</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21723,7 +21708,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934797</v>
+        <v>119934792</v>
       </c>
       <c r="B199" t="n">
         <v>91850</v>
@@ -21756,17 +21741,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752806</v>
+        <v>752867</v>
       </c>
       <c r="R199" t="n">
-        <v>7092716</v>
+        <v>7092495</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21825,10 +21814,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119934748</v>
+        <v>119934798</v>
       </c>
       <c r="B200" t="n">
-        <v>89650</v>
+        <v>91850</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -21841,21 +21830,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1962</v>
+        <v>4361</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21865,10 +21854,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752762</v>
+        <v>752945</v>
       </c>
       <c r="R200" t="n">
-        <v>7092586</v>
+        <v>7092339</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21903,11 +21892,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Undersida knäckt talltopp i mossa</t>
-        </is>
-      </c>
       <c r="AD200" t="b">
         <v>0</v>
       </c>
@@ -21916,21 +21900,6 @@
       </c>
       <c r="AG200" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ200" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
@@ -21947,10 +21916,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119934810</v>
+        <v>119934823</v>
       </c>
       <c r="B201" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21959,30 +21928,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -21991,10 +21960,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752803</v>
+        <v>752959</v>
       </c>
       <c r="R201" t="n">
-        <v>7092670</v>
+        <v>7092467</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22053,10 +22022,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119934787</v>
+        <v>119934771</v>
       </c>
       <c r="B202" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22065,42 +22034,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752738</v>
+        <v>752765</v>
       </c>
       <c r="R202" t="n">
-        <v>7092548</v>
+        <v>7092632</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22137,7 +22102,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Vid stig</t>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22164,10 +22129,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119934778</v>
+        <v>119934758</v>
       </c>
       <c r="B203" t="n">
-        <v>91874</v>
+        <v>91901</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22180,21 +22145,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2059</v>
+        <v>5448</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22204,10 +22169,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752778</v>
+        <v>752979</v>
       </c>
       <c r="R203" t="n">
-        <v>7092476</v>
+        <v>7092382</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22240,6 +22205,11 @@
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22266,10 +22236,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119934773</v>
+        <v>119934767</v>
       </c>
       <c r="B204" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22278,42 +22248,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752853</v>
+        <v>752720</v>
       </c>
       <c r="R204" t="n">
-        <v>7092405</v>
+        <v>7092493</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22346,11 +22312,6 @@
       <c r="AA204" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22377,10 +22338,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119934808</v>
+        <v>119934753</v>
       </c>
       <c r="B205" t="n">
-        <v>89269</v>
+        <v>89292</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -22393,38 +22354,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6276</v>
+        <v>6286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752819</v>
+        <v>752888</v>
       </c>
       <c r="R205" t="n">
-        <v>7092515</v>
+        <v>7092677</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22483,10 +22440,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119934811</v>
+        <v>119934776</v>
       </c>
       <c r="B206" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -22495,38 +22452,42 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752853</v>
+        <v>752759</v>
       </c>
       <c r="R206" t="n">
-        <v>7092405</v>
+        <v>7092525</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22585,10 +22546,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934776</v>
+        <v>119934806</v>
       </c>
       <c r="B207" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -22597,25 +22558,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -22629,10 +22590,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752759</v>
+        <v>752816</v>
       </c>
       <c r="R207" t="n">
-        <v>7092525</v>
+        <v>7092714</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22691,7 +22652,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934798</v>
+        <v>119934784</v>
       </c>
       <c r="B208" t="n">
         <v>91850</v>
@@ -22724,17 +22685,21 @@
           <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752945</v>
+        <v>752891</v>
       </c>
       <c r="R208" t="n">
-        <v>7092339</v>
+        <v>7092445</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22793,10 +22758,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934753</v>
+        <v>119934755</v>
       </c>
       <c r="B209" t="n">
-        <v>89292</v>
+        <v>91481</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -22805,25 +22770,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -22833,10 +22798,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752888</v>
+        <v>752777</v>
       </c>
       <c r="R209" t="n">
-        <v>7092677</v>
+        <v>7092472</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22895,10 +22860,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934775</v>
+        <v>119934763</v>
       </c>
       <c r="B210" t="n">
-        <v>91874</v>
+        <v>91902</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -22911,26 +22876,26 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -22939,10 +22904,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752777</v>
+        <v>752788</v>
       </c>
       <c r="R210" t="n">
-        <v>7092577</v>
+        <v>7092548</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23001,10 +22966,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119934818</v>
+        <v>119934775</v>
       </c>
       <c r="B211" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -23013,38 +22978,42 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>753030</v>
+        <v>752777</v>
       </c>
       <c r="R211" t="n">
-        <v>7092403</v>
+        <v>7092577</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23103,10 +23072,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119934788</v>
+        <v>119934818</v>
       </c>
       <c r="B212" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -23115,42 +23084,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752781</v>
+        <v>753030</v>
       </c>
       <c r="R212" t="n">
-        <v>7092640</v>
+        <v>7092403</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23209,10 +23174,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119934795</v>
+        <v>119934812</v>
       </c>
       <c r="B213" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -23221,42 +23186,38 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752996</v>
+        <v>752796</v>
       </c>
       <c r="R213" t="n">
-        <v>7092398</v>
+        <v>7092694</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23289,11 +23250,6 @@
       <c r="AA213" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23320,10 +23276,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119934815</v>
+        <v>119934760</v>
       </c>
       <c r="B214" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -23332,38 +23288,42 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752779</v>
+        <v>752896</v>
       </c>
       <c r="R214" t="n">
-        <v>7092482</v>
+        <v>7092456</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23422,10 +23382,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119934768</v>
+        <v>119934752</v>
       </c>
       <c r="B215" t="n">
-        <v>91902</v>
+        <v>89292</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -23434,25 +23394,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5449</v>
+        <v>6286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23462,10 +23422,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752771</v>
+        <v>752794</v>
       </c>
       <c r="R215" t="n">
-        <v>7092668</v>
+        <v>7092570</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23498,6 +23458,11 @@
       <c r="AA215" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23524,10 +23489,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119934771</v>
+        <v>119934814</v>
       </c>
       <c r="B216" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -23536,25 +23501,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23564,10 +23529,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752765</v>
+        <v>752764</v>
       </c>
       <c r="R216" t="n">
-        <v>7092632</v>
+        <v>7092560</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23600,11 +23565,6 @@
       <c r="AA216" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC216" t="inlineStr">
-        <is>
-          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23631,10 +23591,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119934782</v>
+        <v>119934748</v>
       </c>
       <c r="B217" t="n">
-        <v>91850</v>
+        <v>89650</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -23647,38 +23607,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4361</v>
+        <v>1962</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752743</v>
+        <v>752762</v>
       </c>
       <c r="R217" t="n">
-        <v>7092544</v>
+        <v>7092586</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -23713,6 +23669,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Undersida knäckt talltopp i mossa</t>
+        </is>
+      </c>
       <c r="AD217" t="b">
         <v>0</v>
       </c>
@@ -23721,6 +23682,21 @@
       </c>
       <c r="AG217" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO217" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
@@ -23737,10 +23713,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119934823</v>
+        <v>119934765</v>
       </c>
       <c r="B218" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -23753,21 +23729,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -23781,10 +23757,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752959</v>
+        <v>752760</v>
       </c>
       <c r="R218" t="n">
-        <v>7092467</v>
+        <v>7092524</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -23843,7 +23819,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119934783</v>
+        <v>119934794</v>
       </c>
       <c r="B219" t="n">
         <v>91850</v>
@@ -23878,7 +23854,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -23887,10 +23863,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752771</v>
+        <v>752999</v>
       </c>
       <c r="R219" t="n">
-        <v>7092674</v>
+        <v>7092455</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23923,11 +23899,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-21</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23954,10 +23925,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119934812</v>
+        <v>119934772</v>
       </c>
       <c r="B220" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -23966,25 +23937,25 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -23994,10 +23965,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752796</v>
+        <v>752757</v>
       </c>
       <c r="R220" t="n">
-        <v>7092694</v>
+        <v>7092617</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24030,6 +24001,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24056,10 +24032,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119934755</v>
+        <v>119934819</v>
       </c>
       <c r="B221" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -24068,25 +24044,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24096,10 +24072,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752777</v>
+        <v>752979</v>
       </c>
       <c r="R221" t="n">
-        <v>7092472</v>
+        <v>7092382</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24158,10 +24134,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119934819</v>
+        <v>119934768</v>
       </c>
       <c r="B222" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -24170,25 +24146,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24198,10 +24174,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752979</v>
+        <v>752771</v>
       </c>
       <c r="R222" t="n">
-        <v>7092382</v>
+        <v>7092668</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24260,10 +24236,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119934765</v>
+        <v>119934783</v>
       </c>
       <c r="B223" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -24276,26 +24252,26 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P223" t="inlineStr">
@@ -24304,10 +24280,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752760</v>
+        <v>752771</v>
       </c>
       <c r="R223" t="n">
-        <v>7092524</v>
+        <v>7092674</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24340,6 +24316,11 @@
       <c r="AA223" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>Invid silverlåga</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24366,10 +24347,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119934784</v>
+        <v>119934815</v>
       </c>
       <c r="B224" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -24378,42 +24359,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752891</v>
+        <v>752779</v>
       </c>
       <c r="R224" t="n">
-        <v>7092445</v>
+        <v>7092482</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24472,10 +24449,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119934786</v>
+        <v>119934778</v>
       </c>
       <c r="B225" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -24488,38 +24465,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752833</v>
+        <v>752778</v>
       </c>
       <c r="R225" t="n">
-        <v>7092510</v>
+        <v>7092476</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24578,10 +24551,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119934763</v>
+        <v>119934785</v>
       </c>
       <c r="B226" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -24594,26 +24567,26 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -24622,10 +24595,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752788</v>
+        <v>752721</v>
       </c>
       <c r="R226" t="n">
-        <v>7092548</v>
+        <v>7092493</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24684,10 +24657,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119934774</v>
+        <v>119934790</v>
       </c>
       <c r="B227" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -24700,26 +24673,26 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -24728,10 +24701,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752891</v>
+        <v>752853</v>
       </c>
       <c r="R227" t="n">
-        <v>7092444</v>
+        <v>7092405</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24790,10 +24763,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119934789</v>
+        <v>119934774</v>
       </c>
       <c r="B228" t="n">
-        <v>91850</v>
+        <v>91874</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -24806,26 +24779,26 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -24834,10 +24807,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752803</v>
+        <v>752891</v>
       </c>
       <c r="R228" t="n">
-        <v>7092378</v>
+        <v>7092444</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24896,10 +24869,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119934806</v>
+        <v>119934795</v>
       </c>
       <c r="B229" t="n">
-        <v>89269</v>
+        <v>91850</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -24908,30 +24881,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -24940,10 +24913,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752816</v>
+        <v>752996</v>
       </c>
       <c r="R229" t="n">
-        <v>7092714</v>
+        <v>7092398</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24976,6 +24949,11 @@
       <c r="AA229" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>10 fruktkroppar i linje, samma mycel troligtvis</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25002,10 +24980,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119934761</v>
+        <v>119934821</v>
       </c>
       <c r="B230" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -25018,26 +24996,26 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -25046,10 +25024,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>752772</v>
+        <v>752994</v>
       </c>
       <c r="R230" t="n">
-        <v>7092487</v>
+        <v>7092431</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25108,10 +25086,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119934759</v>
+        <v>119934787</v>
       </c>
       <c r="B231" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -25124,34 +25102,38 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>752845</v>
+        <v>752738</v>
       </c>
       <c r="R231" t="n">
-        <v>7092505</v>
+        <v>7092548</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25188,7 +25170,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Under silverlåga</t>
+          <t>Vid stig</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -25215,7 +25197,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>119934767</v>
+        <v>119934762</v>
       </c>
       <c r="B232" t="n">
         <v>91902</v>
@@ -25248,17 +25230,21 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P232" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>752720</v>
+        <v>752732</v>
       </c>
       <c r="R232" t="n">
-        <v>7092493</v>
+        <v>7092502</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25317,7 +25303,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>119934762</v>
+        <v>119934764</v>
       </c>
       <c r="B233" t="n">
         <v>91902</v>
@@ -25352,7 +25338,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
@@ -25361,10 +25347,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>752732</v>
+        <v>752759</v>
       </c>
       <c r="R233" t="n">
-        <v>7092502</v>
+        <v>7092478</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -25525,10 +25511,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>119934796</v>
+        <v>119934773</v>
       </c>
       <c r="B235" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -25537,38 +25523,42 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P235" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>752805</v>
+        <v>752853</v>
       </c>
       <c r="R235" t="n">
-        <v>7092505</v>
+        <v>7092405</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -25601,6 +25591,11 @@
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -25627,10 +25622,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>119934821</v>
+        <v>119934766</v>
       </c>
       <c r="B236" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -25643,26 +25638,26 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P236" t="inlineStr">
@@ -25671,10 +25666,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>752994</v>
+        <v>752751</v>
       </c>
       <c r="R236" t="n">
-        <v>7092431</v>
+        <v>7092507</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -25733,7 +25728,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>119934817</v>
+        <v>119934809</v>
       </c>
       <c r="B237" t="n">
         <v>91858</v>
@@ -25766,17 +25761,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P237" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>752778</v>
+        <v>752817</v>
       </c>
       <c r="R237" t="n">
-        <v>7092478</v>
+        <v>7092378</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25835,10 +25834,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>119934777</v>
+        <v>119934796</v>
       </c>
       <c r="B238" t="n">
-        <v>91874</v>
+        <v>91850</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -25851,21 +25850,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -25875,10 +25874,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>752809</v>
+        <v>752805</v>
       </c>
       <c r="R238" t="n">
-        <v>7092467</v>
+        <v>7092505</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -25937,10 +25936,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>119934794</v>
+        <v>119934810</v>
       </c>
       <c r="B239" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -25949,30 +25948,30 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
@@ -25981,10 +25980,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>752999</v>
+        <v>752803</v>
       </c>
       <c r="R239" t="n">
-        <v>7092455</v>
+        <v>7092670</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26043,7 +26042,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>119934760</v>
+        <v>119934759</v>
       </c>
       <c r="B240" t="n">
         <v>91902</v>
@@ -26076,21 +26075,17 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+      <c r="I240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>752896</v>
+        <v>752845</v>
       </c>
       <c r="R240" t="n">
-        <v>7092456</v>
+        <v>7092505</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26123,6 +26118,11 @@
       <c r="AA240" t="inlineStr">
         <is>
           <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC240" t="inlineStr">
+        <is>
+          <t>Under silverlåga</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -26149,10 +26149,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>119934756</v>
+        <v>119934789</v>
       </c>
       <c r="B241" t="n">
-        <v>89292</v>
+        <v>91850</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -26161,30 +26161,30 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6286</v>
+        <v>4361</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P241" t="inlineStr">
@@ -26193,10 +26193,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>752783</v>
+        <v>752803</v>
       </c>
       <c r="R241" t="n">
-        <v>7092657</v>
+        <v>7092378</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY242"/>
+  <dimension ref="A1:AY244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26355,6 +26355,245 @@
       </c>
       <c r="AY242" t="inlineStr"/>
     </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>128587583</v>
+      </c>
+      <c r="B243" t="n">
+        <v>92746</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>752876</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7092345</v>
+      </c>
+      <c r="S243" t="n">
+        <v>5</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>Under tallgren nedsänkt i mossa. Flera sammanväxta fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>128588720</v>
+      </c>
+      <c r="B244" t="n">
+        <v>91858</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>752891</v>
+      </c>
+      <c r="R244" t="n">
+        <v>7092444</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>Talltorraka, med klibbticka och är kottesmedja</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY244"/>
+  <dimension ref="A1:AY247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26594,6 +26594,297 @@
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>128627830</v>
+      </c>
+      <c r="B245" t="n">
+        <v>90276</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>752818</v>
+      </c>
+      <c r="R245" t="n">
+        <v>7092471</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>128627828</v>
+      </c>
+      <c r="B246" t="n">
+        <v>92770</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>752864</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7092415</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>128627827</v>
+      </c>
+      <c r="B247" t="n">
+        <v>92742</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>752892</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7092398</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY247"/>
+  <dimension ref="A1:AY251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26885,6 +26885,421 @@
       </c>
       <c r="AY247" t="inlineStr"/>
     </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>128630176</v>
+      </c>
+      <c r="B248" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>752927</v>
+      </c>
+      <c r="R248" t="n">
+        <v>7092361</v>
+      </c>
+      <c r="S248" t="n">
+        <v>5</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>128630172</v>
+      </c>
+      <c r="B249" t="n">
+        <v>92735</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>752894</v>
+      </c>
+      <c r="R249" t="n">
+        <v>7092403</v>
+      </c>
+      <c r="S249" t="n">
+        <v>5</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>Vid stigen</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>128630168</v>
+      </c>
+      <c r="B250" t="n">
+        <v>92771</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>752927</v>
+      </c>
+      <c r="R250" t="n">
+        <v>7092361</v>
+      </c>
+      <c r="S250" t="n">
+        <v>5</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>128630170</v>
+      </c>
+      <c r="B251" t="n">
+        <v>92755</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>752914</v>
+      </c>
+      <c r="R251" t="n">
+        <v>7092346</v>
+      </c>
+      <c r="S251" t="n">
+        <v>5</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92746</v>
+        <v>92752</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91858</v>
+        <v>91864</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90276</v>
+        <v>90282</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92770</v>
+        <v>92776</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92742</v>
+        <v>92748</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>128630176</v>
       </c>
       <c r="B248" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92735</v>
+        <v>92740</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92771</v>
+        <v>92776</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92755</v>
+        <v>92760</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92752</v>
+        <v>92758</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91864</v>
+        <v>91870</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90282</v>
+        <v>90288</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92748</v>
+        <v>92754</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92740</v>
+        <v>92746</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92758</v>
+        <v>92760</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91870</v>
+        <v>91872</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90288</v>
+        <v>90290</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92760</v>
+        <v>92761</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92784</v>
+        <v>92785</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92761</v>
+        <v>92788</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91873</v>
+        <v>91900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90290</v>
+        <v>90317</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>128630176</v>
       </c>
       <c r="B248" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91900</v>
+        <v>91905</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90317</v>
+        <v>90322</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92776</v>
+        <v>92781</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27111,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27208,7 +27208,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92793</v>
+        <v>92798</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90322</v>
+        <v>90327</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26706,21 +26706,12 @@
       <c r="E246" t="n">
         <v>5449</v>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
@@ -26793,7 +26784,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27009,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92781</v>
+        <v>92786</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27111,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27121,21 +27112,12 @@
       <c r="E250" t="n">
         <v>5449</v>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr"/>
       <c r="P250" t="inlineStr">
         <is>
@@ -27208,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92798</v>
+        <v>92802</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91910</v>
+        <v>91914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90327</v>
+        <v>90331</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>128630176</v>
       </c>
       <c r="B248" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92786</v>
+        <v>92790</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92802</v>
+        <v>92807</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91914</v>
+        <v>91919</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90331</v>
+        <v>90336</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>128630176</v>
       </c>
       <c r="B248" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92790</v>
+        <v>92795</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91922</v>
+        <v>91927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90338</v>
+        <v>90343</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92806</v>
+        <v>92811</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92835</v>
+        <v>92840</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26360,7 +26360,7 @@
         <v>128587583</v>
       </c>
       <c r="B243" t="n">
-        <v>92815</v>
+        <v>92823</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>128588720</v>
       </c>
       <c r="B244" t="n">
-        <v>91927</v>
+        <v>91933</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>128627830</v>
       </c>
       <c r="B245" t="n">
-        <v>90343</v>
+        <v>90349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>128627828</v>
       </c>
       <c r="B246" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -26784,7 +26784,7 @@
         <v>128627827</v>
       </c>
       <c r="B247" t="n">
-        <v>92811</v>
+        <v>92819</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92803</v>
+        <v>92811</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92840</v>
+        <v>92848</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92823</v>
+        <v>92831</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY251"/>
+  <dimension ref="A1:AY252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27282,6 +27282,123 @@
       </c>
       <c r="AY251" t="inlineStr"/>
     </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>129224542</v>
+      </c>
+      <c r="B252" t="n">
+        <v>90908</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>752869</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7092256</v>
+      </c>
+      <c r="S252" t="n">
+        <v>5</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>Tallåga vid stig</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga vid stig</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -26881,7 +26881,7 @@
         <v>128630176</v>
       </c>
       <c r="B248" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>128630172</v>
       </c>
       <c r="B249" t="n">
-        <v>92811</v>
+        <v>92818</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>128630168</v>
       </c>
       <c r="B250" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>128630170</v>
       </c>
       <c r="B251" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -27287,7 +27287,7 @@
         <v>129224542</v>
       </c>
       <c r="B252" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -27287,7 +27287,7 @@
         <v>129224542</v>
       </c>
       <c r="B252" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -27287,7 +27287,7 @@
         <v>129224542</v>
       </c>
       <c r="B252" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -27287,7 +27287,7 @@
         <v>129224542</v>
       </c>
       <c r="B252" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -27287,7 +27287,7 @@
         <v>129224542</v>
       </c>
       <c r="B252" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY228"/>
+  <dimension ref="A1:AZ228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16580294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718981</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934748</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/579968</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379672</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1731,6 +1781,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379678</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379680</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1925,6 +1985,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718972</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2022,6 +2087,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718973</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893423</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934774</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934775</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934776</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2519,6 +2609,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934777</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934778</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2713,6 +2813,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379731</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2810,6 +2915,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797534</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2907,6 +3017,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119892909</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3004,6 +3119,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893016</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3125,6 +3245,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934744</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3251,6 +3376,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403787</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3348,6 +3478,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718971</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3445,6 +3580,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403815</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3547,6 +3687,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818446</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3644,6 +3789,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61126647</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3741,6 +3891,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379665</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3838,6 +3993,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379670</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3935,6 +4095,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379686</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4032,6 +4197,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379689</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4129,6 +4299,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379691</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4226,6 +4401,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313604</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4333,6 +4513,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119495543</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4430,6 +4615,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718974</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4527,6 +4717,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718975</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4624,6 +4819,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718976</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4721,6 +4921,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718977</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4818,6 +5023,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718978</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4915,6 +5125,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718980</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5017,6 +5232,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797570</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5119,6 +5339,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797571</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5216,6 +5441,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797572</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5313,6 +5543,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797573</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5410,6 +5645,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797574</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5507,6 +5747,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797575</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5604,6 +5849,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797576</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5701,6 +5951,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797578</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5798,6 +6053,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797579</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5905,6 +6165,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808300</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6002,6 +6267,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893301</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6099,6 +6369,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893537</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6205,6 +6480,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934781</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6306,6 +6586,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934782</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6412,6 +6697,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934783</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6513,6 +6803,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934784</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6614,6 +6909,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934785</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6715,6 +7015,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934786</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6821,6 +7126,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934787</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6922,6 +7232,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934788</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7023,6 +7338,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934789</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7124,6 +7444,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934790</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7225,6 +7550,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934791</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7326,6 +7656,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934792</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7427,6 +7762,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934794</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7533,6 +7873,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934795</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7630,6 +7975,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934796</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7727,6 +8077,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934797</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7824,6 +8179,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934798</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7926,6 +8286,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630172</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8028,6 +8393,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818459</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8125,6 +8495,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379671</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8222,6 +8597,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379677</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8319,6 +8699,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379681</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8416,6 +8801,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379694</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8513,6 +8903,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379702</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8610,6 +9005,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379732</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8707,6 +9107,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718986</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8804,6 +9209,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718987</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8905,6 +9315,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797607</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9002,6 +9417,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797608</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9099,6 +9519,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797609</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9196,6 +9621,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797610</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9293,6 +9723,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797611</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9400,6 +9835,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808292</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9497,6 +9937,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893466</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9598,6 +10043,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934821</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9699,6 +10149,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934823</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9796,6 +10251,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16580297</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9893,6 +10353,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379666</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9990,6 +10455,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379667</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10087,6 +10557,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379674</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10184,6 +10659,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379676</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10281,6 +10761,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379685</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10378,6 +10863,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379690</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10475,6 +10965,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379693</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10572,6 +11067,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379695</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10669,6 +11169,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379699</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10766,6 +11271,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379700</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10863,6 +11373,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379734</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10960,6 +11475,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379735</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11057,6 +11577,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379741</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11154,6 +11679,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313701</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11261,6 +11791,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119495544</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11358,6 +11893,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718984</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11455,6 +11995,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718985</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11552,6 +12097,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797598</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11649,6 +12199,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797599</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11746,6 +12301,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797600</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11843,6 +12403,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797601</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11940,6 +12505,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797602</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12037,6 +12607,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797603</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12134,6 +12709,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797604</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12231,6 +12811,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797605</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12338,6 +12923,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808293</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12445,6 +13035,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808294</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12552,6 +13147,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808296</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12659,6 +13259,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808299</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12766,6 +13371,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808302</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12867,6 +13477,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934809</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12968,6 +13583,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934810</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13065,6 +13685,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934811</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13162,6 +13787,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934812</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13259,6 +13889,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934813</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13356,6 +13991,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934814</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13453,6 +14093,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934815</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13550,6 +14195,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934817</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13647,6 +14297,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934818</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13744,6 +14399,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934819</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13851,6 +14511,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120374050</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13948,6 +14613,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403835</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14045,6 +14715,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627827</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14142,6 +14817,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379673</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14244,6 +14924,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797561</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14346,6 +15031,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797562</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14456,6 +15146,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797563</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14558,6 +15253,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934771</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14660,6 +15360,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934772</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14766,6 +15471,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934773</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14883,6 +15593,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128587583</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14985,6 +15700,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224524</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15087,6 +15807,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224527</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15189,6 +15914,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224529</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15286,6 +16016,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16580296</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15383,6 +16118,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379703</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15480,6 +16220,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797564</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15577,6 +16322,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797565</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15674,6 +16424,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797566</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -15771,6 +16526,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797567</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -15878,6 +16638,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808307</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -15985,6 +16750,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808311</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16082,6 +16852,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119891959</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16179,6 +16954,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630170</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16276,6 +17056,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379668</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -16373,6 +17158,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379687</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -16470,6 +17260,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379727</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -16577,6 +17372,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808303</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -16674,6 +17474,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934755</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16771,6 +17576,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119892875</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -16873,6 +17683,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54818447</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -16970,6 +17785,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718958</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17072,6 +17892,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797537</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17169,6 +17994,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797538</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17266,6 +18096,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797539</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -17372,6 +18207,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119799792</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -17469,6 +18309,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893348</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -17571,6 +18416,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934758</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -17688,6 +18538,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224542</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -17794,6 +18649,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313635</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -17900,6 +18760,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313647</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18014,6 +18879,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313653</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18120,6 +18990,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797581</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18217,6 +19092,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797583</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18318,6 +19198,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934799</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -18415,6 +19300,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120403828</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -18516,6 +19406,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224532</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -18613,6 +19508,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379669</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -18710,6 +19610,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379675</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -18807,6 +19712,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379679</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -18904,6 +19814,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379682</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19001,6 +19916,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379683</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19098,6 +20018,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379692</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19195,6 +20120,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379696</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -19292,6 +20222,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379697</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -19389,6 +20324,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379698</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -19486,6 +20426,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379726</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -19583,6 +20528,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103379733</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -19689,6 +20639,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112313697</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -19786,6 +20741,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718982</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -19883,6 +20843,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718983</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -19985,6 +20950,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797594</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20091,6 +21061,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797595</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20188,6 +21163,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797597</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20289,6 +21269,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934806</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20390,6 +21375,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934808</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -20487,6 +21477,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718954</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -20584,6 +21579,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718955</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -20681,6 +21681,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797530</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -20778,6 +21783,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797531</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -20885,6 +21895,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119808304</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -20982,6 +21997,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119891898</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21079,6 +22099,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119892118</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21176,6 +22201,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893598</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -21278,6 +22308,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934752</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -21375,6 +22410,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934753</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -21476,6 +22516,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119934756</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -21573,6 +22618,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627826</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -21670,6 +22720,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627830</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -21797,6 +22852,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797560</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -21903,6 +22963,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119718957</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22005,6 +23070,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797532</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22107,6 +23177,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119797533</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -22214,6 +23289,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120374071</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -22333,6 +23413,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128630176</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -22460,6 +23545,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128588720</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -22555,6 +23645,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119891991</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -22650,6 +23745,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119892970</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -22745,6 +23845,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893175</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -22840,6 +23945,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893208</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -22935,6 +24045,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893225</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23030,6 +24145,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893329</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23125,6 +24245,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893430</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -23220,6 +24345,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893473</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -23315,6 +24445,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893483</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -23410,8 +24545,242 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893626</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ228"/>
+  <dimension ref="A1:AZ229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16962,10 +16962,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>103379668</v>
+        <v>135810620</v>
       </c>
       <c r="B157" t="n">
-        <v>92841</v>
+        <v>93357</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16973,37 +16973,46 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Fr.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752806</v>
+        <v>752746</v>
       </c>
       <c r="R157" t="n">
-        <v>7092648</v>
+        <v>7092355</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17027,12 +17036,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17047,24 +17056,24 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379668</t>
+          <t>https://artportalen.se/Sighting/135810620</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103379687</v>
+        <v>103379668</v>
       </c>
       <c r="B158" t="n">
         <v>92841</v>
@@ -17099,10 +17108,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752716</v>
+        <v>752806</v>
       </c>
       <c r="R158" t="n">
-        <v>7092478</v>
+        <v>7092648</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17160,13 +17169,13 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379687</t>
+          <t>https://artportalen.se/Sighting/103379668</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103379727</v>
+        <v>103379687</v>
       </c>
       <c r="B159" t="n">
         <v>92841</v>
@@ -17201,10 +17210,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>753013</v>
+        <v>752716</v>
       </c>
       <c r="R159" t="n">
-        <v>7092351</v>
+        <v>7092478</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17262,13 +17271,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379727</t>
+          <t>https://artportalen.se/Sighting/103379687</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119808303</v>
+        <v>103379727</v>
       </c>
       <c r="B160" t="n">
         <v>92841</v>
@@ -17303,13 +17312,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>752812</v>
+        <v>753013</v>
       </c>
       <c r="R160" t="n">
-        <v>7092433</v>
+        <v>7092351</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17333,22 +17342,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17363,24 +17362,24 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808303</t>
+          <t>https://artportalen.se/Sighting/103379727</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119934755</v>
+        <v>119808303</v>
       </c>
       <c r="B161" t="n">
         <v>92841</v>
@@ -17415,13 +17414,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752777</v>
+        <v>752812</v>
       </c>
       <c r="R161" t="n">
-        <v>7092472</v>
+        <v>7092433</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17445,12 +17444,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17465,27 +17474,27 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934755</t>
+          <t>https://artportalen.se/Sighting/119808303</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119892875</v>
+        <v>119934755</v>
       </c>
       <c r="B162" t="n">
-        <v>90522</v>
+        <v>92841</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17493,34 +17502,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4962</v>
+        <v>4745</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>752854</v>
+        <v>752777</v>
       </c>
       <c r="R162" t="n">
-        <v>7092368</v>
+        <v>7092472</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17567,27 +17576,27 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892875</t>
+          <t>https://artportalen.se/Sighting/119934755</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>54818447</v>
+        <v>119892875</v>
       </c>
       <c r="B163" t="n">
-        <v>91930</v>
+        <v>90522</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17595,34 +17604,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5442</v>
+        <v>4962</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>752938</v>
+        <v>752854</v>
       </c>
       <c r="R163" t="n">
-        <v>7092250</v>
+        <v>7092368</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17649,12 +17658,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17665,36 +17674,31 @@
       </c>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AI163" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54818447</t>
+          <t>https://artportalen.se/Sighting/119892875</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119718958</v>
+        <v>54818447</v>
       </c>
       <c r="B164" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17702,21 +17706,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17726,10 +17730,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752782</v>
+        <v>752938</v>
       </c>
       <c r="R164" t="n">
-        <v>7092728</v>
+        <v>7092250</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17756,12 +17760,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17772,28 +17776,33 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718958</t>
+          <t>https://artportalen.se/Sighting/54818447</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119797537</v>
+        <v>119718958</v>
       </c>
       <c r="B165" t="n">
         <v>93223</v>
@@ -17828,10 +17837,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752807</v>
+        <v>752782</v>
       </c>
       <c r="R165" t="n">
-        <v>7092369</v>
+        <v>7092728</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17858,17 +17867,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>I grop</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17883,24 +17887,24 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797537</t>
+          <t>https://artportalen.se/Sighting/119718958</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119797538</v>
+        <v>119797537</v>
       </c>
       <c r="B166" t="n">
         <v>93223</v>
@@ -17935,10 +17939,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752734</v>
+        <v>752807</v>
       </c>
       <c r="R166" t="n">
-        <v>7092340</v>
+        <v>7092369</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17973,6 +17977,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>I grop</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
@@ -17996,13 +18005,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797538</t>
+          <t>https://artportalen.se/Sighting/119797537</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119797539</v>
+        <v>119797538</v>
       </c>
       <c r="B167" t="n">
         <v>93223</v>
@@ -18037,10 +18046,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752737</v>
+        <v>752734</v>
       </c>
       <c r="R167" t="n">
-        <v>7092298</v>
+        <v>7092340</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18098,13 +18107,13 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797539</t>
+          <t>https://artportalen.se/Sighting/119797538</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119799792</v>
+        <v>119797539</v>
       </c>
       <c r="B168" t="n">
         <v>93223</v>
@@ -18133,19 +18142,16 @@
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752934</v>
+        <v>752737</v>
       </c>
       <c r="R168" t="n">
-        <v>7092206</v>
+        <v>7092298</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18180,18 +18186,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
-        </is>
-      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
       <c r="AE168" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF168" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -18209,13 +18209,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119799792</t>
+          <t>https://artportalen.se/Sighting/119797539</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119893348</v>
+        <v>119799792</v>
       </c>
       <c r="B169" t="n">
         <v>93223</v>
@@ -18244,16 +18244,19 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752893</v>
+        <v>752934</v>
       </c>
       <c r="R169" t="n">
-        <v>7092272</v>
+        <v>7092206</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18280,44 +18283,50 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
         </is>
       </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893348</t>
+          <t>https://artportalen.se/Sighting/119799792</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119934758</v>
+        <v>119893348</v>
       </c>
       <c r="B170" t="n">
         <v>93223</v>
@@ -18348,14 +18357,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752979</v>
+        <v>752893</v>
       </c>
       <c r="R170" t="n">
-        <v>7092382</v>
+        <v>7092272</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18390,11 +18399,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>Under silverlåga, tallgren vid basen</t>
-        </is>
-      </c>
       <c r="AD170" t="b">
         <v>0</v>
       </c>
@@ -18407,49 +18411,49 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934758</t>
+          <t>https://artportalen.se/Sighting/119893348</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129224542</v>
+        <v>119934758</v>
       </c>
       <c r="B171" t="n">
-        <v>91282</v>
+        <v>93223</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5685</v>
+        <v>5448</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18459,13 +18463,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752869</v>
+        <v>752979</v>
       </c>
       <c r="R171" t="n">
-        <v>7092256</v>
+        <v>7092382</v>
       </c>
       <c r="S171" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18489,12 +18493,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18505,26 +18514,6 @@
       </c>
       <c r="AG171" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>Tallåga vid stig</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga vid stig</t>
-        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
@@ -18540,63 +18529,54 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224542</t>
+          <t>https://artportalen.se/Sighting/119934758</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112313635</v>
+        <v>129224542</v>
       </c>
       <c r="B172" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752817</v>
+        <v>752869</v>
       </c>
       <c r="R172" t="n">
-        <v>7092607</v>
+        <v>7092256</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18620,12 +18600,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18636,6 +18616,26 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>Tallåga vid stig</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga vid stig</t>
+        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
@@ -18651,13 +18651,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313635</t>
+          <t>https://artportalen.se/Sighting/129224542</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>112313647</v>
+        <v>112313635</v>
       </c>
       <c r="B173" t="n">
         <v>93235</v>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -18701,10 +18701,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752846</v>
+        <v>752817</v>
       </c>
       <c r="R173" t="n">
-        <v>7092719</v>
+        <v>7092607</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18762,13 +18762,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313647</t>
+          <t>https://artportalen.se/Sighting/112313635</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>112313653</v>
+        <v>112313647</v>
       </c>
       <c r="B174" t="n">
         <v>93235</v>
@@ -18798,7 +18798,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -18806,18 +18806,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752936</v>
+        <v>752846</v>
       </c>
       <c r="R174" t="n">
-        <v>7092682</v>
+        <v>7092719</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18852,18 +18850,12 @@
           <t>2023-09-24</t>
         </is>
       </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD174" t="b">
         <v>0</v>
       </c>
       <c r="AE174" t="b">
         <v>0</v>
       </c>
-      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
@@ -18881,13 +18873,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313653</t>
+          <t>https://artportalen.se/Sighting/112313647</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119797581</v>
+        <v>112313653</v>
       </c>
       <c r="B175" t="n">
         <v>93235</v>
@@ -18917,19 +18909,26 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752686</v>
+        <v>752936</v>
       </c>
       <c r="R175" t="n">
-        <v>7092272</v>
+        <v>7092682</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18956,17 +18955,17 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Nära stigen</t>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18975,6 +18974,7 @@
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -18992,13 +18992,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797581</t>
+          <t>https://artportalen.se/Sighting/112313653</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119797583</v>
+        <v>119797581</v>
       </c>
       <c r="B176" t="n">
         <v>93235</v>
@@ -19026,17 +19026,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752719</v>
+        <v>752686</v>
       </c>
       <c r="R176" t="n">
-        <v>7092452</v>
+        <v>7092272</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19071,6 +19075,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>Nära stigen</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
@@ -19094,13 +19103,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797583</t>
+          <t>https://artportalen.se/Sighting/119797581</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119934799</v>
+        <v>119797583</v>
       </c>
       <c r="B177" t="n">
         <v>93235</v>
@@ -19128,21 +19137,17 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752754</v>
+        <v>752719</v>
       </c>
       <c r="R177" t="n">
-        <v>7092559</v>
+        <v>7092452</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19169,12 +19174,12 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19200,13 +19205,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934799</t>
+          <t>https://artportalen.se/Sighting/119797583</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>120403828</v>
+        <v>119934799</v>
       </c>
       <c r="B178" t="n">
         <v>93235</v>
@@ -19234,17 +19239,21 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752970</v>
+        <v>752754</v>
       </c>
       <c r="R178" t="n">
-        <v>7092257</v>
+        <v>7092559</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19271,12 +19280,12 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19302,13 +19311,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403828</t>
+          <t>https://artportalen.se/Sighting/119934799</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129224532</v>
+        <v>120403828</v>
       </c>
       <c r="B179" t="n">
         <v>93235</v>
@@ -19336,24 +19345,20 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752940</v>
+        <v>752970</v>
       </c>
       <c r="R179" t="n">
-        <v>7092218</v>
+        <v>7092257</v>
       </c>
       <c r="S179" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -19377,12 +19382,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19408,54 +19413,58 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224532</t>
+          <t>https://artportalen.se/Sighting/120403828</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>103379669</v>
+        <v>129224532</v>
       </c>
       <c r="B180" t="n">
-        <v>90691</v>
+        <v>93235</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752766</v>
+        <v>752940</v>
       </c>
       <c r="R180" t="n">
-        <v>7092626</v>
+        <v>7092218</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19479,12 +19488,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19499,24 +19508,24 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379669</t>
+          <t>https://artportalen.se/Sighting/129224532</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>103379675</v>
+        <v>103379669</v>
       </c>
       <c r="B181" t="n">
         <v>90691</v>
@@ -19551,10 +19560,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752854</v>
+        <v>752766</v>
       </c>
       <c r="R181" t="n">
-        <v>7092609</v>
+        <v>7092626</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19612,13 +19621,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379675</t>
+          <t>https://artportalen.se/Sighting/103379669</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>103379679</v>
+        <v>103379675</v>
       </c>
       <c r="B182" t="n">
         <v>90691</v>
@@ -19653,10 +19662,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752820</v>
+        <v>752854</v>
       </c>
       <c r="R182" t="n">
-        <v>7092595</v>
+        <v>7092609</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19714,13 +19723,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379679</t>
+          <t>https://artportalen.se/Sighting/103379675</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103379682</v>
+        <v>103379679</v>
       </c>
       <c r="B183" t="n">
         <v>90691</v>
@@ -19755,10 +19764,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752789</v>
+        <v>752820</v>
       </c>
       <c r="R183" t="n">
-        <v>7092541</v>
+        <v>7092595</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19816,13 +19825,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379682</t>
+          <t>https://artportalen.se/Sighting/103379679</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>103379683</v>
+        <v>103379682</v>
       </c>
       <c r="B184" t="n">
         <v>90691</v>
@@ -19857,10 +19866,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752816</v>
+        <v>752789</v>
       </c>
       <c r="R184" t="n">
-        <v>7092517</v>
+        <v>7092541</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19918,13 +19927,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379683</t>
+          <t>https://artportalen.se/Sighting/103379682</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103379692</v>
+        <v>103379683</v>
       </c>
       <c r="B185" t="n">
         <v>90691</v>
@@ -19959,10 +19968,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752778</v>
+        <v>752816</v>
       </c>
       <c r="R185" t="n">
-        <v>7092448</v>
+        <v>7092517</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20020,13 +20029,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379692</t>
+          <t>https://artportalen.se/Sighting/103379683</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>103379696</v>
+        <v>103379692</v>
       </c>
       <c r="B186" t="n">
         <v>90691</v>
@@ -20061,10 +20070,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752758</v>
+        <v>752778</v>
       </c>
       <c r="R186" t="n">
-        <v>7092310</v>
+        <v>7092448</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20122,13 +20131,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379696</t>
+          <t>https://artportalen.se/Sighting/103379692</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103379697</v>
+        <v>103379696</v>
       </c>
       <c r="B187" t="n">
         <v>90691</v>
@@ -20163,10 +20172,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752764</v>
+        <v>752758</v>
       </c>
       <c r="R187" t="n">
-        <v>7092301</v>
+        <v>7092310</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20224,13 +20233,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379697</t>
+          <t>https://artportalen.se/Sighting/103379696</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>103379698</v>
+        <v>103379697</v>
       </c>
       <c r="B188" t="n">
         <v>90691</v>
@@ -20265,10 +20274,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752734</v>
+        <v>752764</v>
       </c>
       <c r="R188" t="n">
-        <v>7092295</v>
+        <v>7092301</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20326,13 +20335,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379698</t>
+          <t>https://artportalen.se/Sighting/103379697</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>103379726</v>
+        <v>103379698</v>
       </c>
       <c r="B189" t="n">
         <v>90691</v>
@@ -20367,10 +20376,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752993</v>
+        <v>752734</v>
       </c>
       <c r="R189" t="n">
-        <v>7092362</v>
+        <v>7092295</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20428,13 +20437,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379726</t>
+          <t>https://artportalen.se/Sighting/103379698</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>103379733</v>
+        <v>103379726</v>
       </c>
       <c r="B190" t="n">
         <v>90691</v>
@@ -20469,10 +20478,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>753013</v>
+        <v>752993</v>
       </c>
       <c r="R190" t="n">
-        <v>7092487</v>
+        <v>7092362</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20530,13 +20539,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379733</t>
+          <t>https://artportalen.se/Sighting/103379726</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>112313697</v>
+        <v>103379733</v>
       </c>
       <c r="B191" t="n">
         <v>90691</v>
@@ -20564,26 +20573,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>752888</v>
+        <v>753013</v>
       </c>
       <c r="R191" t="n">
-        <v>7092644</v>
+        <v>7092487</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20610,12 +20610,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20630,24 +20630,24 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313697</t>
+          <t>https://artportalen.se/Sighting/103379733</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119718982</v>
+        <v>112313697</v>
       </c>
       <c r="B192" t="n">
         <v>90691</v>
@@ -20675,17 +20675,26 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752792</v>
+        <v>752888</v>
       </c>
       <c r="R192" t="n">
-        <v>7092573</v>
+        <v>7092644</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20712,12 +20721,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20732,24 +20741,24 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718982</t>
+          <t>https://artportalen.se/Sighting/112313697</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119718983</v>
+        <v>119718982</v>
       </c>
       <c r="B193" t="n">
         <v>90691</v>
@@ -20784,10 +20793,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752779</v>
+        <v>752792</v>
       </c>
       <c r="R193" t="n">
-        <v>7092474</v>
+        <v>7092573</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20845,13 +20854,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718983</t>
+          <t>https://artportalen.se/Sighting/119718982</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119797594</v>
+        <v>119718983</v>
       </c>
       <c r="B194" t="n">
         <v>90691</v>
@@ -20886,10 +20895,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752842</v>
+        <v>752779</v>
       </c>
       <c r="R194" t="n">
-        <v>7092347</v>
+        <v>7092474</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20916,17 +20925,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20941,24 +20945,24 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797594</t>
+          <t>https://artportalen.se/Sighting/119718983</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119797595</v>
+        <v>119797594</v>
       </c>
       <c r="B195" t="n">
         <v>90691</v>
@@ -20986,21 +20990,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752803</v>
+        <v>752842</v>
       </c>
       <c r="R195" t="n">
-        <v>7092370</v>
+        <v>7092347</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21037,7 +21037,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Bredvid grop</t>
+          <t>Äldre fruktkropp</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21063,13 +21063,13 @@
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797595</t>
+          <t>https://artportalen.se/Sighting/119797594</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119797597</v>
+        <v>119797595</v>
       </c>
       <c r="B196" t="n">
         <v>90691</v>
@@ -21097,17 +21097,21 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752839</v>
+        <v>752803</v>
       </c>
       <c r="R196" t="n">
-        <v>7092201</v>
+        <v>7092370</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21142,6 +21146,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Bredvid grop</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
@@ -21165,13 +21174,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797597</t>
+          <t>https://artportalen.se/Sighting/119797595</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119934806</v>
+        <v>119797597</v>
       </c>
       <c r="B197" t="n">
         <v>90691</v>
@@ -21199,21 +21208,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752816</v>
+        <v>752839</v>
       </c>
       <c r="R197" t="n">
-        <v>7092714</v>
+        <v>7092201</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21240,12 +21245,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21271,13 +21276,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934806</t>
+          <t>https://artportalen.se/Sighting/119797597</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934808</v>
+        <v>119934806</v>
       </c>
       <c r="B198" t="n">
         <v>90691</v>
@@ -21316,10 +21321,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752819</v>
+        <v>752816</v>
       </c>
       <c r="R198" t="n">
-        <v>7092515</v>
+        <v>7092714</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21377,16 +21382,16 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934808</t>
+          <t>https://artportalen.se/Sighting/119934806</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119718954</v>
+        <v>119934808</v>
       </c>
       <c r="B199" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21394,34 +21399,38 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752778</v>
+        <v>752819</v>
       </c>
       <c r="R199" t="n">
-        <v>7092543</v>
+        <v>7092515</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21448,12 +21457,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21468,24 +21477,24 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718954</t>
+          <t>https://artportalen.se/Sighting/119934808</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119718955</v>
+        <v>119718954</v>
       </c>
       <c r="B200" t="n">
         <v>90710</v>
@@ -21520,10 +21529,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752793</v>
+        <v>752778</v>
       </c>
       <c r="R200" t="n">
-        <v>7092549</v>
+        <v>7092543</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21581,13 +21590,13 @@
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718955</t>
+          <t>https://artportalen.se/Sighting/119718954</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119797530</v>
+        <v>119718955</v>
       </c>
       <c r="B201" t="n">
         <v>90710</v>
@@ -21622,10 +21631,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752727</v>
+        <v>752793</v>
       </c>
       <c r="R201" t="n">
-        <v>7092459</v>
+        <v>7092549</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21652,19 +21661,19 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -21672,24 +21681,24 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797530</t>
+          <t>https://artportalen.se/Sighting/119718955</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119797531</v>
+        <v>119797530</v>
       </c>
       <c r="B202" t="n">
         <v>90710</v>
@@ -21724,10 +21733,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752941</v>
+        <v>752727</v>
       </c>
       <c r="R202" t="n">
-        <v>7092217</v>
+        <v>7092459</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21785,13 +21794,13 @@
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797531</t>
+          <t>https://artportalen.se/Sighting/119797530</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119808304</v>
+        <v>119797531</v>
       </c>
       <c r="B203" t="n">
         <v>90710</v>
@@ -21826,13 +21835,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752773</v>
+        <v>752941</v>
       </c>
       <c r="R203" t="n">
-        <v>7092434</v>
+        <v>7092217</v>
       </c>
       <c r="S203" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -21859,26 +21868,16 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -21886,24 +21885,24 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808304</t>
+          <t>https://artportalen.se/Sighting/119797531</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119891898</v>
+        <v>119808304</v>
       </c>
       <c r="B204" t="n">
         <v>90710</v>
@@ -21938,13 +21937,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752740</v>
+        <v>752773</v>
       </c>
       <c r="R204" t="n">
-        <v>7092396</v>
+        <v>7092434</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21968,12 +21967,22 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -21988,24 +21997,24 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891898</t>
+          <t>https://artportalen.se/Sighting/119808304</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119892118</v>
+        <v>119891898</v>
       </c>
       <c r="B205" t="n">
         <v>90710</v>
@@ -22036,14 +22045,14 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752838</v>
+        <v>752740</v>
       </c>
       <c r="R205" t="n">
-        <v>7092399</v>
+        <v>7092396</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22101,13 +22110,13 @@
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892118</t>
+          <t>https://artportalen.se/Sighting/119891898</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119893598</v>
+        <v>119892118</v>
       </c>
       <c r="B206" t="n">
         <v>90710</v>
@@ -22142,10 +22151,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752767</v>
+        <v>752838</v>
       </c>
       <c r="R206" t="n">
-        <v>7092395</v>
+        <v>7092399</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22203,13 +22212,13 @@
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893598</t>
+          <t>https://artportalen.se/Sighting/119892118</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119934752</v>
+        <v>119893598</v>
       </c>
       <c r="B207" t="n">
         <v>90710</v>
@@ -22240,14 +22249,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752794</v>
+        <v>752767</v>
       </c>
       <c r="R207" t="n">
-        <v>7092570</v>
+        <v>7092395</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22282,11 +22291,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD207" t="b">
         <v>0</v>
       </c>
@@ -22299,24 +22303,24 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934752</t>
+          <t>https://artportalen.se/Sighting/119893598</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934753</v>
+        <v>119934752</v>
       </c>
       <c r="B208" t="n">
         <v>90710</v>
@@ -22351,10 +22355,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752888</v>
+        <v>752794</v>
       </c>
       <c r="R208" t="n">
-        <v>7092677</v>
+        <v>7092570</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22389,6 +22393,11 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
@@ -22412,13 +22421,13 @@
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934753</t>
+          <t>https://artportalen.se/Sighting/119934752</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934756</v>
+        <v>119934753</v>
       </c>
       <c r="B209" t="n">
         <v>90710</v>
@@ -22446,21 +22455,17 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752783</v>
+        <v>752888</v>
       </c>
       <c r="R209" t="n">
-        <v>7092657</v>
+        <v>7092677</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22499,7 +22504,7 @@
         <v>0</v>
       </c>
       <c r="AE209" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG209" t="b">
         <v>0</v>
@@ -22518,13 +22523,13 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934756</t>
+          <t>https://artportalen.se/Sighting/119934753</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128627826</v>
+        <v>119934756</v>
       </c>
       <c r="B210" t="n">
         <v>90710</v>
@@ -22552,17 +22557,21 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>753005</v>
+        <v>752783</v>
       </c>
       <c r="R210" t="n">
-        <v>7092360</v>
+        <v>7092657</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22589,19 +22598,19 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -22609,24 +22618,24 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627826</t>
+          <t>https://artportalen.se/Sighting/119934756</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128627830</v>
+        <v>128627826</v>
       </c>
       <c r="B211" t="n">
         <v>90710</v>
@@ -22661,10 +22670,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>752818</v>
+        <v>753005</v>
       </c>
       <c r="R211" t="n">
-        <v>7092471</v>
+        <v>7092360</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22722,56 +22731,51 @@
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627830</t>
+          <t>https://artportalen.se/Sighting/128627826</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119797560</v>
+        <v>128627830</v>
       </c>
       <c r="B212" t="n">
-        <v>57950</v>
+        <v>90710</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752728</v>
+        <v>752818</v>
       </c>
       <c r="R212" t="n">
-        <v>7092269</v>
+        <v>7092471</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22798,17 +22802,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22819,83 +22818,59 @@
       </c>
       <c r="AG212" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ212" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL212" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797560</t>
+          <t>https://artportalen.se/Sighting/128627830</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119718957</v>
+        <v>119797560</v>
       </c>
       <c r="B213" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -22904,10 +22879,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752907</v>
+        <v>752728</v>
       </c>
       <c r="R213" t="n">
-        <v>7092425</v>
+        <v>7092269</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22934,12 +22909,17 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22950,28 +22930,48 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL213" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718957</t>
+          <t>https://artportalen.se/Sighting/119797560</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119797532</v>
+        <v>119718957</v>
       </c>
       <c r="B214" t="n">
         <v>58114</v>
@@ -22999,10 +22999,14 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -23011,10 +23015,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752730</v>
+        <v>752907</v>
       </c>
       <c r="R214" t="n">
-        <v>7092301</v>
+        <v>7092425</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23041,12 +23045,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23061,24 +23065,24 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797532</t>
+          <t>https://artportalen.se/Sighting/119718957</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119797533</v>
+        <v>119797532</v>
       </c>
       <c r="B215" t="n">
         <v>58114</v>
@@ -23118,10 +23122,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752826</v>
+        <v>752730</v>
       </c>
       <c r="R215" t="n">
-        <v>7092234</v>
+        <v>7092301</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23179,13 +23183,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797533</t>
+          <t>https://artportalen.se/Sighting/119797532</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>120374071</v>
+        <v>119797533</v>
       </c>
       <c r="B216" t="n">
         <v>58114</v>
@@ -23214,19 +23218,24 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752960</v>
+        <v>752826</v>
       </c>
       <c r="R216" t="n">
-        <v>7092251</v>
+        <v>7092234</v>
       </c>
       <c r="S216" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -23250,22 +23259,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z216" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB216" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23280,24 +23279,24 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120374071</t>
+          <t>https://artportalen.se/Sighting/119797533</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128630176</v>
+        <v>120374071</v>
       </c>
       <c r="B217" t="n">
         <v>58114</v>
@@ -23325,32 +23324,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752927</v>
+        <v>752960</v>
       </c>
       <c r="R217" t="n">
-        <v>7092361</v>
+        <v>7092251</v>
       </c>
       <c r="S217" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23374,22 +23361,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23404,27 +23391,27 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128630176</t>
+          <t>https://artportalen.se/Sighting/120374071</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128588720</v>
+        <v>128630176</v>
       </c>
       <c r="B218" t="n">
-        <v>92328</v>
+        <v>58114</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -23432,37 +23419,49 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6040162</v>
+        <v>103021</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752891</v>
+        <v>752927</v>
       </c>
       <c r="R218" t="n">
-        <v>7092444</v>
+        <v>7092361</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23491,7 +23490,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -23501,12 +23500,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Talltorraka, med klibbticka och är kottesmedja</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23517,21 +23511,6 @@
       </c>
       <c r="AG218" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ218" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
@@ -23547,16 +23526,16 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128588720</t>
+          <t>https://artportalen.se/Sighting/128630176</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119891991</v>
+        <v>128588720</v>
       </c>
       <c r="B219" t="n">
-        <v>93218</v>
+        <v>92328</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23564,31 +23543,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6331648</v>
+        <v>6040162</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752740</v>
+        <v>752891</v>
       </c>
       <c r="R219" t="n">
-        <v>7092396</v>
+        <v>7092444</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -23615,12 +23597,27 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Talltorraka, med klibbticka och är kottesmedja</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23629,31 +23626,45 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891991</t>
+          <t>https://artportalen.se/Sighting/128588720</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119892970</v>
+        <v>119891991</v>
       </c>
       <c r="B220" t="n">
         <v>93218</v>
@@ -23685,10 +23696,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752853</v>
+        <v>752740</v>
       </c>
       <c r="R220" t="n">
-        <v>7092386</v>
+        <v>7092396</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23747,13 +23758,13 @@
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892970</t>
+          <t>https://artportalen.se/Sighting/119891991</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119893175</v>
+        <v>119892970</v>
       </c>
       <c r="B221" t="n">
         <v>93218</v>
@@ -23785,10 +23796,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752982</v>
+        <v>752853</v>
       </c>
       <c r="R221" t="n">
-        <v>7092371</v>
+        <v>7092386</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23847,13 +23858,13 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893175</t>
+          <t>https://artportalen.se/Sighting/119892970</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119893208</v>
+        <v>119893175</v>
       </c>
       <c r="B222" t="n">
         <v>93218</v>
@@ -23885,10 +23896,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752928</v>
+        <v>752982</v>
       </c>
       <c r="R222" t="n">
-        <v>7092309</v>
+        <v>7092371</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23947,13 +23958,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893208</t>
+          <t>https://artportalen.se/Sighting/119893175</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119893225</v>
+        <v>119893208</v>
       </c>
       <c r="B223" t="n">
         <v>93218</v>
@@ -23985,10 +23996,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752927</v>
+        <v>752928</v>
       </c>
       <c r="R223" t="n">
-        <v>7092298</v>
+        <v>7092309</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24047,13 +24058,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893225</t>
+          <t>https://artportalen.se/Sighting/119893208</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119893329</v>
+        <v>119893225</v>
       </c>
       <c r="B224" t="n">
         <v>93218</v>
@@ -24085,10 +24096,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752893</v>
+        <v>752927</v>
       </c>
       <c r="R224" t="n">
-        <v>7092272</v>
+        <v>7092298</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24147,13 +24158,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893329</t>
+          <t>https://artportalen.se/Sighting/119893225</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119893430</v>
+        <v>119893329</v>
       </c>
       <c r="B225" t="n">
         <v>93218</v>
@@ -24185,10 +24196,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752897</v>
+        <v>752893</v>
       </c>
       <c r="R225" t="n">
-        <v>7092235</v>
+        <v>7092272</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24247,13 +24258,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893430</t>
+          <t>https://artportalen.se/Sighting/119893329</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119893473</v>
+        <v>119893430</v>
       </c>
       <c r="B226" t="n">
         <v>93218</v>
@@ -24285,10 +24296,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752827</v>
+        <v>752897</v>
       </c>
       <c r="R226" t="n">
-        <v>7092232</v>
+        <v>7092235</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24347,13 +24358,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893473</t>
+          <t>https://artportalen.se/Sighting/119893430</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119893483</v>
+        <v>119893473</v>
       </c>
       <c r="B227" t="n">
         <v>93218</v>
@@ -24385,10 +24396,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752795</v>
+        <v>752827</v>
       </c>
       <c r="R227" t="n">
-        <v>7092265</v>
+        <v>7092232</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24447,13 +24458,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893483</t>
+          <t>https://artportalen.se/Sighting/119893473</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119893626</v>
+        <v>119893483</v>
       </c>
       <c r="B228" t="n">
         <v>93218</v>
@@ -24485,10 +24496,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752767</v>
+        <v>752795</v>
       </c>
       <c r="R228" t="n">
-        <v>7092396</v>
+        <v>7092265</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24546,6 +24557,106 @@
       </c>
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893483</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>119893626</v>
+      </c>
+      <c r="B229" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>752767</v>
+      </c>
+      <c r="R229" t="n">
+        <v>7092396</v>
+      </c>
+      <c r="S229" t="n">
+        <v>10</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119893626</t>
         </is>
@@ -24780,6 +24891,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14723,48 +14723,59 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>103379673</v>
+        <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93201</v>
+        <v>93347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>752869</v>
+        <v>752746</v>
       </c>
       <c r="R136" t="n">
-        <v>7092623</v>
+        <v>7092355</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14788,12 +14799,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14802,30 +14813,31 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379673</t>
+          <t>https://artportalen.se/Sighting/135810620</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119797561</v>
+        <v>103379673</v>
       </c>
       <c r="B137" t="n">
         <v>93201</v>
@@ -14860,10 +14872,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752774</v>
+        <v>752869</v>
       </c>
       <c r="R137" t="n">
-        <v>7092461</v>
+        <v>7092623</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14890,17 +14902,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14915,24 +14922,24 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797561</t>
+          <t>https://artportalen.se/Sighting/103379673</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797562</v>
+        <v>119797561</v>
       </c>
       <c r="B138" t="n">
         <v>93201</v>
@@ -14967,10 +14974,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752870</v>
+        <v>752774</v>
       </c>
       <c r="R138" t="n">
-        <v>7092247</v>
+        <v>7092461</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15007,7 +15014,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Under silverlåga vid stig</t>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15033,13 +15040,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797562</t>
+          <t>https://artportalen.se/Sighting/119797561</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797563</v>
+        <v>119797562</v>
       </c>
       <c r="B139" t="n">
         <v>93201</v>
@@ -15067,24 +15074,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752807</v>
+        <v>752870</v>
       </c>
       <c r="R139" t="n">
-        <v>7092367</v>
+        <v>7092247</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15130,7 +15130,6 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -15148,13 +15147,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797563</t>
+          <t>https://artportalen.se/Sighting/119797562</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119934771</v>
+        <v>119797563</v>
       </c>
       <c r="B140" t="n">
         <v>93201</v>
@@ -15182,17 +15181,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>752765</v>
+        <v>752807</v>
       </c>
       <c r="R140" t="n">
-        <v>7092632</v>
+        <v>7092367</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15219,17 +15225,17 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Under tunn tallåga</t>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15238,6 +15244,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15255,13 +15262,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934771</t>
+          <t>https://artportalen.se/Sighting/119797563</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119934772</v>
+        <v>119934771</v>
       </c>
       <c r="B141" t="n">
         <v>93201</v>
@@ -15296,10 +15303,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>752757</v>
+        <v>752765</v>
       </c>
       <c r="R141" t="n">
-        <v>7092617</v>
+        <v>7092632</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15336,7 +15343,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i mossmatta</t>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15362,13 +15369,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934772</t>
+          <t>https://artportalen.se/Sighting/119934771</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119934773</v>
+        <v>119934772</v>
       </c>
       <c r="B142" t="n">
         <v>93201</v>
@@ -15396,21 +15403,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>752853</v>
+        <v>752757</v>
       </c>
       <c r="R142" t="n">
-        <v>7092405</v>
+        <v>7092617</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15447,7 +15450,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15473,13 +15476,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934773</t>
+          <t>https://artportalen.se/Sighting/119934772</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128587583</v>
+        <v>119934773</v>
       </c>
       <c r="B143" t="n">
         <v>93201</v>
@@ -15507,20 +15510,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>752876</v>
+        <v>752853</v>
       </c>
       <c r="R143" t="n">
-        <v>7092345</v>
+        <v>7092405</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -15544,27 +15551,17 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Under tallgren nedsänkt i mossa. Flera sammanväxta fruktkroppar</t>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15575,11 +15572,6 @@
       </c>
       <c r="AG143" t="b">
         <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
@@ -15595,13 +15587,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128587583</t>
+          <t>https://artportalen.se/Sighting/119934773</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129224524</v>
+        <v>128587583</v>
       </c>
       <c r="B144" t="n">
         <v>93201</v>
@@ -15636,10 +15628,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752870</v>
+        <v>752876</v>
       </c>
       <c r="R144" t="n">
-        <v>7092608</v>
+        <v>7092345</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -15666,17 +15658,27 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Silverlåga, vid basen</t>
+          <t>Under tallgren nedsänkt i mossa. Flera sammanväxta fruktkroppar</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15687,6 +15689,11 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -15702,13 +15709,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224524</t>
+          <t>https://artportalen.se/Sighting/128587583</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129224527</v>
+        <v>129224524</v>
       </c>
       <c r="B145" t="n">
         <v>93201</v>
@@ -15743,10 +15750,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752884</v>
+        <v>752870</v>
       </c>
       <c r="R145" t="n">
-        <v>7092646</v>
+        <v>7092608</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15783,7 +15790,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Många sammanväxta fruktkroppar under tallåga</t>
+          <t>Silverlåga, vid basen</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15809,13 +15816,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224527</t>
+          <t>https://artportalen.se/Sighting/129224524</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129224529</v>
+        <v>129224527</v>
       </c>
       <c r="B146" t="n">
         <v>93201</v>
@@ -15850,10 +15857,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752861</v>
+        <v>752884</v>
       </c>
       <c r="R146" t="n">
-        <v>7092617</v>
+        <v>7092646</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15890,7 +15897,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Kort kapad äldre tallåga, mossbevuxen</t>
+          <t>Många sammanväxta fruktkroppar under tallåga</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15916,38 +15923,38 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224529</t>
+          <t>https://artportalen.se/Sighting/129224527</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>16580296</v>
+        <v>129224529</v>
       </c>
       <c r="B147" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15957,13 +15964,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752967</v>
+        <v>752861</v>
       </c>
       <c r="R147" t="n">
-        <v>7092346</v>
+        <v>7092617</v>
       </c>
       <c r="S147" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -15987,12 +15994,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Kort kapad äldre tallåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16007,24 +16019,24 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16580296</t>
+          <t>https://artportalen.se/Sighting/129224529</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>103379703</v>
+        <v>16580296</v>
       </c>
       <c r="B148" t="n">
         <v>93209</v>
@@ -16059,10 +16071,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752959</v>
+        <v>752967</v>
       </c>
       <c r="R148" t="n">
-        <v>7092217</v>
+        <v>7092346</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16089,12 +16101,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16109,24 +16121,24 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379703</t>
+          <t>https://artportalen.se/Sighting/16580296</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119797564</v>
+        <v>103379703</v>
       </c>
       <c r="B149" t="n">
         <v>93209</v>
@@ -16161,10 +16173,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752716</v>
+        <v>752959</v>
       </c>
       <c r="R149" t="n">
-        <v>7092384</v>
+        <v>7092217</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16191,12 +16203,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16211,24 +16223,24 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797564</t>
+          <t>https://artportalen.se/Sighting/103379703</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119797565</v>
+        <v>119797564</v>
       </c>
       <c r="B150" t="n">
         <v>93209</v>
@@ -16263,10 +16275,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752765</v>
+        <v>752716</v>
       </c>
       <c r="R150" t="n">
-        <v>7092391</v>
+        <v>7092384</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16324,13 +16336,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797565</t>
+          <t>https://artportalen.se/Sighting/119797564</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119797566</v>
+        <v>119797565</v>
       </c>
       <c r="B151" t="n">
         <v>93209</v>
@@ -16365,10 +16377,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752868</v>
+        <v>752765</v>
       </c>
       <c r="R151" t="n">
-        <v>7092254</v>
+        <v>7092391</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16426,13 +16438,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797566</t>
+          <t>https://artportalen.se/Sighting/119797565</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119797567</v>
+        <v>119797566</v>
       </c>
       <c r="B152" t="n">
         <v>93209</v>
@@ -16467,10 +16479,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752807</v>
+        <v>752868</v>
       </c>
       <c r="R152" t="n">
-        <v>7092251</v>
+        <v>7092254</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16528,13 +16540,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797567</t>
+          <t>https://artportalen.se/Sighting/119797566</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119808307</v>
+        <v>119797567</v>
       </c>
       <c r="B153" t="n">
         <v>93209</v>
@@ -16569,13 +16581,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752764</v>
+        <v>752807</v>
       </c>
       <c r="R153" t="n">
-        <v>7092409</v>
+        <v>7092251</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16602,19 +16614,9 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16629,24 +16631,24 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808307</t>
+          <t>https://artportalen.se/Sighting/119797567</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808311</v>
+        <v>119808307</v>
       </c>
       <c r="B154" t="n">
         <v>93209</v>
@@ -16681,10 +16683,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752771</v>
+        <v>752764</v>
       </c>
       <c r="R154" t="n">
-        <v>7092333</v>
+        <v>7092409</v>
       </c>
       <c r="S154" t="n">
         <v>25</v>
@@ -16716,7 +16718,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16726,7 +16728,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16752,13 +16754,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808311</t>
+          <t>https://artportalen.se/Sighting/119808307</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119891959</v>
+        <v>119808311</v>
       </c>
       <c r="B155" t="n">
         <v>93209</v>
@@ -16789,17 +16791,17 @@
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752740</v>
+        <v>752771</v>
       </c>
       <c r="R155" t="n">
-        <v>7092396</v>
+        <v>7092333</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16823,12 +16825,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16843,24 +16855,24 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891959</t>
+          <t>https://artportalen.se/Sighting/119808311</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128630170</v>
+        <v>119891959</v>
       </c>
       <c r="B156" t="n">
         <v>93209</v>
@@ -16891,17 +16903,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752914</v>
+        <v>752740</v>
       </c>
       <c r="R156" t="n">
-        <v>7092346</v>
+        <v>7092396</v>
       </c>
       <c r="S156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16925,12 +16937,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16945,27 +16957,27 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128630170</t>
+          <t>https://artportalen.se/Sighting/119891959</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>135810620</v>
+        <v>128630170</v>
       </c>
       <c r="B157" t="n">
-        <v>93357</v>
+        <v>93209</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16990,26 +17002,17 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752746</v>
+        <v>752914</v>
       </c>
       <c r="R157" t="n">
-        <v>7092355</v>
+        <v>7092346</v>
       </c>
       <c r="S157" t="n">
         <v>5</v>
@@ -17036,12 +17039,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17067,7 +17070,7 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135810620</t>
+          <t>https://artportalen.se/Sighting/128630170</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14726,7 +14726,7 @@
         <v>135810620</v>
       </c>
       <c r="B136" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ229"/>
+  <dimension ref="A1:AZ231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10157,10 +10157,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>16580297</v>
+        <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93197</v>
+        <v>93372</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10168,37 +10168,46 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kullaskogen lilla sandgrop , Kullaskogen lilla sandgrop , Vb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>753031</v>
+        <v>753025</v>
       </c>
       <c r="R92" t="n">
-        <v>7092419</v>
+        <v>7092436</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10222,12 +10231,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10242,24 +10251,24 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16580297</t>
+          <t>https://artportalen.se/Sighting/136339695</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>103379666</v>
+        <v>16580297</v>
       </c>
       <c r="B93" t="n">
         <v>93197</v>
@@ -10294,10 +10303,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>752811</v>
+        <v>753031</v>
       </c>
       <c r="R93" t="n">
-        <v>7092710</v>
+        <v>7092419</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10324,12 +10333,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10344,24 +10353,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379666</t>
+          <t>https://artportalen.se/Sighting/16580297</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>103379667</v>
+        <v>103379666</v>
       </c>
       <c r="B94" t="n">
         <v>93197</v>
@@ -10396,10 +10405,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>752787</v>
+        <v>752811</v>
       </c>
       <c r="R94" t="n">
-        <v>7092676</v>
+        <v>7092710</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10457,13 +10466,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379667</t>
+          <t>https://artportalen.se/Sighting/103379666</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>103379674</v>
+        <v>103379667</v>
       </c>
       <c r="B95" t="n">
         <v>93197</v>
@@ -10498,10 +10507,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>752859</v>
+        <v>752787</v>
       </c>
       <c r="R95" t="n">
-        <v>7092610</v>
+        <v>7092676</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10559,13 +10568,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379674</t>
+          <t>https://artportalen.se/Sighting/103379667</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>103379676</v>
+        <v>103379674</v>
       </c>
       <c r="B96" t="n">
         <v>93197</v>
@@ -10600,10 +10609,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>752845</v>
+        <v>752859</v>
       </c>
       <c r="R96" t="n">
-        <v>7092598</v>
+        <v>7092610</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10661,13 +10670,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379676</t>
+          <t>https://artportalen.se/Sighting/103379674</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>103379685</v>
+        <v>103379676</v>
       </c>
       <c r="B97" t="n">
         <v>93197</v>
@@ -10702,10 +10711,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>752790</v>
+        <v>752845</v>
       </c>
       <c r="R97" t="n">
-        <v>7092527</v>
+        <v>7092598</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10763,13 +10772,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379685</t>
+          <t>https://artportalen.se/Sighting/103379676</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>103379690</v>
+        <v>103379685</v>
       </c>
       <c r="B98" t="n">
         <v>93197</v>
@@ -10804,10 +10813,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>752731</v>
+        <v>752790</v>
       </c>
       <c r="R98" t="n">
-        <v>7092436</v>
+        <v>7092527</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10865,13 +10874,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379690</t>
+          <t>https://artportalen.se/Sighting/103379685</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>103379693</v>
+        <v>103379690</v>
       </c>
       <c r="B99" t="n">
         <v>93197</v>
@@ -10906,10 +10915,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>752799</v>
+        <v>752731</v>
       </c>
       <c r="R99" t="n">
-        <v>7092461</v>
+        <v>7092436</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10967,13 +10976,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379693</t>
+          <t>https://artportalen.se/Sighting/103379690</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>103379695</v>
+        <v>103379693</v>
       </c>
       <c r="B100" t="n">
         <v>93197</v>
@@ -11008,10 +11017,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>752773</v>
+        <v>752799</v>
       </c>
       <c r="R100" t="n">
-        <v>7092444</v>
+        <v>7092461</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11069,13 +11078,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379695</t>
+          <t>https://artportalen.se/Sighting/103379693</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>103379699</v>
+        <v>103379695</v>
       </c>
       <c r="B101" t="n">
         <v>93197</v>
@@ -11110,10 +11119,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>752809</v>
+        <v>752773</v>
       </c>
       <c r="R101" t="n">
-        <v>7092270</v>
+        <v>7092444</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11171,13 +11180,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379699</t>
+          <t>https://artportalen.se/Sighting/103379695</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>103379700</v>
+        <v>103379699</v>
       </c>
       <c r="B102" t="n">
         <v>93197</v>
@@ -11212,10 +11221,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>752841</v>
+        <v>752809</v>
       </c>
       <c r="R102" t="n">
-        <v>7092268</v>
+        <v>7092270</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11273,13 +11282,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379700</t>
+          <t>https://artportalen.se/Sighting/103379699</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>103379734</v>
+        <v>103379700</v>
       </c>
       <c r="B103" t="n">
         <v>93197</v>
@@ -11314,10 +11323,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>752971</v>
+        <v>752841</v>
       </c>
       <c r="R103" t="n">
-        <v>7092482</v>
+        <v>7092268</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11375,13 +11384,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379734</t>
+          <t>https://artportalen.se/Sighting/103379700</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103379735</v>
+        <v>103379734</v>
       </c>
       <c r="B104" t="n">
         <v>93197</v>
@@ -11416,10 +11425,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>752913</v>
+        <v>752971</v>
       </c>
       <c r="R104" t="n">
-        <v>7092496</v>
+        <v>7092482</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11477,13 +11486,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379735</t>
+          <t>https://artportalen.se/Sighting/103379734</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>103379741</v>
+        <v>103379735</v>
       </c>
       <c r="B105" t="n">
         <v>93197</v>
@@ -11518,10 +11527,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>752797</v>
+        <v>752913</v>
       </c>
       <c r="R105" t="n">
-        <v>7092693</v>
+        <v>7092496</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11579,13 +11588,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379741</t>
+          <t>https://artportalen.se/Sighting/103379735</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>112313701</v>
+        <v>103379741</v>
       </c>
       <c r="B106" t="n">
         <v>93197</v>
@@ -11616,14 +11625,14 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>752811</v>
+        <v>752797</v>
       </c>
       <c r="R106" t="n">
-        <v>7092715</v>
+        <v>7092693</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11650,12 +11659,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11670,24 +11679,24 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313701</t>
+          <t>https://artportalen.se/Sighting/103379741</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119495544</v>
+        <v>112313701</v>
       </c>
       <c r="B107" t="n">
         <v>93197</v>
@@ -11718,17 +11727,17 @@
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>752820</v>
+        <v>752811</v>
       </c>
       <c r="R107" t="n">
-        <v>7092675</v>
+        <v>7092715</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11752,22 +11761,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:06</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11782,24 +11781,24 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119495544</t>
+          <t>https://artportalen.se/Sighting/112313701</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119718984</v>
+        <v>119495544</v>
       </c>
       <c r="B108" t="n">
         <v>93197</v>
@@ -11834,13 +11833,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>752957</v>
+        <v>752820</v>
       </c>
       <c r="R108" t="n">
-        <v>7092406</v>
+        <v>7092675</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11864,12 +11863,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11884,24 +11893,24 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718984</t>
+          <t>https://artportalen.se/Sighting/119495544</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119718985</v>
+        <v>119718984</v>
       </c>
       <c r="B109" t="n">
         <v>93197</v>
@@ -11936,10 +11945,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>752967</v>
+        <v>752957</v>
       </c>
       <c r="R109" t="n">
-        <v>7092339</v>
+        <v>7092406</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11997,13 +12006,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718985</t>
+          <t>https://artportalen.se/Sighting/119718984</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119797598</v>
+        <v>119718985</v>
       </c>
       <c r="B110" t="n">
         <v>93197</v>
@@ -12038,10 +12047,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>752740</v>
+        <v>752967</v>
       </c>
       <c r="R110" t="n">
-        <v>7092313</v>
+        <v>7092339</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12068,12 +12077,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12088,24 +12097,24 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797598</t>
+          <t>https://artportalen.se/Sighting/119718985</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119797599</v>
+        <v>119797598</v>
       </c>
       <c r="B111" t="n">
         <v>93197</v>
@@ -12140,10 +12149,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>752863</v>
+        <v>752740</v>
       </c>
       <c r="R111" t="n">
-        <v>7092380</v>
+        <v>7092313</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12201,13 +12210,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797599</t>
+          <t>https://artportalen.se/Sighting/119797598</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119797600</v>
+        <v>119797599</v>
       </c>
       <c r="B112" t="n">
         <v>93197</v>
@@ -12242,10 +12251,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>752886</v>
+        <v>752863</v>
       </c>
       <c r="R112" t="n">
-        <v>7092295</v>
+        <v>7092380</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12303,13 +12312,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797600</t>
+          <t>https://artportalen.se/Sighting/119797599</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119797601</v>
+        <v>119797600</v>
       </c>
       <c r="B113" t="n">
         <v>93197</v>
@@ -12344,10 +12353,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>752857</v>
+        <v>752886</v>
       </c>
       <c r="R113" t="n">
-        <v>7092283</v>
+        <v>7092295</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12405,13 +12414,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797601</t>
+          <t>https://artportalen.se/Sighting/119797600</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119797602</v>
+        <v>119797601</v>
       </c>
       <c r="B114" t="n">
         <v>93197</v>
@@ -12446,10 +12455,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>752769</v>
+        <v>752857</v>
       </c>
       <c r="R114" t="n">
-        <v>7092291</v>
+        <v>7092283</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12507,13 +12516,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797602</t>
+          <t>https://artportalen.se/Sighting/119797601</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119797603</v>
+        <v>119797602</v>
       </c>
       <c r="B115" t="n">
         <v>93197</v>
@@ -12548,10 +12557,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>752819</v>
+        <v>752769</v>
       </c>
       <c r="R115" t="n">
-        <v>7092254</v>
+        <v>7092291</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12609,13 +12618,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797603</t>
+          <t>https://artportalen.se/Sighting/119797602</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119797604</v>
+        <v>119797603</v>
       </c>
       <c r="B116" t="n">
         <v>93197</v>
@@ -12650,10 +12659,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>752825</v>
+        <v>752819</v>
       </c>
       <c r="R116" t="n">
-        <v>7092235</v>
+        <v>7092254</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12711,13 +12720,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797604</t>
+          <t>https://artportalen.se/Sighting/119797603</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119797605</v>
+        <v>119797604</v>
       </c>
       <c r="B117" t="n">
         <v>93197</v>
@@ -12752,10 +12761,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>752888</v>
+        <v>752825</v>
       </c>
       <c r="R117" t="n">
-        <v>7092191</v>
+        <v>7092235</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12813,13 +12822,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797605</t>
+          <t>https://artportalen.se/Sighting/119797604</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119808293</v>
+        <v>119797605</v>
       </c>
       <c r="B118" t="n">
         <v>93197</v>
@@ -12854,13 +12863,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>752820</v>
+        <v>752888</v>
       </c>
       <c r="R118" t="n">
-        <v>7092239</v>
+        <v>7092191</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12887,19 +12896,9 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>12:41</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12914,24 +12913,24 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808293</t>
+          <t>https://artportalen.se/Sighting/119797605</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119808294</v>
+        <v>119808293</v>
       </c>
       <c r="B119" t="n">
         <v>93197</v>
@@ -12966,10 +12965,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>752867</v>
+        <v>752820</v>
       </c>
       <c r="R119" t="n">
-        <v>7092294</v>
+        <v>7092239</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -13001,7 +13000,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13011,7 +13010,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13037,13 +13036,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808294</t>
+          <t>https://artportalen.se/Sighting/119808293</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119808296</v>
+        <v>119808294</v>
       </c>
       <c r="B120" t="n">
         <v>93197</v>
@@ -13078,10 +13077,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>752902</v>
+        <v>752867</v>
       </c>
       <c r="R120" t="n">
-        <v>7092285</v>
+        <v>7092294</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -13113,7 +13112,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13123,7 +13122,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13149,13 +13148,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808296</t>
+          <t>https://artportalen.se/Sighting/119808294</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119808299</v>
+        <v>119808296</v>
       </c>
       <c r="B121" t="n">
         <v>93197</v>
@@ -13190,10 +13189,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>752962</v>
+        <v>752902</v>
       </c>
       <c r="R121" t="n">
-        <v>7092343</v>
+        <v>7092285</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -13225,7 +13224,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13235,7 +13234,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13261,13 +13260,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808299</t>
+          <t>https://artportalen.se/Sighting/119808296</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119808302</v>
+        <v>119808299</v>
       </c>
       <c r="B122" t="n">
         <v>93197</v>
@@ -13302,10 +13301,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>752841</v>
+        <v>752962</v>
       </c>
       <c r="R122" t="n">
-        <v>7092401</v>
+        <v>7092343</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -13337,7 +13336,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13347,7 +13346,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13373,13 +13372,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808302</t>
+          <t>https://artportalen.se/Sighting/119808299</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119934809</v>
+        <v>119808302</v>
       </c>
       <c r="B123" t="n">
         <v>93197</v>
@@ -13407,24 +13406,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>752817</v>
+        <v>752841</v>
       </c>
       <c r="R123" t="n">
-        <v>7092378</v>
+        <v>7092401</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13448,12 +13443,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13468,24 +13473,24 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934809</t>
+          <t>https://artportalen.se/Sighting/119808302</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119934810</v>
+        <v>119934809</v>
       </c>
       <c r="B124" t="n">
         <v>93197</v>
@@ -13515,7 +13520,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -13524,10 +13529,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>752803</v>
+        <v>752817</v>
       </c>
       <c r="R124" t="n">
-        <v>7092670</v>
+        <v>7092378</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13585,13 +13590,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934810</t>
+          <t>https://artportalen.se/Sighting/119934809</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119934811</v>
+        <v>119934810</v>
       </c>
       <c r="B125" t="n">
         <v>93197</v>
@@ -13619,17 +13624,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>752853</v>
+        <v>752803</v>
       </c>
       <c r="R125" t="n">
-        <v>7092405</v>
+        <v>7092670</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13687,13 +13696,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934811</t>
+          <t>https://artportalen.se/Sighting/119934810</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119934812</v>
+        <v>119934811</v>
       </c>
       <c r="B126" t="n">
         <v>93197</v>
@@ -13728,10 +13737,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>752796</v>
+        <v>752853</v>
       </c>
       <c r="R126" t="n">
-        <v>7092694</v>
+        <v>7092405</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13789,13 +13798,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934812</t>
+          <t>https://artportalen.se/Sighting/119934811</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119934813</v>
+        <v>119934812</v>
       </c>
       <c r="B127" t="n">
         <v>93197</v>
@@ -13830,10 +13839,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>752857</v>
+        <v>752796</v>
       </c>
       <c r="R127" t="n">
-        <v>7092672</v>
+        <v>7092694</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13891,13 +13900,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934813</t>
+          <t>https://artportalen.se/Sighting/119934812</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119934814</v>
+        <v>119934813</v>
       </c>
       <c r="B128" t="n">
         <v>93197</v>
@@ -13932,10 +13941,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>752764</v>
+        <v>752857</v>
       </c>
       <c r="R128" t="n">
-        <v>7092560</v>
+        <v>7092672</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13993,13 +14002,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934814</t>
+          <t>https://artportalen.se/Sighting/119934813</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119934815</v>
+        <v>119934814</v>
       </c>
       <c r="B129" t="n">
         <v>93197</v>
@@ -14034,10 +14043,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>752779</v>
+        <v>752764</v>
       </c>
       <c r="R129" t="n">
-        <v>7092482</v>
+        <v>7092560</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14095,13 +14104,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934815</t>
+          <t>https://artportalen.se/Sighting/119934814</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119934817</v>
+        <v>119934815</v>
       </c>
       <c r="B130" t="n">
         <v>93197</v>
@@ -14136,10 +14145,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>752778</v>
+        <v>752779</v>
       </c>
       <c r="R130" t="n">
-        <v>7092478</v>
+        <v>7092482</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14197,13 +14206,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934817</t>
+          <t>https://artportalen.se/Sighting/119934815</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119934818</v>
+        <v>119934817</v>
       </c>
       <c r="B131" t="n">
         <v>93197</v>
@@ -14238,10 +14247,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>753030</v>
+        <v>752778</v>
       </c>
       <c r="R131" t="n">
-        <v>7092403</v>
+        <v>7092478</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14299,13 +14308,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934818</t>
+          <t>https://artportalen.se/Sighting/119934817</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119934819</v>
+        <v>119934818</v>
       </c>
       <c r="B132" t="n">
         <v>93197</v>
@@ -14340,10 +14349,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>752979</v>
+        <v>753030</v>
       </c>
       <c r="R132" t="n">
-        <v>7092382</v>
+        <v>7092403</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14401,13 +14410,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934819</t>
+          <t>https://artportalen.se/Sighting/119934818</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120374050</v>
+        <v>119934819</v>
       </c>
       <c r="B133" t="n">
         <v>93197</v>
@@ -14438,17 +14447,17 @@
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>752955</v>
+        <v>752979</v>
       </c>
       <c r="R133" t="n">
-        <v>7092262</v>
+        <v>7092382</v>
       </c>
       <c r="S133" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14472,22 +14481,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>09:28</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14502,24 +14501,24 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120374050</t>
+          <t>https://artportalen.se/Sighting/119934819</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120403835</v>
+        <v>120374050</v>
       </c>
       <c r="B134" t="n">
         <v>93197</v>
@@ -14550,17 +14549,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>752971</v>
+        <v>752955</v>
       </c>
       <c r="R134" t="n">
-        <v>7092254</v>
+        <v>7092262</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14587,9 +14586,19 @@
           <t>2024-10-13</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14604,24 +14613,24 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403835</t>
+          <t>https://artportalen.se/Sighting/120374050</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128627827</v>
+        <v>120403835</v>
       </c>
       <c r="B135" t="n">
         <v>93197</v>
@@ -14656,10 +14665,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>752892</v>
+        <v>752971</v>
       </c>
       <c r="R135" t="n">
-        <v>7092398</v>
+        <v>7092254</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14686,12 +14695,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14706,27 +14715,27 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627827</t>
+          <t>https://artportalen.se/Sighting/120403835</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135810620</v>
+        <v>128627827</v>
       </c>
       <c r="B136" t="n">
-        <v>93372</v>
+        <v>93197</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14751,31 +14760,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>752746</v>
+        <v>752892</v>
       </c>
       <c r="R136" t="n">
-        <v>7092355</v>
+        <v>7092398</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14799,12 +14797,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14813,72 +14811,82 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135810620</t>
+          <t>https://artportalen.se/Sighting/128627827</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>103379673</v>
+        <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93201</v>
+        <v>93372</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>752869</v>
+        <v>752746</v>
       </c>
       <c r="R137" t="n">
-        <v>7092623</v>
+        <v>7092355</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14902,12 +14910,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14916,68 +14924,78 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379673</t>
+          <t>https://artportalen.se/Sighting/135810620</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119797561</v>
+        <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93201</v>
+        <v>93378</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kullaskogen lilla sandgrop , Kullaskogen lilla sandgrop , Vb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>752774</v>
+        <v>752984</v>
       </c>
       <c r="R138" t="n">
-        <v>7092461</v>
+        <v>7092379</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15004,17 +15022,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Under tunn talllåga vid stig, vid rotfästet</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15029,24 +15052,24 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jonas Eilertsen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797561</t>
+          <t>https://artportalen.se/Sighting/136339459</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119797562</v>
+        <v>103379673</v>
       </c>
       <c r="B139" t="n">
         <v>93201</v>
@@ -15081,10 +15104,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>752870</v>
+        <v>752869</v>
       </c>
       <c r="R139" t="n">
-        <v>7092247</v>
+        <v>7092623</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15111,17 +15134,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Under silverlåga vid stig</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15136,24 +15154,24 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797562</t>
+          <t>https://artportalen.se/Sighting/103379673</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119797563</v>
+        <v>119797561</v>
       </c>
       <c r="B140" t="n">
         <v>93201</v>
@@ -15181,24 +15199,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>752807</v>
+        <v>752774</v>
       </c>
       <c r="R140" t="n">
-        <v>7092367</v>
+        <v>7092461</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15235,7 +15246,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
+          <t>Under tunn talllåga vid stig, vid rotfästet</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15244,7 +15255,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15262,13 +15272,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797563</t>
+          <t>https://artportalen.se/Sighting/119797561</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119934771</v>
+        <v>119797562</v>
       </c>
       <c r="B141" t="n">
         <v>93201</v>
@@ -15303,10 +15313,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>752765</v>
+        <v>752870</v>
       </c>
       <c r="R141" t="n">
-        <v>7092632</v>
+        <v>7092247</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15333,17 +15343,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Under tunn tallåga</t>
+          <t>Under silverlåga vid stig</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15369,13 +15379,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934771</t>
+          <t>https://artportalen.se/Sighting/119797562</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119934772</v>
+        <v>119797563</v>
       </c>
       <c r="B142" t="n">
         <v>93201</v>
@@ -15403,17 +15413,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>752757</v>
+        <v>752807</v>
       </c>
       <c r="R142" t="n">
-        <v>7092617</v>
+        <v>7092367</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15440,17 +15457,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Under tunn tallåga i mossmatta</t>
+          <t>6 fruktkroppar(minst) under 2 tunna tallågor i grop. Troligen samma mycel. Uppdatering 20240921. Hittades fler fruktkroppar som var sammanväxta under en annan tunn talllåga vid gropen.</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15459,6 +15476,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15476,13 +15494,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934772</t>
+          <t>https://artportalen.se/Sighting/119797563</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119934773</v>
+        <v>119934771</v>
       </c>
       <c r="B143" t="n">
         <v>93201</v>
@@ -15510,21 +15528,17 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>752853</v>
+        <v>752765</v>
       </c>
       <c r="R143" t="n">
-        <v>7092405</v>
+        <v>7092632</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15561,7 +15575,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
+          <t>Under tunn tallåga</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15587,13 +15601,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934773</t>
+          <t>https://artportalen.se/Sighting/119934771</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128587583</v>
+        <v>119934772</v>
       </c>
       <c r="B144" t="n">
         <v>93201</v>
@@ -15628,13 +15642,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>752876</v>
+        <v>752757</v>
       </c>
       <c r="R144" t="n">
-        <v>7092345</v>
+        <v>7092617</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15658,27 +15672,17 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Under tallgren nedsänkt i mossa. Flera sammanväxta fruktkroppar</t>
+          <t>Under tunn tallåga i mossmatta</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15689,11 +15693,6 @@
       </c>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
@@ -15709,13 +15708,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128587583</t>
+          <t>https://artportalen.se/Sighting/119934772</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129224524</v>
+        <v>119934773</v>
       </c>
       <c r="B145" t="n">
         <v>93201</v>
@@ -15743,20 +15742,24 @@
           <t>(P.Karst) P.Karst</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>752870</v>
+        <v>752853</v>
       </c>
       <c r="R145" t="n">
-        <v>7092608</v>
+        <v>7092405</v>
       </c>
       <c r="S145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15780,17 +15783,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Silverlåga, vid basen</t>
+          <t>Under tunn tallåga, knäckt med flera brott, flera delar</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15816,13 +15819,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224524</t>
+          <t>https://artportalen.se/Sighting/119934773</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129224527</v>
+        <v>128587583</v>
       </c>
       <c r="B146" t="n">
         <v>93201</v>
@@ -15857,10 +15860,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>752884</v>
+        <v>752876</v>
       </c>
       <c r="R146" t="n">
-        <v>7092646</v>
+        <v>7092345</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15887,17 +15890,27 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Många sammanväxta fruktkroppar under tallåga</t>
+          <t>Under tallgren nedsänkt i mossa. Flera sammanväxta fruktkroppar</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15908,6 +15921,11 @@
       </c>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
@@ -15923,13 +15941,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224527</t>
+          <t>https://artportalen.se/Sighting/128587583</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129224529</v>
+        <v>129224524</v>
       </c>
       <c r="B147" t="n">
         <v>93201</v>
@@ -15964,10 +15982,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>752861</v>
+        <v>752870</v>
       </c>
       <c r="R147" t="n">
-        <v>7092617</v>
+        <v>7092608</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -16004,7 +16022,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Kort kapad äldre tallåga, mossbevuxen</t>
+          <t>Silverlåga, vid basen</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16030,38 +16048,38 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224529</t>
+          <t>https://artportalen.se/Sighting/129224524</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>16580296</v>
+        <v>129224527</v>
       </c>
       <c r="B148" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16071,13 +16089,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>752967</v>
+        <v>752884</v>
       </c>
       <c r="R148" t="n">
-        <v>7092346</v>
+        <v>7092646</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16101,12 +16119,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2014-09-10</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Många sammanväxta fruktkroppar under tallåga</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16121,49 +16144,49 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16580296</t>
+          <t>https://artportalen.se/Sighting/129224527</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>103379703</v>
+        <v>129224529</v>
       </c>
       <c r="B149" t="n">
-        <v>93209</v>
+        <v>93201</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16173,13 +16196,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>752959</v>
+        <v>752861</v>
       </c>
       <c r="R149" t="n">
-        <v>7092217</v>
+        <v>7092617</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16203,12 +16226,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Kort kapad äldre tallåga, mossbevuxen</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16223,24 +16251,24 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379703</t>
+          <t>https://artportalen.se/Sighting/129224529</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119797564</v>
+        <v>16580296</v>
       </c>
       <c r="B150" t="n">
         <v>93209</v>
@@ -16275,10 +16303,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>752716</v>
+        <v>752967</v>
       </c>
       <c r="R150" t="n">
-        <v>7092384</v>
+        <v>7092346</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16305,12 +16333,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2014-09-10</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16325,24 +16353,24 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797564</t>
+          <t>https://artportalen.se/Sighting/16580296</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119797565</v>
+        <v>103379703</v>
       </c>
       <c r="B151" t="n">
         <v>93209</v>
@@ -16377,10 +16405,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>752765</v>
+        <v>752959</v>
       </c>
       <c r="R151" t="n">
-        <v>7092391</v>
+        <v>7092217</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16407,12 +16435,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16427,24 +16455,24 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797565</t>
+          <t>https://artportalen.se/Sighting/103379703</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119797566</v>
+        <v>119797564</v>
       </c>
       <c r="B152" t="n">
         <v>93209</v>
@@ -16479,10 +16507,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>752868</v>
+        <v>752716</v>
       </c>
       <c r="R152" t="n">
-        <v>7092254</v>
+        <v>7092384</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16540,13 +16568,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797566</t>
+          <t>https://artportalen.se/Sighting/119797564</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119797567</v>
+        <v>119797565</v>
       </c>
       <c r="B153" t="n">
         <v>93209</v>
@@ -16581,10 +16609,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>752807</v>
+        <v>752765</v>
       </c>
       <c r="R153" t="n">
-        <v>7092251</v>
+        <v>7092391</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16642,13 +16670,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797567</t>
+          <t>https://artportalen.se/Sighting/119797565</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119808307</v>
+        <v>119797566</v>
       </c>
       <c r="B154" t="n">
         <v>93209</v>
@@ -16683,13 +16711,13 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>752764</v>
+        <v>752868</v>
       </c>
       <c r="R154" t="n">
-        <v>7092409</v>
+        <v>7092254</v>
       </c>
       <c r="S154" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -16716,19 +16744,9 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16743,24 +16761,24 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808307</t>
+          <t>https://artportalen.se/Sighting/119797566</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119808311</v>
+        <v>119797567</v>
       </c>
       <c r="B155" t="n">
         <v>93209</v>
@@ -16795,13 +16813,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>752771</v>
+        <v>752807</v>
       </c>
       <c r="R155" t="n">
-        <v>7092333</v>
+        <v>7092251</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16828,19 +16846,9 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>11:32</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16855,24 +16863,24 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808311</t>
+          <t>https://artportalen.se/Sighting/119797567</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119891959</v>
+        <v>119808307</v>
       </c>
       <c r="B156" t="n">
         <v>93209</v>
@@ -16903,17 +16911,17 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>752740</v>
+        <v>752764</v>
       </c>
       <c r="R156" t="n">
-        <v>7092396</v>
+        <v>7092409</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16937,12 +16945,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16957,24 +16975,24 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891959</t>
+          <t>https://artportalen.se/Sighting/119808307</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128630170</v>
+        <v>119808311</v>
       </c>
       <c r="B157" t="n">
         <v>93209</v>
@@ -17009,13 +17027,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>752914</v>
+        <v>752771</v>
       </c>
       <c r="R157" t="n">
-        <v>7092346</v>
+        <v>7092333</v>
       </c>
       <c r="S157" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17039,12 +17057,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17059,27 +17087,27 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128630170</t>
+          <t>https://artportalen.se/Sighting/119808311</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>103379668</v>
+        <v>119891959</v>
       </c>
       <c r="B158" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17087,34 +17115,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>752806</v>
+        <v>752740</v>
       </c>
       <c r="R158" t="n">
-        <v>7092648</v>
+        <v>7092396</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17141,12 +17169,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17161,27 +17189,27 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379668</t>
+          <t>https://artportalen.se/Sighting/119891959</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>103379687</v>
+        <v>128630170</v>
       </c>
       <c r="B159" t="n">
-        <v>92841</v>
+        <v>93209</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17189,21 +17217,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17213,13 +17241,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>752716</v>
+        <v>752914</v>
       </c>
       <c r="R159" t="n">
-        <v>7092478</v>
+        <v>7092346</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17243,12 +17271,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17263,24 +17291,24 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379687</t>
+          <t>https://artportalen.se/Sighting/128630170</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>103379727</v>
+        <v>103379668</v>
       </c>
       <c r="B160" t="n">
         <v>92841</v>
@@ -17315,10 +17343,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>753013</v>
+        <v>752806</v>
       </c>
       <c r="R160" t="n">
-        <v>7092351</v>
+        <v>7092648</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17376,13 +17404,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379727</t>
+          <t>https://artportalen.se/Sighting/103379668</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119808303</v>
+        <v>103379687</v>
       </c>
       <c r="B161" t="n">
         <v>92841</v>
@@ -17417,13 +17445,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>752812</v>
+        <v>752716</v>
       </c>
       <c r="R161" t="n">
-        <v>7092433</v>
+        <v>7092478</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17447,22 +17475,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17477,24 +17495,24 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808303</t>
+          <t>https://artportalen.se/Sighting/103379687</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119934755</v>
+        <v>103379727</v>
       </c>
       <c r="B162" t="n">
         <v>92841</v>
@@ -17529,10 +17547,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>752777</v>
+        <v>753013</v>
       </c>
       <c r="R162" t="n">
-        <v>7092472</v>
+        <v>7092351</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17559,12 +17577,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17579,27 +17597,27 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934755</t>
+          <t>https://artportalen.se/Sighting/103379727</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119892875</v>
+        <v>119808303</v>
       </c>
       <c r="B163" t="n">
-        <v>90522</v>
+        <v>92841</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17607,37 +17625,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4962</v>
+        <v>4745</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>752854</v>
+        <v>752812</v>
       </c>
       <c r="R163" t="n">
-        <v>7092368</v>
+        <v>7092433</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17661,12 +17679,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17681,27 +17709,27 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892875</t>
+          <t>https://artportalen.se/Sighting/119808303</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>54818447</v>
+        <v>119934755</v>
       </c>
       <c r="B164" t="n">
-        <v>91930</v>
+        <v>92841</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17709,21 +17737,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5442</v>
+        <v>4745</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17733,10 +17761,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>752938</v>
+        <v>752777</v>
       </c>
       <c r="R164" t="n">
-        <v>7092250</v>
+        <v>7092472</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17763,12 +17791,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2015-08-12</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17779,36 +17807,31 @@
       </c>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>äldre sandtallskog</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54818447</t>
+          <t>https://artportalen.se/Sighting/119934755</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119718958</v>
+        <v>119892875</v>
       </c>
       <c r="B165" t="n">
-        <v>93223</v>
+        <v>90522</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17816,34 +17839,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>752782</v>
+        <v>752854</v>
       </c>
       <c r="R165" t="n">
-        <v>7092728</v>
+        <v>7092368</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17870,12 +17893,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17890,27 +17913,27 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718958</t>
+          <t>https://artportalen.se/Sighting/119892875</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119797537</v>
+        <v>54818447</v>
       </c>
       <c r="B166" t="n">
-        <v>93223</v>
+        <v>91930</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17918,21 +17941,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17942,10 +17965,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>752807</v>
+        <v>752938</v>
       </c>
       <c r="R166" t="n">
-        <v>7092369</v>
+        <v>7092250</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17972,17 +17995,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>I grop</t>
+          <t>2015-08-12</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17993,28 +18011,33 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Andreas Garpebring</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797537</t>
+          <t>https://artportalen.se/Sighting/54818447</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119797538</v>
+        <v>119718958</v>
       </c>
       <c r="B167" t="n">
         <v>93223</v>
@@ -18049,10 +18072,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>752734</v>
+        <v>752782</v>
       </c>
       <c r="R167" t="n">
-        <v>7092340</v>
+        <v>7092728</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18079,12 +18102,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18099,24 +18122,24 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797538</t>
+          <t>https://artportalen.se/Sighting/119718958</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119797539</v>
+        <v>119797537</v>
       </c>
       <c r="B168" t="n">
         <v>93223</v>
@@ -18151,10 +18174,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>752737</v>
+        <v>752807</v>
       </c>
       <c r="R168" t="n">
-        <v>7092298</v>
+        <v>7092369</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18189,6 +18212,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>I grop</t>
+        </is>
+      </c>
       <c r="AD168" t="b">
         <v>0</v>
       </c>
@@ -18212,13 +18240,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797539</t>
+          <t>https://artportalen.se/Sighting/119797537</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119799792</v>
+        <v>119797538</v>
       </c>
       <c r="B169" t="n">
         <v>93223</v>
@@ -18247,19 +18275,16 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>752934</v>
+        <v>752734</v>
       </c>
       <c r="R169" t="n">
-        <v>7092206</v>
+        <v>7092340</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18294,18 +18319,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
-        </is>
-      </c>
       <c r="AD169" t="b">
         <v>0</v>
       </c>
       <c r="AE169" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF169" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -18323,13 +18342,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119799792</t>
+          <t>https://artportalen.se/Sighting/119797538</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119893348</v>
+        <v>119797539</v>
       </c>
       <c r="B170" t="n">
         <v>93223</v>
@@ -18360,14 +18379,14 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>752893</v>
+        <v>752737</v>
       </c>
       <c r="R170" t="n">
-        <v>7092272</v>
+        <v>7092298</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18394,12 +18413,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18414,24 +18433,24 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893348</t>
+          <t>https://artportalen.se/Sighting/119797539</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119934758</v>
+        <v>119799792</v>
       </c>
       <c r="B171" t="n">
         <v>93223</v>
@@ -18460,16 +18479,19 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>752979</v>
+        <v>752934</v>
       </c>
       <c r="R171" t="n">
-        <v>7092382</v>
+        <v>7092206</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18496,25 +18518,26 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Under silverlåga, tallgren vid basen</t>
+          <t>Ska återbesökas och dokumenteras ordentligt. Efter diskussion med validerare och experter: Troligen svartvit taggsvamp eller obeskriven art under arbetsnamn "mukkas skinn".</t>
         </is>
       </c>
       <c r="AD171" t="b">
         <v>0</v>
       </c>
       <c r="AE171" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18532,54 +18555,54 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934758</t>
+          <t>https://artportalen.se/Sighting/119799792</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129224542</v>
+        <v>119893348</v>
       </c>
       <c r="B172" t="n">
-        <v>91282</v>
+        <v>93223</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5685</v>
+        <v>5448</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>752869</v>
+        <v>752893</v>
       </c>
       <c r="R172" t="n">
-        <v>7092256</v>
+        <v>7092272</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -18603,12 +18626,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18619,51 +18642,31 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL172" t="inlineStr">
-        <is>
-          <t>Tallåga vid stig</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga vid stig</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224542</t>
+          <t>https://artportalen.se/Sighting/119893348</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>112313635</v>
+        <v>119934758</v>
       </c>
       <c r="B173" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18671,43 +18674,34 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>752817</v>
+        <v>752979</v>
       </c>
       <c r="R173" t="n">
-        <v>7092607</v>
+        <v>7092382</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18734,12 +18728,17 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Under silverlåga, tallgren vid basen</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18765,63 +18764,54 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313635</t>
+          <t>https://artportalen.se/Sighting/119934758</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>112313647</v>
+        <v>129224542</v>
       </c>
       <c r="B174" t="n">
-        <v>93235</v>
+        <v>91282</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5966</v>
+        <v>5685</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>752846</v>
+        <v>752869</v>
       </c>
       <c r="R174" t="n">
-        <v>7092719</v>
+        <v>7092256</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18845,12 +18835,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18861,6 +18851,26 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>Tallåga vid stig</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga vid stig</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
@@ -18876,13 +18886,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313647</t>
+          <t>https://artportalen.se/Sighting/129224542</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>112313653</v>
+        <v>112313635</v>
       </c>
       <c r="B175" t="n">
         <v>93235</v>
@@ -18912,7 +18922,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -18920,18 +18930,16 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>752936</v>
+        <v>752817</v>
       </c>
       <c r="R175" t="n">
-        <v>7092682</v>
+        <v>7092607</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18966,18 +18974,12 @@
           <t>2023-09-24</t>
         </is>
       </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>Häxring</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
       </c>
@@ -18995,13 +18997,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313653</t>
+          <t>https://artportalen.se/Sighting/112313635</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119797581</v>
+        <v>112313647</v>
       </c>
       <c r="B176" t="n">
         <v>93235</v>
@@ -19031,19 +19033,24 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>752686</v>
+        <v>752846</v>
       </c>
       <c r="R176" t="n">
-        <v>7092272</v>
+        <v>7092719</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19070,17 +19077,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Nära stigen</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19106,13 +19108,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797581</t>
+          <t>https://artportalen.se/Sighting/112313647</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119797583</v>
+        <v>112313653</v>
       </c>
       <c r="B177" t="n">
         <v>93235</v>
@@ -19140,17 +19142,28 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>752719</v>
+        <v>752936</v>
       </c>
       <c r="R177" t="n">
-        <v>7092452</v>
+        <v>7092682</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19177,12 +19190,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Häxring</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19191,6 +19209,7 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
+      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
@@ -19208,13 +19227,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797583</t>
+          <t>https://artportalen.se/Sighting/112313653</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119934799</v>
+        <v>119797581</v>
       </c>
       <c r="B178" t="n">
         <v>93235</v>
@@ -19244,7 +19263,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -19253,10 +19272,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>752754</v>
+        <v>752686</v>
       </c>
       <c r="R178" t="n">
-        <v>7092559</v>
+        <v>7092272</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19283,12 +19302,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Nära stigen</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19314,13 +19338,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934799</t>
+          <t>https://artportalen.se/Sighting/119797581</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>120403828</v>
+        <v>119797583</v>
       </c>
       <c r="B179" t="n">
         <v>93235</v>
@@ -19355,10 +19379,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>752970</v>
+        <v>752719</v>
       </c>
       <c r="R179" t="n">
-        <v>7092257</v>
+        <v>7092452</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19385,12 +19409,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19416,13 +19440,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120403828</t>
+          <t>https://artportalen.se/Sighting/119797583</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129224532</v>
+        <v>119934799</v>
       </c>
       <c r="B180" t="n">
         <v>93235</v>
@@ -19452,7 +19476,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -19461,13 +19485,13 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>752940</v>
+        <v>752754</v>
       </c>
       <c r="R180" t="n">
-        <v>7092218</v>
+        <v>7092559</v>
       </c>
       <c r="S180" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -19491,12 +19515,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -19522,38 +19546,38 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129224532</t>
+          <t>https://artportalen.se/Sighting/119934799</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>103379669</v>
+        <v>120403828</v>
       </c>
       <c r="B181" t="n">
-        <v>90691</v>
+        <v>93235</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19563,10 +19587,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>752766</v>
+        <v>752970</v>
       </c>
       <c r="R181" t="n">
-        <v>7092626</v>
+        <v>7092257</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19593,12 +19617,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19613,65 +19637,69 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379669</t>
+          <t>https://artportalen.se/Sighting/120403828</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>103379675</v>
+        <v>129224532</v>
       </c>
       <c r="B182" t="n">
-        <v>90691</v>
+        <v>93235</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>752854</v>
+        <v>752940</v>
       </c>
       <c r="R182" t="n">
-        <v>7092609</v>
+        <v>7092218</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -19695,12 +19723,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2022-09-03</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19715,24 +19743,24 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379675</t>
+          <t>https://artportalen.se/Sighting/129224532</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>103379679</v>
+        <v>103379669</v>
       </c>
       <c r="B183" t="n">
         <v>90691</v>
@@ -19767,10 +19795,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>752820</v>
+        <v>752766</v>
       </c>
       <c r="R183" t="n">
-        <v>7092595</v>
+        <v>7092626</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19828,13 +19856,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379679</t>
+          <t>https://artportalen.se/Sighting/103379669</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>103379682</v>
+        <v>103379675</v>
       </c>
       <c r="B184" t="n">
         <v>90691</v>
@@ -19869,10 +19897,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>752789</v>
+        <v>752854</v>
       </c>
       <c r="R184" t="n">
-        <v>7092541</v>
+        <v>7092609</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19930,13 +19958,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379682</t>
+          <t>https://artportalen.se/Sighting/103379675</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>103379683</v>
+        <v>103379679</v>
       </c>
       <c r="B185" t="n">
         <v>90691</v>
@@ -19971,10 +19999,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>752816</v>
+        <v>752820</v>
       </c>
       <c r="R185" t="n">
-        <v>7092517</v>
+        <v>7092595</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20032,13 +20060,13 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379683</t>
+          <t>https://artportalen.se/Sighting/103379679</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>103379692</v>
+        <v>103379682</v>
       </c>
       <c r="B186" t="n">
         <v>90691</v>
@@ -20073,10 +20101,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>752778</v>
+        <v>752789</v>
       </c>
       <c r="R186" t="n">
-        <v>7092448</v>
+        <v>7092541</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20134,13 +20162,13 @@
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379692</t>
+          <t>https://artportalen.se/Sighting/103379682</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>103379696</v>
+        <v>103379683</v>
       </c>
       <c r="B187" t="n">
         <v>90691</v>
@@ -20175,10 +20203,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>752758</v>
+        <v>752816</v>
       </c>
       <c r="R187" t="n">
-        <v>7092310</v>
+        <v>7092517</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20236,13 +20264,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379696</t>
+          <t>https://artportalen.se/Sighting/103379683</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>103379697</v>
+        <v>103379692</v>
       </c>
       <c r="B188" t="n">
         <v>90691</v>
@@ -20277,10 +20305,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>752764</v>
+        <v>752778</v>
       </c>
       <c r="R188" t="n">
-        <v>7092301</v>
+        <v>7092448</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20338,13 +20366,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379697</t>
+          <t>https://artportalen.se/Sighting/103379692</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>103379698</v>
+        <v>103379696</v>
       </c>
       <c r="B189" t="n">
         <v>90691</v>
@@ -20379,10 +20407,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>752734</v>
+        <v>752758</v>
       </c>
       <c r="R189" t="n">
-        <v>7092295</v>
+        <v>7092310</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20440,13 +20468,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379698</t>
+          <t>https://artportalen.se/Sighting/103379696</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>103379726</v>
+        <v>103379697</v>
       </c>
       <c r="B190" t="n">
         <v>90691</v>
@@ -20481,10 +20509,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>752993</v>
+        <v>752764</v>
       </c>
       <c r="R190" t="n">
-        <v>7092362</v>
+        <v>7092301</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20542,13 +20570,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379726</t>
+          <t>https://artportalen.se/Sighting/103379697</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>103379733</v>
+        <v>103379698</v>
       </c>
       <c r="B191" t="n">
         <v>90691</v>
@@ -20583,10 +20611,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>753013</v>
+        <v>752734</v>
       </c>
       <c r="R191" t="n">
-        <v>7092487</v>
+        <v>7092295</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20644,13 +20672,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103379733</t>
+          <t>https://artportalen.se/Sighting/103379698</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>112313697</v>
+        <v>103379726</v>
       </c>
       <c r="B192" t="n">
         <v>90691</v>
@@ -20678,26 +20706,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Trollberget-Kullaheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>752888</v>
+        <v>752993</v>
       </c>
       <c r="R192" t="n">
-        <v>7092644</v>
+        <v>7092362</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20724,12 +20743,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20744,24 +20763,24 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112313697</t>
+          <t>https://artportalen.se/Sighting/103379726</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119718982</v>
+        <v>103379733</v>
       </c>
       <c r="B193" t="n">
         <v>90691</v>
@@ -20796,10 +20815,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>752792</v>
+        <v>753013</v>
       </c>
       <c r="R193" t="n">
-        <v>7092573</v>
+        <v>7092487</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20826,12 +20845,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2022-09-03</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20857,13 +20876,13 @@
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718982</t>
+          <t>https://artportalen.se/Sighting/103379733</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119718983</v>
+        <v>112313697</v>
       </c>
       <c r="B194" t="n">
         <v>90691</v>
@@ -20891,17 +20910,26 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Trollberget-Kullaheden, Vb</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>752779</v>
+        <v>752888</v>
       </c>
       <c r="R194" t="n">
-        <v>7092474</v>
+        <v>7092644</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20928,12 +20956,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -20948,24 +20976,24 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718983</t>
+          <t>https://artportalen.se/Sighting/112313697</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119797594</v>
+        <v>119718982</v>
       </c>
       <c r="B195" t="n">
         <v>90691</v>
@@ -21000,10 +21028,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>752842</v>
+        <v>752792</v>
       </c>
       <c r="R195" t="n">
-        <v>7092347</v>
+        <v>7092573</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21030,17 +21058,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Äldre fruktkropp</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21055,24 +21078,24 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797594</t>
+          <t>https://artportalen.se/Sighting/119718982</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119797595</v>
+        <v>119718983</v>
       </c>
       <c r="B196" t="n">
         <v>90691</v>
@@ -21100,21 +21123,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>752803</v>
+        <v>752779</v>
       </c>
       <c r="R196" t="n">
-        <v>7092370</v>
+        <v>7092474</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21141,17 +21160,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Bredvid grop</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21166,24 +21180,24 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797595</t>
+          <t>https://artportalen.se/Sighting/119718983</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119797597</v>
+        <v>119797594</v>
       </c>
       <c r="B197" t="n">
         <v>90691</v>
@@ -21218,10 +21232,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>752839</v>
+        <v>752842</v>
       </c>
       <c r="R197" t="n">
-        <v>7092201</v>
+        <v>7092347</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21256,6 +21270,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Äldre fruktkropp</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
@@ -21279,13 +21298,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797597</t>
+          <t>https://artportalen.se/Sighting/119797594</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119934806</v>
+        <v>119797595</v>
       </c>
       <c r="B198" t="n">
         <v>90691</v>
@@ -21315,7 +21334,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -21324,10 +21343,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>752816</v>
+        <v>752803</v>
       </c>
       <c r="R198" t="n">
-        <v>7092714</v>
+        <v>7092370</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21354,12 +21373,17 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Bredvid grop</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21385,13 +21409,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934806</t>
+          <t>https://artportalen.se/Sighting/119797595</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119934808</v>
+        <v>119797597</v>
       </c>
       <c r="B199" t="n">
         <v>90691</v>
@@ -21419,21 +21443,17 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>752819</v>
+        <v>752839</v>
       </c>
       <c r="R199" t="n">
-        <v>7092515</v>
+        <v>7092201</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21460,12 +21480,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -21491,16 +21511,16 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934808</t>
+          <t>https://artportalen.se/Sighting/119797597</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119718954</v>
+        <v>119934806</v>
       </c>
       <c r="B200" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -21508,34 +21528,38 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>752778</v>
+        <v>752816</v>
       </c>
       <c r="R200" t="n">
-        <v>7092543</v>
+        <v>7092714</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -21562,12 +21586,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21582,27 +21606,27 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718954</t>
+          <t>https://artportalen.se/Sighting/119934806</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119718955</v>
+        <v>119934808</v>
       </c>
       <c r="B201" t="n">
-        <v>90710</v>
+        <v>90691</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -21610,34 +21634,38 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>752793</v>
+        <v>752819</v>
       </c>
       <c r="R201" t="n">
-        <v>7092549</v>
+        <v>7092515</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21664,12 +21692,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21684,24 +21712,24 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718955</t>
+          <t>https://artportalen.se/Sighting/119934808</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119797530</v>
+        <v>119718954</v>
       </c>
       <c r="B202" t="n">
         <v>90710</v>
@@ -21736,10 +21764,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>752727</v>
+        <v>752778</v>
       </c>
       <c r="R202" t="n">
-        <v>7092459</v>
+        <v>7092543</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21766,19 +21794,19 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG202" t="b">
         <v>0</v>
@@ -21786,24 +21814,24 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797530</t>
+          <t>https://artportalen.se/Sighting/119718954</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119797531</v>
+        <v>119718955</v>
       </c>
       <c r="B203" t="n">
         <v>90710</v>
@@ -21838,10 +21866,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>752941</v>
+        <v>752793</v>
       </c>
       <c r="R203" t="n">
-        <v>7092217</v>
+        <v>7092549</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21868,19 +21896,19 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG203" t="b">
         <v>0</v>
@@ -21888,24 +21916,24 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797531</t>
+          <t>https://artportalen.se/Sighting/119718955</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119808304</v>
+        <v>119797530</v>
       </c>
       <c r="B204" t="n">
         <v>90710</v>
@@ -21940,13 +21968,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>752773</v>
+        <v>752727</v>
       </c>
       <c r="R204" t="n">
-        <v>7092434</v>
+        <v>7092459</v>
       </c>
       <c r="S204" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21973,26 +22001,16 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>11:49</t>
-        </is>
-      </c>
       <c r="AD204" t="b">
         <v>0</v>
       </c>
       <c r="AE204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG204" t="b">
         <v>0</v>
@@ -22000,24 +22018,24 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Yasmine Kindlund</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119808304</t>
+          <t>https://artportalen.se/Sighting/119797530</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119891898</v>
+        <v>119797531</v>
       </c>
       <c r="B205" t="n">
         <v>90710</v>
@@ -22052,10 +22070,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>752740</v>
+        <v>752941</v>
       </c>
       <c r="R205" t="n">
-        <v>7092396</v>
+        <v>7092217</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22082,19 +22100,19 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD205" t="b">
         <v>0</v>
       </c>
       <c r="AE205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG205" t="b">
         <v>0</v>
@@ -22102,24 +22120,24 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891898</t>
+          <t>https://artportalen.se/Sighting/119797531</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119892118</v>
+        <v>119808304</v>
       </c>
       <c r="B206" t="n">
         <v>90710</v>
@@ -22150,17 +22168,17 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>752838</v>
+        <v>752773</v>
       </c>
       <c r="R206" t="n">
-        <v>7092399</v>
+        <v>7092434</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -22184,12 +22202,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-14</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22204,24 +22232,24 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Yasmine Kindlund</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892118</t>
+          <t>https://artportalen.se/Sighting/119808304</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119893598</v>
+        <v>119891898</v>
       </c>
       <c r="B207" t="n">
         <v>90710</v>
@@ -22252,14 +22280,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>752767</v>
+        <v>752740</v>
       </c>
       <c r="R207" t="n">
-        <v>7092395</v>
+        <v>7092396</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22317,13 +22345,13 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893598</t>
+          <t>https://artportalen.se/Sighting/119891898</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119934752</v>
+        <v>119892118</v>
       </c>
       <c r="B208" t="n">
         <v>90710</v>
@@ -22354,14 +22382,14 @@
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>752794</v>
+        <v>752838</v>
       </c>
       <c r="R208" t="n">
-        <v>7092570</v>
+        <v>7092399</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -22396,11 +22424,6 @@
           <t>2024-09-21</t>
         </is>
       </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Äldre fruktkroppar</t>
-        </is>
-      </c>
       <c r="AD208" t="b">
         <v>0</v>
       </c>
@@ -22413,24 +22436,24 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934752</t>
+          <t>https://artportalen.se/Sighting/119892118</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119934753</v>
+        <v>119893598</v>
       </c>
       <c r="B209" t="n">
         <v>90710</v>
@@ -22461,14 +22484,14 @@
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>752888</v>
+        <v>752767</v>
       </c>
       <c r="R209" t="n">
-        <v>7092677</v>
+        <v>7092395</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -22515,24 +22538,24 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934753</t>
+          <t>https://artportalen.se/Sighting/119893598</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119934756</v>
+        <v>119934752</v>
       </c>
       <c r="B210" t="n">
         <v>90710</v>
@@ -22560,21 +22583,17 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>752783</v>
+        <v>752794</v>
       </c>
       <c r="R210" t="n">
-        <v>7092657</v>
+        <v>7092570</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22609,11 +22628,16 @@
           <t>2024-09-21</t>
         </is>
       </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Äldre fruktkroppar</t>
+        </is>
+      </c>
       <c r="AD210" t="b">
         <v>0</v>
       </c>
       <c r="AE210" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG210" t="b">
         <v>0</v>
@@ -22632,13 +22656,13 @@
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119934756</t>
+          <t>https://artportalen.se/Sighting/119934752</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128627826</v>
+        <v>119934753</v>
       </c>
       <c r="B211" t="n">
         <v>90710</v>
@@ -22673,10 +22697,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>753005</v>
+        <v>752888</v>
       </c>
       <c r="R211" t="n">
-        <v>7092360</v>
+        <v>7092677</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22703,12 +22727,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22723,24 +22747,24 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627826</t>
+          <t>https://artportalen.se/Sighting/119934753</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128627830</v>
+        <v>119934756</v>
       </c>
       <c r="B212" t="n">
         <v>90710</v>
@@ -22768,17 +22792,21 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>752818</v>
+        <v>752783</v>
       </c>
       <c r="R212" t="n">
-        <v>7092471</v>
+        <v>7092657</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22805,19 +22833,19 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD212" t="b">
         <v>0</v>
       </c>
       <c r="AE212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -22825,67 +22853,62 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128627830</t>
+          <t>https://artportalen.se/Sighting/119934756</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119797560</v>
+        <v>128627826</v>
       </c>
       <c r="B213" t="n">
-        <v>57950</v>
+        <v>90710</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>100049</v>
+        <v>6286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>752728</v>
+        <v>753005</v>
       </c>
       <c r="R213" t="n">
-        <v>7092269</v>
+        <v>7092360</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22912,17 +22935,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Äldre hack</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -22933,95 +22951,66 @@
       </c>
       <c r="AG213" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL213" t="inlineStr">
-        <is>
-          <t>Torraka</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Torraka</t>
-        </is>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797560</t>
+          <t>https://artportalen.se/Sighting/128627826</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119718957</v>
+        <v>128627830</v>
       </c>
       <c r="B214" t="n">
-        <v>58114</v>
+        <v>90710</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>103021</v>
+        <v>6286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>752907</v>
+        <v>752818</v>
       </c>
       <c r="R214" t="n">
-        <v>7092425</v>
+        <v>7092471</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23048,12 +23037,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23079,44 +23068,44 @@
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119718957</t>
+          <t>https://artportalen.se/Sighting/128627830</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119797532</v>
+        <v>119797560</v>
       </c>
       <c r="B215" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -23125,10 +23114,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>752730</v>
+        <v>752728</v>
       </c>
       <c r="R215" t="n">
-        <v>7092301</v>
+        <v>7092269</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23163,6 +23152,11 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>Äldre hack</t>
+        </is>
+      </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
@@ -23171,6 +23165,26 @@
       </c>
       <c r="AG215" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL215" t="inlineStr">
+        <is>
+          <t>Torraka</t>
+        </is>
+      </c>
+      <c r="AO215" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Torraka</t>
+        </is>
       </c>
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
@@ -23186,13 +23200,13 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797532</t>
+          <t>https://artportalen.se/Sighting/119797560</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119797533</v>
+        <v>119718957</v>
       </c>
       <c r="B216" t="n">
         <v>58114</v>
@@ -23220,10 +23234,14 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -23232,10 +23250,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>752826</v>
+        <v>752907</v>
       </c>
       <c r="R216" t="n">
-        <v>7092234</v>
+        <v>7092425</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23262,12 +23280,12 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23282,24 +23300,24 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119797533</t>
+          <t>https://artportalen.se/Sighting/119718957</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>120374071</v>
+        <v>119797532</v>
       </c>
       <c r="B217" t="n">
         <v>58114</v>
@@ -23328,19 +23346,24 @@
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>752960</v>
+        <v>752730</v>
       </c>
       <c r="R217" t="n">
-        <v>7092251</v>
+        <v>7092301</v>
       </c>
       <c r="S217" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23364,22 +23387,12 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
-        </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23394,24 +23407,24 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120374071</t>
+          <t>https://artportalen.se/Sighting/119797532</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128630176</v>
+        <v>119797533</v>
       </c>
       <c r="B218" t="n">
         <v>58114</v>
@@ -23439,32 +23452,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N218" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P218" t="inlineStr">
         <is>
           <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>752927</v>
+        <v>752826</v>
       </c>
       <c r="R218" t="n">
-        <v>7092361</v>
+        <v>7092234</v>
       </c>
       <c r="S218" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23488,22 +23494,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="Z218" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
-        </is>
-      </c>
-      <c r="AB218" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23529,16 +23525,16 @@
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128630176</t>
+          <t>https://artportalen.se/Sighting/119797533</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128588720</v>
+        <v>120374071</v>
       </c>
       <c r="B219" t="n">
-        <v>92328</v>
+        <v>58114</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -23546,37 +23542,37 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6040162</v>
+        <v>103021</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Kåddisheden, Vb</t>
+          <t>Kåddisheden vid Olles spår, entrén, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>752891</v>
+        <v>752960</v>
       </c>
       <c r="R219" t="n">
-        <v>7092444</v>
+        <v>7092251</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23600,27 +23596,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Talltorraka, med klibbticka och är kottesmedja</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23631,46 +23622,31 @@
       </c>
       <c r="AG219" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ219" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128588720</t>
+          <t>https://artportalen.se/Sighting/120374071</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119891991</v>
+        <v>128630176</v>
       </c>
       <c r="B220" t="n">
-        <v>93218</v>
+        <v>58114</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -23678,34 +23654,49 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6331648</v>
+        <v>103021</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
-        </is>
-      </c>
-      <c r="I220" t="inlineStr"/>
-      <c r="J220" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>752740</v>
+        <v>752927</v>
       </c>
       <c r="R220" t="n">
-        <v>7092396</v>
+        <v>7092361</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -23729,12 +23720,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB220" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -23743,34 +23744,33 @@
       <c r="AE220" t="b">
         <v>0</v>
       </c>
-      <c r="AF220" t="inlineStr"/>
       <c r="AG220" t="b">
         <v>0</v>
       </c>
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119891991</t>
+          <t>https://artportalen.se/Sighting/128630176</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119892970</v>
+        <v>128588720</v>
       </c>
       <c r="B221" t="n">
-        <v>93218</v>
+        <v>92328</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -23778,31 +23778,34 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6331648</v>
+        <v>6040162</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="J221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Kåddisheden, Kåddisheden, Vb</t>
+          <t>Kåddisheden, Vb</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>752853</v>
+        <v>752891</v>
       </c>
       <c r="R221" t="n">
-        <v>7092386</v>
+        <v>7092444</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23829,12 +23832,27 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Talltorraka, med klibbticka och är kottesmedja</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -23843,31 +23861,45 @@
       <c r="AE221" t="b">
         <v>0</v>
       </c>
-      <c r="AF221" t="inlineStr"/>
       <c r="AG221" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT221" t="inlineStr"/>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119892970</t>
+          <t>https://artportalen.se/Sighting/128588720</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119893175</v>
+        <v>119891991</v>
       </c>
       <c r="B222" t="n">
         <v>93218</v>
@@ -23899,10 +23931,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>752982</v>
+        <v>752740</v>
       </c>
       <c r="R222" t="n">
-        <v>7092371</v>
+        <v>7092396</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23961,13 +23993,13 @@
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893175</t>
+          <t>https://artportalen.se/Sighting/119891991</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119893208</v>
+        <v>119892970</v>
       </c>
       <c r="B223" t="n">
         <v>93218</v>
@@ -23999,10 +24031,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>752928</v>
+        <v>752853</v>
       </c>
       <c r="R223" t="n">
-        <v>7092309</v>
+        <v>7092386</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24061,13 +24093,13 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893208</t>
+          <t>https://artportalen.se/Sighting/119892970</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119893225</v>
+        <v>119893175</v>
       </c>
       <c r="B224" t="n">
         <v>93218</v>
@@ -24099,10 +24131,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>752927</v>
+        <v>752982</v>
       </c>
       <c r="R224" t="n">
-        <v>7092298</v>
+        <v>7092371</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24161,13 +24193,13 @@
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893225</t>
+          <t>https://artportalen.se/Sighting/119893175</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119893329</v>
+        <v>119893208</v>
       </c>
       <c r="B225" t="n">
         <v>93218</v>
@@ -24199,10 +24231,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>752893</v>
+        <v>752928</v>
       </c>
       <c r="R225" t="n">
-        <v>7092272</v>
+        <v>7092309</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24261,13 +24293,13 @@
       <c r="AY225" t="inlineStr"/>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893329</t>
+          <t>https://artportalen.se/Sighting/119893208</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119893430</v>
+        <v>119893225</v>
       </c>
       <c r="B226" t="n">
         <v>93218</v>
@@ -24299,10 +24331,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>752897</v>
+        <v>752927</v>
       </c>
       <c r="R226" t="n">
-        <v>7092235</v>
+        <v>7092298</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24361,13 +24393,13 @@
       <c r="AY226" t="inlineStr"/>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893430</t>
+          <t>https://artportalen.se/Sighting/119893225</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119893473</v>
+        <v>119893329</v>
       </c>
       <c r="B227" t="n">
         <v>93218</v>
@@ -24399,10 +24431,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>752827</v>
+        <v>752893</v>
       </c>
       <c r="R227" t="n">
-        <v>7092232</v>
+        <v>7092272</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -24461,13 +24493,13 @@
       <c r="AY227" t="inlineStr"/>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893473</t>
+          <t>https://artportalen.se/Sighting/119893329</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119893483</v>
+        <v>119893430</v>
       </c>
       <c r="B228" t="n">
         <v>93218</v>
@@ -24499,10 +24531,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>752795</v>
+        <v>752897</v>
       </c>
       <c r="R228" t="n">
-        <v>7092265</v>
+        <v>7092235</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -24561,13 +24593,13 @@
       <c r="AY228" t="inlineStr"/>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119893483</t>
+          <t>https://artportalen.se/Sighting/119893430</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119893626</v>
+        <v>119893473</v>
       </c>
       <c r="B229" t="n">
         <v>93218</v>
@@ -24599,10 +24631,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>752767</v>
+        <v>752827</v>
       </c>
       <c r="R229" t="n">
-        <v>7092396</v>
+        <v>7092232</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -24660,6 +24692,206 @@
       </c>
       <c r="AY229" t="inlineStr"/>
       <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893473</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>119893483</v>
+      </c>
+      <c r="B230" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>752795</v>
+      </c>
+      <c r="R230" t="n">
+        <v>7092265</v>
+      </c>
+      <c r="S230" t="n">
+        <v>10</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119893483</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>119893626</v>
+      </c>
+      <c r="B231" t="n">
+        <v>93218</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Kåddisheden, Kåddisheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>752767</v>
+      </c>
+      <c r="R231" t="n">
+        <v>7092396</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF231" t="inlineStr"/>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119893626</t>
         </is>
@@ -24895,6 +25127,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -14837,7 +14837,7 @@
         <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93372</v>
+        <v>93379</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 38554-2024 artfynd.xlsx
+++ b/artfynd/A 38554-2024 artfynd.xlsx
@@ -10160,7 +10160,7 @@
         <v>136339695</v>
       </c>
       <c r="B92" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>135810620</v>
       </c>
       <c r="B137" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>136339459</v>
       </c>
       <c r="B138" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
